--- a/bpsr_key_table.xlsx
+++ b/bpsr_key_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kokoukohiro\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GitHub\BPSRControllerHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DAD3A84-CA4C-4018-88C9-CF41FCD739CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC7B431-EFE3-4FCF-BDBB-695270898243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3473,7 +3473,7 @@
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -3485,188 +3485,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDDEBF7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7159,7 +6977,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="164" spans="1:6" ht="27.75">
+    <row r="164" spans="1:6" ht="28.5">
       <c r="A164" s="2" t="s">
         <v>229</v>
       </c>
@@ -9519,7 +9337,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="282" spans="1:6" ht="28.5">
+    <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
         <v>871</v>
       </c>
@@ -9559,7 +9377,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="27.75">
+    <row r="284" spans="1:6">
       <c r="A284" s="2" t="s">
         <v>278</v>
       </c>
@@ -9599,7 +9417,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="286" spans="1:6" ht="27.75">
+    <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
         <v>875</v>
       </c>
@@ -10239,7 +10057,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="318" spans="1:6" ht="28.5">
+    <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
         <v>883</v>
       </c>
@@ -10259,7 +10077,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="319" spans="1:6" ht="28.5">
+    <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
         <v>884</v>
       </c>
@@ -10419,7 +10237,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="327" spans="1:6" ht="28.5">
+    <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
         <v>890</v>
       </c>
@@ -10439,7 +10257,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="328" spans="1:6" ht="28.5">
+    <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
         <v>892</v>
       </c>
@@ -10579,7 +10397,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="335" spans="1:6" ht="28.5">
+    <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
         <v>896</v>
       </c>
@@ -10599,7 +10417,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="336" spans="1:6" ht="28.5">
+    <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
         <v>897</v>
       </c>
@@ -10999,7 +10817,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="356" spans="1:6" ht="27">
+    <row r="356" spans="1:6">
       <c r="A356" s="2" t="s">
         <v>338</v>
       </c>
@@ -11019,7 +10837,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="357" spans="1:6" ht="28.5">
+    <row r="357" spans="1:6">
       <c r="A357" s="2" t="s">
         <v>339</v>
       </c>
@@ -11179,7 +10997,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="365" spans="1:6" ht="28.5">
+    <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
         <v>913</v>
       </c>
@@ -11199,7 +11017,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="366" spans="1:6" ht="28.5">
+    <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
         <v>915</v>
       </c>
@@ -11359,7 +11177,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="374" spans="1:6" ht="28.5">
+    <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
         <v>921</v>
       </c>
@@ -11399,7 +11217,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="28.5">
+    <row r="376" spans="1:6">
       <c r="A376" s="2" t="s">
         <v>348</v>
       </c>
@@ -11439,7 +11257,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="378" spans="1:6" ht="28.5">
+    <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
         <v>924</v>
       </c>
@@ -14802,20 +14620,20 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="C2:C7 C310:C545 C304:C307 C288:C289 C9:C286">
-    <cfRule type="expression" dxfId="32" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>ISNUMBER(SEARCH("不明",C2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E7 E9:E545">
-    <cfRule type="expression" dxfId="31" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>ISNUMBER(SEARCH("不明",E2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B7 B9:B545">
-    <cfRule type="expression" dxfId="30" priority="6">
+    <cfRule type="expression" dxfId="4" priority="6">
       <formula>B2="controller"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>B2="kb/mouse"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16077,8 +15895,9 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/bpsr_key_table.xlsx
+++ b/bpsr_key_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GitHub\BPSRControllerHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC7B431-EFE3-4FCF-BDBB-695270898243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8690FA-7011-400E-8538-49DE64A71D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2048,9 +2048,6 @@
   </si>
   <si>
     <t>マウス左クリック</t>
-  </si>
-  <si>
-    <t>マウスキー以外設定不可イガイセッテイフカ</t>
   </si>
   <si>
     <t>+0x002BB, +0x0143A</t>
@@ -3329,6 +3326,10 @@
   </si>
   <si>
     <t>+0x00624</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>マウスキー以外設定不可</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3875,10 +3876,10 @@
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1">
@@ -3895,10 +3896,10 @@
         <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3989,7 +3990,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -4157,8 +4158,8 @@
       <c r="E22" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>674</v>
+      <c r="F22" s="3" t="s">
+        <v>1045</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4183,7 +4184,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
@@ -4223,7 +4224,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
@@ -4263,7 +4264,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
@@ -4303,7 +4304,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
@@ -4343,7 +4344,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
@@ -4443,7 +4444,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>7</v>
@@ -4458,12 +4459,12 @@
         <v>673</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
@@ -4503,7 +4504,7 @@
     </row>
     <row r="40" spans="1:6" ht="28.5">
       <c r="A40" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>7</v>
@@ -4543,7 +4544,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>7</v>
@@ -4581,7 +4582,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>7</v>
@@ -4621,7 +4622,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>7</v>
@@ -4656,7 +4657,7 @@
         <v>637</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.5">
@@ -4667,7 +4668,7 @@
         <v>7</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>35</v>
@@ -4721,7 +4722,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>7</v>
@@ -4741,7 +4742,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>7</v>
@@ -4761,47 +4762,47 @@
     </row>
     <row r="53" spans="1:6" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>1016</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>7</v>
@@ -4821,7 +4822,7 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>7</v>
@@ -4836,12 +4837,12 @@
         <v>673</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>7</v>
@@ -4881,7 +4882,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>7</v>
@@ -4921,7 +4922,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>7</v>
@@ -4961,7 +4962,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>7</v>
@@ -4976,12 +4977,12 @@
         <v>553</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>7</v>
@@ -5001,7 +5002,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>7</v>
@@ -5041,7 +5042,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>7</v>
@@ -5056,18 +5057,18 @@
         <v>553</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>703</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>704</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>9</v>
@@ -5081,7 +5082,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>7</v>
@@ -5096,12 +5097,12 @@
         <v>553</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>7</v>
@@ -5121,7 +5122,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>7</v>
@@ -5136,12 +5137,12 @@
         <v>553</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>7</v>
@@ -5161,7 +5162,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>7</v>
@@ -5241,7 +5242,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>7</v>
@@ -5256,18 +5257,18 @@
         <v>553</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
@@ -5281,7 +5282,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>7</v>
@@ -5321,7 +5322,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>7</v>
@@ -5336,12 +5337,12 @@
         <v>553</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
@@ -5361,7 +5362,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>7</v>
@@ -5396,12 +5397,12 @@
         <v>652</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>7</v>
@@ -5416,7 +5417,7 @@
         <v>673</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5441,7 +5442,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>7</v>
@@ -5456,7 +5457,7 @@
         <v>553</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5481,7 +5482,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>7</v>
@@ -5521,7 +5522,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>7</v>
@@ -5561,7 +5562,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>7</v>
@@ -5601,7 +5602,7 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>7</v>
@@ -5641,7 +5642,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>7</v>
@@ -5681,7 +5682,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>7</v>
@@ -5696,7 +5697,7 @@
         <v>553</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -5721,7 +5722,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>7</v>
@@ -5736,7 +5737,7 @@
         <v>553</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5761,7 +5762,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>7</v>
@@ -5776,18 +5777,18 @@
         <v>553</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>728</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
@@ -5801,7 +5802,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>7</v>
@@ -5841,7 +5842,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>7</v>
@@ -5856,18 +5857,18 @@
         <v>553</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
@@ -5879,7 +5880,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>7</v>
@@ -5919,7 +5920,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>7</v>
@@ -5959,7 +5960,7 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>7</v>
@@ -5994,12 +5995,12 @@
         <v>575</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>7</v>
@@ -6014,18 +6015,18 @@
         <v>553</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>737</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>738</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>9</v>
@@ -6039,7 +6040,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>7</v>
@@ -6079,7 +6080,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>7</v>
@@ -6119,7 +6120,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>7</v>
@@ -6159,7 +6160,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>7</v>
@@ -6199,7 +6200,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>7</v>
@@ -6214,18 +6215,18 @@
         <v>553</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>745</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>9</v>
@@ -6239,7 +6240,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>7</v>
@@ -6254,18 +6255,18 @@
         <v>553</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>747</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>748</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>9</v>
@@ -6279,7 +6280,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>7</v>
@@ -6294,18 +6295,18 @@
         <v>553</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>750</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C130" s="2" t="s">
-        <v>751</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>9</v>
@@ -6319,7 +6320,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>7</v>
@@ -6334,18 +6335,18 @@
         <v>553</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>753</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>9</v>
@@ -6359,7 +6360,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>7</v>
@@ -6374,18 +6375,18 @@
         <v>553</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C134" s="2" t="s">
-        <v>757</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>9</v>
@@ -6399,7 +6400,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>7</v>
@@ -6414,18 +6415,18 @@
         <v>553</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>759</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C136" s="2" t="s">
-        <v>760</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>9</v>
@@ -6439,7 +6440,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>7</v>
@@ -6454,18 +6455,18 @@
         <v>553</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>763</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>9</v>
@@ -6479,7 +6480,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>7</v>
@@ -6494,18 +6495,18 @@
         <v>553</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>765</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>766</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>9</v>
@@ -6519,7 +6520,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>7</v>
@@ -6534,18 +6535,18 @@
         <v>553</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="2" t="s">
         <v>768</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C142" s="2" t="s">
-        <v>769</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>9</v>
@@ -6559,7 +6560,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>7</v>
@@ -6574,18 +6575,18 @@
         <v>553</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="2" t="s">
         <v>771</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>9</v>
@@ -6599,7 +6600,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>7</v>
@@ -6614,18 +6615,18 @@
         <v>553</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>774</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>775</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>9</v>
@@ -6679,7 +6680,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>7</v>
@@ -6694,18 +6695,18 @@
         <v>553</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>9</v>
@@ -6719,7 +6720,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>7</v>
@@ -6734,18 +6735,18 @@
         <v>553</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>779</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>780</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>9</v>
@@ -6799,13 +6800,13 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>781</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>782</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -6825,7 +6826,7 @@
         <v>24</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>25</v>
@@ -6845,7 +6846,7 @@
         <v>24</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>25</v>
@@ -6865,7 +6866,7 @@
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>9</v>
@@ -6879,7 +6880,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>7</v>
@@ -6919,7 +6920,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>7</v>
@@ -6959,7 +6960,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>7</v>
@@ -6974,7 +6975,7 @@
         <v>553</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="28.5">
@@ -6985,7 +6986,7 @@
         <v>7</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>9</v>
@@ -6999,7 +7000,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>7</v>
@@ -7014,7 +7015,7 @@
         <v>553</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="27.75">
@@ -7025,7 +7026,7 @@
         <v>7</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>9</v>
@@ -7039,7 +7040,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>7</v>
@@ -7054,7 +7055,7 @@
         <v>553</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="27.75">
@@ -7065,7 +7066,7 @@
         <v>7</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>9</v>
@@ -7079,7 +7080,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>7</v>
@@ -7094,7 +7095,7 @@
         <v>553</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="27.75">
@@ -7105,7 +7106,7 @@
         <v>7</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>9</v>
@@ -7279,7 +7280,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>7</v>
@@ -7339,7 +7340,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>7</v>
@@ -7359,7 +7360,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>7</v>
@@ -7374,18 +7375,18 @@
         <v>553</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>793</v>
-      </c>
-      <c r="B184" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>794</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>9</v>
@@ -7399,7 +7400,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>7</v>
@@ -7419,7 +7420,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>7</v>
@@ -7439,7 +7440,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>7</v>
@@ -7454,12 +7455,12 @@
         <v>553</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>7</v>
@@ -7479,7 +7480,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>7</v>
@@ -7494,12 +7495,12 @@
         <v>553</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>7</v>
@@ -7514,12 +7515,12 @@
         <v>553</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>7</v>
@@ -7534,7 +7535,7 @@
         <v>553</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7559,7 +7560,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>7</v>
@@ -7574,12 +7575,12 @@
         <v>553</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>7</v>
@@ -7594,12 +7595,12 @@
         <v>673</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>7</v>
@@ -7614,12 +7615,12 @@
         <v>553</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>7</v>
@@ -7634,12 +7635,12 @@
         <v>553</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>7</v>
@@ -7654,12 +7655,12 @@
         <v>553</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>7</v>
@@ -7674,12 +7675,12 @@
         <v>553</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>7</v>
@@ -7694,12 +7695,12 @@
         <v>553</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>7</v>
@@ -7714,12 +7715,12 @@
         <v>553</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>7</v>
@@ -7734,12 +7735,12 @@
         <v>553</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>7</v>
@@ -7754,12 +7755,12 @@
         <v>553</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>7</v>
@@ -7774,12 +7775,12 @@
         <v>553</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>7</v>
@@ -7794,7 +7795,7 @@
         <v>553</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -7819,7 +7820,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>7</v>
@@ -7839,7 +7840,7 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>7</v>
@@ -7859,7 +7860,7 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>7</v>
@@ -7874,12 +7875,12 @@
         <v>673</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>7</v>
@@ -7894,12 +7895,12 @@
         <v>553</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>7</v>
@@ -7914,12 +7915,12 @@
         <v>553</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>7</v>
@@ -7934,12 +7935,12 @@
         <v>553</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>7</v>
@@ -7954,12 +7955,12 @@
         <v>553</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>7</v>
@@ -7974,12 +7975,12 @@
         <v>553</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>7</v>
@@ -7994,12 +7995,12 @@
         <v>553</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>7</v>
@@ -8014,12 +8015,12 @@
         <v>553</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>7</v>
@@ -8034,12 +8035,12 @@
         <v>553</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>7</v>
@@ -8054,7 +8055,7 @@
         <v>553</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8099,7 +8100,7 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>7</v>
@@ -8114,12 +8115,12 @@
         <v>553</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>7</v>
@@ -8159,7 +8160,7 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>7</v>
@@ -8174,7 +8175,7 @@
         <v>553</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -8199,7 +8200,7 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>7</v>
@@ -8214,7 +8215,7 @@
         <v>673</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -8239,7 +8240,7 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>7</v>
@@ -8254,7 +8255,7 @@
         <v>553</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -8279,7 +8280,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>7</v>
@@ -8294,12 +8295,12 @@
         <v>553</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>7</v>
@@ -8314,12 +8315,12 @@
         <v>553</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>7</v>
@@ -8334,12 +8335,12 @@
         <v>553</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>7</v>
@@ -8354,12 +8355,12 @@
         <v>553</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>7</v>
@@ -8374,12 +8375,12 @@
         <v>553</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>7</v>
@@ -8394,7 +8395,7 @@
         <v>553</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -8419,7 +8420,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>7</v>
@@ -8434,7 +8435,7 @@
         <v>553</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -8459,7 +8460,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>7</v>
@@ -8474,12 +8475,12 @@
         <v>553</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>7</v>
@@ -8494,12 +8495,12 @@
         <v>553</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>7</v>
@@ -8514,12 +8515,12 @@
         <v>553</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>7</v>
@@ -8534,7 +8535,7 @@
         <v>553</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -8579,7 +8580,7 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>7</v>
@@ -8594,12 +8595,12 @@
         <v>553</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>7</v>
@@ -8614,12 +8615,12 @@
         <v>553</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>7</v>
@@ -8634,12 +8635,12 @@
         <v>553</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>7</v>
@@ -8654,12 +8655,12 @@
         <v>553</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>7</v>
@@ -8674,12 +8675,12 @@
         <v>553</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>7</v>
@@ -8694,12 +8695,12 @@
         <v>553</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>7</v>
@@ -8714,12 +8715,12 @@
         <v>553</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>7</v>
@@ -8734,12 +8735,12 @@
         <v>553</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>7</v>
@@ -8754,12 +8755,12 @@
         <v>553</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>7</v>
@@ -8774,12 +8775,12 @@
         <v>553</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>7</v>
@@ -8794,12 +8795,12 @@
         <v>553</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>7</v>
@@ -8814,12 +8815,12 @@
         <v>553</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>7</v>
@@ -8834,12 +8835,12 @@
         <v>553</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>7</v>
@@ -8854,12 +8855,12 @@
         <v>553</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>7</v>
@@ -8874,12 +8875,12 @@
         <v>553</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>7</v>
@@ -8894,7 +8895,7 @@
         <v>553</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -8939,7 +8940,7 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>7</v>
@@ -8954,12 +8955,12 @@
         <v>553</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>7</v>
@@ -8974,12 +8975,12 @@
         <v>553</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>7</v>
@@ -8994,7 +8995,7 @@
         <v>553</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -9019,7 +9020,7 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>7</v>
@@ -9034,12 +9035,12 @@
         <v>553</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>7</v>
@@ -9054,7 +9055,7 @@
         <v>553</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -9079,7 +9080,7 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>7</v>
@@ -9094,12 +9095,12 @@
         <v>553</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>7</v>
@@ -9114,12 +9115,12 @@
         <v>553</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>7</v>
@@ -9134,7 +9135,7 @@
         <v>553</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -9159,7 +9160,7 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>7</v>
@@ -9174,7 +9175,7 @@
         <v>553</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -9199,7 +9200,7 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>7</v>
@@ -9214,7 +9215,7 @@
         <v>553</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -9239,7 +9240,7 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>7</v>
@@ -9254,7 +9255,7 @@
         <v>553</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -9279,7 +9280,7 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>7</v>
@@ -9294,7 +9295,7 @@
         <v>553</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -9319,7 +9320,7 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>7</v>
@@ -9334,12 +9335,12 @@
         <v>553</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>24</v>
@@ -9351,15 +9352,15 @@
         <v>25</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>7</v>
@@ -9374,7 +9375,7 @@
         <v>553</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -9391,7 +9392,7 @@
         <v>25</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>279</v>
@@ -9399,7 +9400,7 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>7</v>
@@ -9414,12 +9415,12 @@
         <v>553</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>24</v>
@@ -9431,10 +9432,10 @@
         <v>25</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -9445,7 +9446,7 @@
         <v>24</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>25</v>
@@ -9479,7 +9480,7 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>7</v>
@@ -9494,7 +9495,7 @@
         <v>553</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -9505,7 +9506,7 @@
         <v>7</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>9</v>
@@ -9525,7 +9526,7 @@
         <v>24</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>25</v>
@@ -9545,7 +9546,7 @@
         <v>7</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>9</v>
@@ -9565,7 +9566,7 @@
         <v>24</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>25</v>
@@ -9585,7 +9586,7 @@
         <v>7</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>9</v>
@@ -9605,7 +9606,7 @@
         <v>7</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>9</v>
@@ -9625,7 +9626,7 @@
         <v>24</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>25</v>
@@ -9645,7 +9646,7 @@
         <v>24</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>25</v>
@@ -9665,7 +9666,7 @@
         <v>7</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>9</v>
@@ -9685,7 +9686,7 @@
         <v>24</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>25</v>
@@ -9705,7 +9706,7 @@
         <v>7</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -9725,7 +9726,7 @@
         <v>24</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>25</v>
@@ -9745,7 +9746,7 @@
         <v>7</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -9765,7 +9766,7 @@
         <v>24</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>25</v>
@@ -9865,7 +9866,7 @@
         <v>7</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -9885,7 +9886,7 @@
         <v>24</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>25</v>
@@ -9899,7 +9900,7 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>7</v>
@@ -9914,7 +9915,7 @@
         <v>553</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -9945,7 +9946,7 @@
         <v>7</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>9</v>
@@ -9965,7 +9966,7 @@
         <v>7</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>9</v>
@@ -9985,7 +9986,7 @@
         <v>7</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>9</v>
@@ -9999,7 +10000,7 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>7</v>
@@ -10025,7 +10026,7 @@
         <v>7</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>9</v>
@@ -10039,7 +10040,7 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>7</v>
@@ -10059,47 +10060,47 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F318" s="13" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>7</v>
@@ -10114,7 +10115,7 @@
         <v>673</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -10125,7 +10126,7 @@
         <v>7</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>9</v>
@@ -10145,7 +10146,7 @@
         <v>7</v>
       </c>
       <c r="C322" s="13" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>9</v>
@@ -10165,7 +10166,7 @@
         <v>7</v>
       </c>
       <c r="C323" s="13" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>9</v>
@@ -10179,7 +10180,7 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>7</v>
@@ -10205,7 +10206,7 @@
         <v>7</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>9</v>
@@ -10219,7 +10220,7 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>7</v>
@@ -10239,42 +10240,42 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -10285,7 +10286,7 @@
         <v>7</v>
       </c>
       <c r="C329" s="13" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>9</v>
@@ -10305,7 +10306,7 @@
         <v>7</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>9</v>
@@ -10325,7 +10326,7 @@
         <v>7</v>
       </c>
       <c r="C331" s="13" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>9</v>
@@ -10339,7 +10340,7 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>7</v>
@@ -10365,7 +10366,7 @@
         <v>7</v>
       </c>
       <c r="C333" s="13" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -10379,7 +10380,7 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>7</v>
@@ -10399,47 +10400,47 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>7</v>
@@ -10465,7 +10466,7 @@
         <v>7</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>9</v>
@@ -10485,7 +10486,7 @@
         <v>24</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>25</v>
@@ -10505,7 +10506,7 @@
         <v>7</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>9</v>
@@ -10525,7 +10526,7 @@
         <v>24</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>25</v>
@@ -10545,7 +10546,7 @@
         <v>7</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -10565,7 +10566,7 @@
         <v>24</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>25</v>
@@ -10585,7 +10586,7 @@
         <v>7</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>9</v>
@@ -10605,7 +10606,7 @@
         <v>24</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>25</v>
@@ -10625,7 +10626,7 @@
         <v>7</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>9</v>
@@ -10645,7 +10646,7 @@
         <v>24</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>25</v>
@@ -10665,7 +10666,7 @@
         <v>7</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>9</v>
@@ -10685,7 +10686,7 @@
         <v>24</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>25</v>
@@ -10699,7 +10700,7 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>7</v>
@@ -10714,7 +10715,7 @@
         <v>553</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="351" spans="1:6">
@@ -10725,7 +10726,7 @@
         <v>7</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>9</v>
@@ -10739,7 +10740,7 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>7</v>
@@ -10754,7 +10755,7 @@
         <v>553</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -10779,7 +10780,7 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>7</v>
@@ -10794,7 +10795,7 @@
         <v>553</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -10825,7 +10826,7 @@
         <v>7</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>9</v>
@@ -10845,7 +10846,7 @@
         <v>24</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>25</v>
@@ -10865,7 +10866,7 @@
         <v>7</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>9</v>
@@ -10885,7 +10886,7 @@
         <v>24</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>25</v>
@@ -10899,7 +10900,7 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>7</v>
@@ -10914,12 +10915,12 @@
         <v>617</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>7</v>
@@ -10934,7 +10935,7 @@
         <v>553</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -10945,7 +10946,7 @@
         <v>7</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>9</v>
@@ -10959,7 +10960,7 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>7</v>
@@ -10979,7 +10980,7 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>7</v>
@@ -10999,7 +11000,7 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>24</v>
@@ -11011,15 +11012,15 @@
         <v>25</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>24</v>
@@ -11031,15 +11032,15 @@
         <v>25</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>7</v>
@@ -11054,7 +11055,7 @@
         <v>553</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -11079,7 +11080,7 @@
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>7</v>
@@ -11094,7 +11095,7 @@
         <v>553</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -11119,7 +11120,7 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>7</v>
@@ -11134,7 +11135,7 @@
         <v>553</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -11159,7 +11160,7 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>7</v>
@@ -11174,12 +11175,12 @@
         <v>553</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>24</v>
@@ -11191,15 +11192,15 @@
         <v>25</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>7</v>
@@ -11214,7 +11215,7 @@
         <v>553</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -11231,7 +11232,7 @@
         <v>25</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>279</v>
@@ -11239,7 +11240,7 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>7</v>
@@ -11254,12 +11255,12 @@
         <v>553</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>24</v>
@@ -11271,15 +11272,15 @@
         <v>25</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>7</v>
@@ -11294,7 +11295,7 @@
         <v>553</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -11325,7 +11326,7 @@
         <v>7</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>35</v>
@@ -11345,7 +11346,7 @@
         <v>24</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>25</v>
@@ -11365,7 +11366,7 @@
         <v>24</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>25</v>
@@ -11459,7 +11460,7 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B388" t="s">
         <v>7</v>
@@ -11474,7 +11475,7 @@
         <v>553</v>
       </c>
       <c r="F388" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -11499,7 +11500,7 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B390" t="s">
         <v>7</v>
@@ -11514,7 +11515,7 @@
         <v>673</v>
       </c>
       <c r="F390" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -11759,7 +11760,7 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B403" t="s">
         <v>24</v>
@@ -11774,12 +11775,12 @@
         <v>641</v>
       </c>
       <c r="F403" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B404" t="s">
         <v>7</v>
@@ -11794,7 +11795,7 @@
         <v>553</v>
       </c>
       <c r="F404" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -11879,7 +11880,7 @@
     </row>
     <row r="409" spans="1:6">
       <c r="A409" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B409" t="s">
         <v>7</v>
@@ -11919,7 +11920,7 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B411" t="s">
         <v>7</v>
@@ -11939,7 +11940,7 @@
     </row>
     <row r="412" spans="1:6">
       <c r="A412" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B412" t="s">
         <v>24</v>
@@ -11951,15 +11952,15 @@
         <v>25</v>
       </c>
       <c r="E412" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="F412" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B413" t="s">
         <v>24</v>
@@ -11971,10 +11972,10 @@
         <v>25</v>
       </c>
       <c r="E413" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="F413" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -12059,7 +12060,7 @@
     </row>
     <row r="418" spans="1:6">
       <c r="A418" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B418" t="s">
         <v>7</v>
@@ -12074,7 +12075,7 @@
         <v>553</v>
       </c>
       <c r="F418" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -12099,7 +12100,7 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B420" t="s">
         <v>7</v>
@@ -12114,7 +12115,7 @@
         <v>553</v>
       </c>
       <c r="F420" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -12139,7 +12140,7 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B422" t="s">
         <v>7</v>
@@ -12154,7 +12155,7 @@
         <v>553</v>
       </c>
       <c r="F422" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -12179,7 +12180,7 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B424" t="s">
         <v>7</v>
@@ -12194,7 +12195,7 @@
         <v>553</v>
       </c>
       <c r="F424" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="425" spans="1:6">
@@ -12219,7 +12220,7 @@
     </row>
     <row r="426" spans="1:6">
       <c r="A426" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B426" t="s">
         <v>7</v>
@@ -12234,7 +12235,7 @@
         <v>553</v>
       </c>
       <c r="F426" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -12259,7 +12260,7 @@
     </row>
     <row r="428" spans="1:6">
       <c r="A428" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B428" t="s">
         <v>7</v>
@@ -12274,7 +12275,7 @@
         <v>553</v>
       </c>
       <c r="F428" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -12299,7 +12300,7 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B430" t="s">
         <v>7</v>
@@ -12314,7 +12315,7 @@
         <v>553</v>
       </c>
       <c r="F430" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -12339,7 +12340,7 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B432" t="s">
         <v>7</v>
@@ -12354,7 +12355,7 @@
         <v>553</v>
       </c>
       <c r="F432" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -12379,7 +12380,7 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B434" t="s">
         <v>7</v>
@@ -12394,7 +12395,7 @@
         <v>553</v>
       </c>
       <c r="F434" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -12419,7 +12420,7 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B436" t="s">
         <v>7</v>
@@ -12434,7 +12435,7 @@
         <v>553</v>
       </c>
       <c r="F436" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -12459,7 +12460,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B438" t="s">
         <v>7</v>
@@ -12474,7 +12475,7 @@
         <v>553</v>
       </c>
       <c r="F438" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -12499,7 +12500,7 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B440" t="s">
         <v>7</v>
@@ -12514,7 +12515,7 @@
         <v>553</v>
       </c>
       <c r="F440" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -12539,7 +12540,7 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B442" t="s">
         <v>7</v>
@@ -12554,7 +12555,7 @@
         <v>553</v>
       </c>
       <c r="F442" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -12579,7 +12580,7 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B444" t="s">
         <v>7</v>
@@ -12594,7 +12595,7 @@
         <v>553</v>
       </c>
       <c r="F444" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -12619,7 +12620,7 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B446" t="s">
         <v>7</v>
@@ -12634,7 +12635,7 @@
         <v>553</v>
       </c>
       <c r="F446" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -12659,7 +12660,7 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B448" t="s">
         <v>7</v>
@@ -12674,7 +12675,7 @@
         <v>553</v>
       </c>
       <c r="F448" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -12699,7 +12700,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B450" t="s">
         <v>7</v>
@@ -12714,7 +12715,7 @@
         <v>553</v>
       </c>
       <c r="F450" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="451" spans="1:6">
@@ -12739,7 +12740,7 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B452" t="s">
         <v>7</v>
@@ -12754,7 +12755,7 @@
         <v>553</v>
       </c>
       <c r="F452" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="453" spans="1:6">
@@ -12779,7 +12780,7 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B454" t="s">
         <v>7</v>
@@ -12794,7 +12795,7 @@
         <v>553</v>
       </c>
       <c r="F454" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -12819,7 +12820,7 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B456" t="s">
         <v>7</v>
@@ -12834,7 +12835,7 @@
         <v>553</v>
       </c>
       <c r="F456" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="457" spans="1:6">
@@ -12859,7 +12860,7 @@
     </row>
     <row r="458" spans="1:6">
       <c r="A458" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B458" t="s">
         <v>7</v>
@@ -12874,7 +12875,7 @@
         <v>553</v>
       </c>
       <c r="F458" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -12899,7 +12900,7 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B460" t="s">
         <v>7</v>
@@ -12914,7 +12915,7 @@
         <v>553</v>
       </c>
       <c r="F460" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="461" spans="1:6">
@@ -12939,7 +12940,7 @@
     </row>
     <row r="462" spans="1:6">
       <c r="A462" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B462" t="s">
         <v>7</v>
@@ -12954,7 +12955,7 @@
         <v>553</v>
       </c>
       <c r="F462" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="463" spans="1:6">
@@ -12979,7 +12980,7 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B464" t="s">
         <v>7</v>
@@ -12994,7 +12995,7 @@
         <v>553</v>
       </c>
       <c r="F464" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -13019,7 +13020,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B466" t="s">
         <v>7</v>
@@ -13034,7 +13035,7 @@
         <v>553</v>
       </c>
       <c r="F466" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -13059,7 +13060,7 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B468" t="s">
         <v>7</v>
@@ -13074,7 +13075,7 @@
         <v>553</v>
       </c>
       <c r="F468" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="469" spans="1:6">
@@ -13099,7 +13100,7 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B470" t="s">
         <v>7</v>
@@ -13114,7 +13115,7 @@
         <v>553</v>
       </c>
       <c r="F470" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -13139,7 +13140,7 @@
     </row>
     <row r="472" spans="1:6">
       <c r="A472" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B472" t="s">
         <v>7</v>
@@ -13154,7 +13155,7 @@
         <v>553</v>
       </c>
       <c r="F472" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -13179,7 +13180,7 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B474" t="s">
         <v>7</v>
@@ -13194,7 +13195,7 @@
         <v>553</v>
       </c>
       <c r="F474" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="475" spans="1:6">
@@ -13219,7 +13220,7 @@
     </row>
     <row r="476" spans="1:6">
       <c r="A476" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B476" t="s">
         <v>7</v>
@@ -13234,7 +13235,7 @@
         <v>553</v>
       </c>
       <c r="F476" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -13259,7 +13260,7 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B478" t="s">
         <v>7</v>
@@ -13274,7 +13275,7 @@
         <v>553</v>
       </c>
       <c r="F478" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -13299,7 +13300,7 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B480" t="s">
         <v>7</v>
@@ -13314,7 +13315,7 @@
         <v>553</v>
       </c>
       <c r="F480" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="481" spans="1:6">
@@ -13339,7 +13340,7 @@
     </row>
     <row r="482" spans="1:6">
       <c r="A482" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B482" t="s">
         <v>7</v>
@@ -13354,7 +13355,7 @@
         <v>553</v>
       </c>
       <c r="F482" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -13379,7 +13380,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B484" t="s">
         <v>7</v>
@@ -13394,7 +13395,7 @@
         <v>553</v>
       </c>
       <c r="F484" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -13419,7 +13420,7 @@
     </row>
     <row r="486" spans="1:6">
       <c r="A486" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B486" t="s">
         <v>7</v>
@@ -13434,7 +13435,7 @@
         <v>553</v>
       </c>
       <c r="F486" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="487" spans="1:6">
@@ -13459,7 +13460,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B488" t="s">
         <v>7</v>
@@ -13474,7 +13475,7 @@
         <v>553</v>
       </c>
       <c r="F488" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -13499,7 +13500,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B490" t="s">
         <v>7</v>
@@ -13514,7 +13515,7 @@
         <v>553</v>
       </c>
       <c r="F490" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="491" spans="1:6">
@@ -13539,7 +13540,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B492" t="s">
         <v>7</v>
@@ -13554,7 +13555,7 @@
         <v>553</v>
       </c>
       <c r="F492" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -13579,7 +13580,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B494" t="s">
         <v>7</v>
@@ -13594,7 +13595,7 @@
         <v>553</v>
       </c>
       <c r="F494" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -13619,7 +13620,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B496" t="s">
         <v>7</v>
@@ -13634,7 +13635,7 @@
         <v>553</v>
       </c>
       <c r="F496" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="497" spans="1:6">
@@ -13659,7 +13660,7 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B498" t="s">
         <v>7</v>
@@ -13674,7 +13675,7 @@
         <v>553</v>
       </c>
       <c r="F498" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -13699,7 +13700,7 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B500" t="s">
         <v>7</v>
@@ -13714,7 +13715,7 @@
         <v>553</v>
       </c>
       <c r="F500" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="501" spans="1:6">
@@ -13739,7 +13740,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B502" t="s">
         <v>7</v>
@@ -13754,7 +13755,7 @@
         <v>553</v>
       </c>
       <c r="F502" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="503" spans="1:6">
@@ -13779,7 +13780,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B504" t="s">
         <v>7</v>
@@ -13794,7 +13795,7 @@
         <v>553</v>
       </c>
       <c r="F504" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="505" spans="1:6">
@@ -13819,7 +13820,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B506" t="s">
         <v>7</v>
@@ -13834,7 +13835,7 @@
         <v>553</v>
       </c>
       <c r="F506" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="507" spans="1:6">
@@ -13859,7 +13860,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B508" t="s">
         <v>7</v>
@@ -13874,7 +13875,7 @@
         <v>553</v>
       </c>
       <c r="F508" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -13899,7 +13900,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B510" t="s">
         <v>7</v>
@@ -13914,7 +13915,7 @@
         <v>553</v>
       </c>
       <c r="F510" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -13939,7 +13940,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B512" t="s">
         <v>7</v>
@@ -13954,7 +13955,7 @@
         <v>553</v>
       </c>
       <c r="F512" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -13979,7 +13980,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B514" t="s">
         <v>7</v>
@@ -13994,7 +13995,7 @@
         <v>553</v>
       </c>
       <c r="F514" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="515" spans="1:6">
@@ -14019,7 +14020,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B516" t="s">
         <v>7</v>
@@ -14034,7 +14035,7 @@
         <v>553</v>
       </c>
       <c r="F516" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="517" spans="1:6">
@@ -14059,7 +14060,7 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B518" t="s">
         <v>7</v>
@@ -14074,7 +14075,7 @@
         <v>553</v>
       </c>
       <c r="F518" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="519" spans="1:6">
@@ -14099,7 +14100,7 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B520" t="s">
         <v>7</v>
@@ -14114,7 +14115,7 @@
         <v>553</v>
       </c>
       <c r="F520" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="521" spans="1:6">
@@ -14139,7 +14140,7 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B522" t="s">
         <v>7</v>
@@ -14154,7 +14155,7 @@
         <v>553</v>
       </c>
       <c r="F522" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="523" spans="1:6">
@@ -14179,7 +14180,7 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B524" t="s">
         <v>7</v>
@@ -14194,7 +14195,7 @@
         <v>553</v>
       </c>
       <c r="F524" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="525" spans="1:6">
@@ -14219,7 +14220,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B526" t="s">
         <v>7</v>
@@ -14234,7 +14235,7 @@
         <v>553</v>
       </c>
       <c r="F526" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="527" spans="1:6">
@@ -14259,7 +14260,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B528" t="s">
         <v>7</v>
@@ -14274,7 +14275,7 @@
         <v>553</v>
       </c>
       <c r="F528" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="529" spans="1:6">
@@ -14299,7 +14300,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B530" t="s">
         <v>7</v>
@@ -14314,7 +14315,7 @@
         <v>553</v>
       </c>
       <c r="F530" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="531" spans="1:6">
@@ -14339,7 +14340,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B532" t="s">
         <v>7</v>
@@ -14354,7 +14355,7 @@
         <v>553</v>
       </c>
       <c r="F532" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="533" spans="1:6">
@@ -14379,7 +14380,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B534" t="s">
         <v>7</v>
@@ -14394,7 +14395,7 @@
         <v>553</v>
       </c>
       <c r="F534" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="535" spans="1:6">
@@ -14419,7 +14420,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B536" t="s">
         <v>7</v>
@@ -14434,7 +14435,7 @@
         <v>553</v>
       </c>
       <c r="F536" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="537" spans="1:6">
@@ -14459,7 +14460,7 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B538" t="s">
         <v>7</v>
@@ -14474,7 +14475,7 @@
         <v>553</v>
       </c>
       <c r="F538" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
     <row r="539" spans="1:6">
@@ -14539,7 +14540,7 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B542" t="s">
         <v>7</v>
@@ -14554,12 +14555,12 @@
         <v>673</v>
       </c>
       <c r="F542" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="543" spans="1:6">
       <c r="A543" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B543" t="s">
         <v>7</v>
@@ -14574,12 +14575,12 @@
         <v>673</v>
       </c>
       <c r="F543" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="544" spans="1:6">
       <c r="A544" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B544" t="s">
         <v>7</v>
@@ -14594,12 +14595,12 @@
         <v>673</v>
       </c>
       <c r="F544" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="545" spans="1:6">
       <c r="A545" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B545" t="s">
         <v>7</v>
@@ -14614,7 +14615,7 @@
         <v>673</v>
       </c>
       <c r="F545" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
   </sheetData>

--- a/bpsr_key_table.xlsx
+++ b/bpsr_key_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GitHub\BPSRControllerHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8690FA-7011-400E-8538-49DE64A71D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E2620CC-7FAA-4BA4-8E69-7191AC4C5E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="1046">
   <si>
     <t>offsets</t>
   </si>
@@ -1873,9 +1873,6 @@
     <t>0x00000134</t>
   </si>
   <si>
-    <t>マウス左クリックヒダリ</t>
-  </si>
-  <si>
     <t>0x00000000</t>
   </si>
   <si>
@@ -1924,12 +1921,6 @@
     <t>コントローラ</t>
   </si>
   <si>
-    <t>L方向入力</t>
-  </si>
-  <si>
-    <t>R方向入力</t>
-  </si>
-  <si>
     <t>L2</t>
   </si>
   <si>
@@ -2020,9 +2011,6 @@
     <t>type=0x00000002, value=0x00000005</t>
   </si>
   <si>
-    <t>+0x000B2</t>
-  </si>
-  <si>
     <t>移動-前後</t>
   </si>
   <si>
@@ -2662,9 +2650,6 @@
     <t>+0x02284</t>
   </si>
   <si>
-    <t>撮影モードカメラ移動-上ウエ</t>
-  </si>
-  <si>
     <t>+0x022EB</t>
   </si>
   <si>
@@ -2698,15 +2683,9 @@
     <t>+0x0239F</t>
   </si>
   <si>
-    <t>撮影モードカメラパン-上下</t>
-  </si>
-  <si>
     <t>+0x023B4</t>
   </si>
   <si>
-    <t>撮影モードカメラパン-左右</t>
-  </si>
-  <si>
     <t>+0x0240D</t>
   </si>
   <si>
@@ -2764,13 +2743,7 @@
     <t>+0x02731</t>
   </si>
   <si>
-    <t>+0x0273A</t>
-  </si>
-  <si>
     <t>key=0x00000003, state=単独, third=0x00000001</t>
-  </si>
-  <si>
-    <t>+0x0274F</t>
   </si>
   <si>
     <t>key=0x00000004, state=単独, third=0x00000002</t>
@@ -3122,12 +3095,6 @@
   </si>
   <si>
     <t>撮影モードカメラパン-左</t>
-  </si>
-  <si>
-    <t>撮影モードカメラ移動-上下</t>
-  </si>
-  <si>
-    <t>撮影モードカメラ移動-左右</t>
   </si>
   <si>
     <t>撮影モードキャラ移動-上</t>
@@ -3330,6 +3297,197 @@
   </si>
   <si>
     <t>マウスキー以外設定不可</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撮影モードカメラ移動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>上</t>
+    </r>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>マウス左クリック</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x000B2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>前後入力</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>ゼンゴ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>L</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>左右</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>入力</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>サユウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>前後入力</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>ゼンゴ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t>R</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>左右入力</t>
+    </r>
+    <rPh sb="1" eb="3">
+      <t>サユウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撮影モードカメラパン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>上下</t>
+    </r>
+    <rPh sb="12" eb="13">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撮影モードカメラパン</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>左右</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>サユウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x0273A</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x0274F</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -3552,7 +3710,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="KeyListTable" displayName="KeyListTable" ref="A1:C111">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="KeyListTable" displayName="KeyListTable" ref="A1:C113">
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="入力種別"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="キー"/>
@@ -3804,7 +3962,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
@@ -3819,7 +3977,7 @@
         <v>561</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3844,7 +4002,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>7</v>
@@ -3856,55 +4014,55 @@
         <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>664</v>
+        <v>1037</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>7</v>
@@ -3916,10 +4074,10 @@
         <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3956,7 +4114,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>243</v>
@@ -3964,7 +4122,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>7</v>
@@ -3976,10 +4134,10 @@
         <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3990,7 +4148,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1041</v>
+        <v>1030</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -4036,7 +4194,7 @@
         <v>35</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>36</v>
@@ -4056,7 +4214,7 @@
         <v>25</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>39</v>
@@ -4064,7 +4222,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>7</v>
@@ -4096,7 +4254,7 @@
         <v>25</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>43</v>
@@ -4116,7 +4274,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>29</v>
@@ -4144,7 +4302,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>7</v>
@@ -4156,10 +4314,10 @@
         <v>35</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1045</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4176,7 +4334,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>50</v>
@@ -4184,7 +4342,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>7</v>
@@ -4216,7 +4374,7 @@
         <v>25</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>54</v>
@@ -4224,7 +4382,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>7</v>
@@ -4256,7 +4414,7 @@
         <v>25</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>58</v>
@@ -4264,7 +4422,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="2" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>7</v>
@@ -4296,7 +4454,7 @@
         <v>25</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>62</v>
@@ -4304,7 +4462,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>7</v>
@@ -4336,7 +4494,7 @@
         <v>25</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>66</v>
@@ -4344,7 +4502,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>7</v>
@@ -4416,7 +4574,7 @@
         <v>25</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>76</v>
@@ -4436,7 +4594,7 @@
         <v>35</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>79</v>
@@ -4444,7 +4602,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>7</v>
@@ -4456,15 +4614,15 @@
         <v>35</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>7</v>
@@ -4496,7 +4654,7 @@
         <v>25</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>83</v>
@@ -4504,7 +4662,7 @@
     </row>
     <row r="40" spans="1:6" ht="28.5">
       <c r="A40" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>7</v>
@@ -4536,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>87</v>
@@ -4544,7 +4702,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>7</v>
@@ -4574,7 +4732,7 @@
         <v>25</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>90</v>
@@ -4582,7 +4740,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>7</v>
@@ -4622,7 +4780,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>7</v>
@@ -4654,10 +4812,10 @@
         <v>25</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="28.5">
@@ -4668,13 +4826,13 @@
         <v>7</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>98</v>
@@ -4694,7 +4852,7 @@
         <v>25</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>101</v>
@@ -4714,7 +4872,7 @@
         <v>25</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>104</v>
@@ -4722,7 +4880,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>7</v>
@@ -4734,15 +4892,15 @@
         <v>35</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>7</v>
@@ -4754,55 +4912,55 @@
         <v>35</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>1044</v>
+        <v>1033</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>7</v>
@@ -4814,15 +4972,15 @@
         <v>35</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>7</v>
@@ -4834,15 +4992,15 @@
         <v>35</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>7</v>
@@ -4874,7 +5032,7 @@
         <v>25</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>108</v>
@@ -4882,7 +5040,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>7</v>
@@ -4922,7 +5080,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>7</v>
@@ -4954,7 +5112,7 @@
         <v>25</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>108</v>
@@ -4962,7 +5120,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>7</v>
@@ -4977,12 +5135,12 @@
         <v>553</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>7</v>
@@ -5002,7 +5160,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>7</v>
@@ -5034,7 +5192,7 @@
         <v>25</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>121</v>
@@ -5042,7 +5200,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>7</v>
@@ -5057,18 +5215,18 @@
         <v>553</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>9</v>
@@ -5082,7 +5240,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>7</v>
@@ -5097,12 +5255,12 @@
         <v>553</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>7</v>
@@ -5122,7 +5280,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>7</v>
@@ -5137,12 +5295,12 @@
         <v>553</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>7</v>
@@ -5162,7 +5320,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>7</v>
@@ -5194,7 +5352,7 @@
         <v>25</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>130</v>
@@ -5234,7 +5392,7 @@
         <v>25</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>135</v>
@@ -5242,7 +5400,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>7</v>
@@ -5257,18 +5415,18 @@
         <v>553</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
@@ -5282,7 +5440,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>7</v>
@@ -5297,7 +5455,7 @@
         <v>561</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -5314,7 +5472,7 @@
         <v>25</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>76</v>
@@ -5322,7 +5480,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>7</v>
@@ -5337,12 +5495,12 @@
         <v>553</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>7</v>
@@ -5362,7 +5520,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>7</v>
@@ -5394,15 +5552,15 @@
         <v>25</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>7</v>
@@ -5414,10 +5572,10 @@
         <v>35</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -5434,7 +5592,7 @@
         <v>25</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>50</v>
@@ -5442,7 +5600,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>7</v>
@@ -5457,7 +5615,7 @@
         <v>553</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -5482,7 +5640,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>7</v>
@@ -5514,7 +5672,7 @@
         <v>25</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>149</v>
@@ -5522,7 +5680,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>7</v>
@@ -5554,7 +5712,7 @@
         <v>25</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>153</v>
@@ -5562,7 +5720,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>7</v>
@@ -5594,7 +5752,7 @@
         <v>25</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>157</v>
@@ -5602,7 +5760,7 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>7</v>
@@ -5634,7 +5792,7 @@
         <v>25</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>161</v>
@@ -5642,7 +5800,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>7</v>
@@ -5674,7 +5832,7 @@
         <v>25</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>83</v>
@@ -5682,7 +5840,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>7</v>
@@ -5697,7 +5855,7 @@
         <v>553</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -5722,7 +5880,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>7</v>
@@ -5737,7 +5895,7 @@
         <v>553</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -5762,7 +5920,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>7</v>
@@ -5777,18 +5935,18 @@
         <v>553</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
@@ -5802,7 +5960,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>7</v>
@@ -5834,7 +5992,7 @@
         <v>25</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>172</v>
@@ -5842,7 +6000,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>7</v>
@@ -5857,18 +6015,18 @@
         <v>553</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1038</v>
+        <v>1027</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
@@ -5880,7 +6038,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>7</v>
@@ -5912,7 +6070,7 @@
         <v>25</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>176</v>
@@ -5920,7 +6078,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="2" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>7</v>
@@ -5960,7 +6118,7 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>7</v>
@@ -5995,12 +6153,12 @@
         <v>575</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>7</v>
@@ -6015,18 +6173,18 @@
         <v>553</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="116" spans="1:6">
       <c r="A116" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>9</v>
@@ -6040,7 +6198,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>7</v>
@@ -6072,7 +6230,7 @@
         <v>25</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>130</v>
@@ -6080,7 +6238,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" s="2" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>7</v>
@@ -6112,7 +6270,7 @@
         <v>25</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>189</v>
@@ -6120,7 +6278,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>7</v>
@@ -6160,7 +6318,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>7</v>
@@ -6200,7 +6358,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>7</v>
@@ -6215,18 +6373,18 @@
         <v>553</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="126" spans="1:6">
       <c r="A126" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>9</v>
@@ -6240,7 +6398,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>7</v>
@@ -6255,18 +6413,18 @@
         <v>553</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="128" spans="1:6">
       <c r="A128" s="2" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>9</v>
@@ -6280,7 +6438,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>7</v>
@@ -6295,18 +6453,18 @@
         <v>553</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="130" spans="1:6">
       <c r="A130" s="2" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>9</v>
@@ -6320,7 +6478,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>7</v>
@@ -6335,18 +6493,18 @@
         <v>553</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="132" spans="1:6">
       <c r="A132" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>9</v>
@@ -6360,7 +6518,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" s="2" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>7</v>
@@ -6375,18 +6533,18 @@
         <v>553</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="134" spans="1:6">
       <c r="A134" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>9</v>
@@ -6400,7 +6558,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>7</v>
@@ -6415,18 +6573,18 @@
         <v>553</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="136" spans="1:6">
       <c r="A136" s="2" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>9</v>
@@ -6440,7 +6598,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" s="2" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>7</v>
@@ -6455,18 +6613,18 @@
         <v>553</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="138" spans="1:6">
       <c r="A138" s="2" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>9</v>
@@ -6480,7 +6638,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" s="2" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>7</v>
@@ -6495,18 +6653,18 @@
         <v>553</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="140" spans="1:6">
       <c r="A140" s="2" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>9</v>
@@ -6520,7 +6678,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" s="2" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>7</v>
@@ -6535,18 +6693,18 @@
         <v>553</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="142" spans="1:6">
       <c r="A142" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>9</v>
@@ -6560,7 +6718,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" s="2" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>7</v>
@@ -6575,18 +6733,18 @@
         <v>553</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="144" spans="1:6">
       <c r="A144" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>9</v>
@@ -6600,7 +6758,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>7</v>
@@ -6615,18 +6773,18 @@
         <v>553</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>9</v>
@@ -6672,7 +6830,7 @@
         <v>25</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>29</v>
@@ -6680,7 +6838,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>7</v>
@@ -6695,18 +6853,18 @@
         <v>553</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="150" spans="1:6">
       <c r="A150" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1037</v>
+        <v>1026</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>9</v>
@@ -6720,7 +6878,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>7</v>
@@ -6735,18 +6893,18 @@
         <v>553</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="152" spans="1:6">
       <c r="A152" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>9</v>
@@ -6800,13 +6958,13 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -6826,7 +6984,7 @@
         <v>24</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>25</v>
@@ -6846,7 +7004,7 @@
         <v>24</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>25</v>
@@ -6866,7 +7024,7 @@
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>9</v>
@@ -6880,7 +7038,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>7</v>
@@ -6920,7 +7078,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>7</v>
@@ -6960,7 +7118,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>7</v>
@@ -6975,7 +7133,7 @@
         <v>553</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="28.5">
@@ -6986,7 +7144,7 @@
         <v>7</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>1033</v>
+        <v>1022</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>9</v>
@@ -7000,7 +7158,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>7</v>
@@ -7015,7 +7173,7 @@
         <v>553</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="27.75">
@@ -7026,7 +7184,7 @@
         <v>7</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>1034</v>
+        <v>1023</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>9</v>
@@ -7040,7 +7198,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B167" s="2" t="s">
         <v>7</v>
@@ -7055,7 +7213,7 @@
         <v>553</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="27.75">
@@ -7066,7 +7224,7 @@
         <v>7</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>1035</v>
+        <v>1024</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>9</v>
@@ -7080,7 +7238,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>7</v>
@@ -7095,7 +7253,7 @@
         <v>553</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="170" spans="1:6" ht="27.75">
@@ -7106,7 +7264,7 @@
         <v>7</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>1036</v>
+        <v>1025</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>9</v>
@@ -7152,7 +7310,7 @@
         <v>25</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F172" s="2" t="s">
         <v>153</v>
@@ -7192,7 +7350,7 @@
         <v>25</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>243</v>
@@ -7232,7 +7390,7 @@
         <v>25</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F176" s="2" t="s">
         <v>39</v>
@@ -7272,7 +7430,7 @@
         <v>25</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>50</v>
@@ -7280,7 +7438,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>7</v>
@@ -7312,7 +7470,7 @@
         <v>25</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F180" s="2" t="s">
         <v>252</v>
@@ -7332,7 +7490,7 @@
         <v>25</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F181" s="2" t="s">
         <v>161</v>
@@ -7340,7 +7498,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" s="2" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>7</v>
@@ -7360,7 +7518,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>7</v>
@@ -7375,18 +7533,18 @@
         <v>553</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="2" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>9</v>
@@ -7400,7 +7558,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="2" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>7</v>
@@ -7415,12 +7573,12 @@
         <v>561</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>7</v>
@@ -7432,15 +7590,15 @@
         <v>35</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>7</v>
@@ -7455,12 +7613,12 @@
         <v>553</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="2" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>7</v>
@@ -7472,15 +7630,15 @@
         <v>35</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>7</v>
@@ -7495,12 +7653,12 @@
         <v>553</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>7</v>
@@ -7515,12 +7673,12 @@
         <v>553</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>7</v>
@@ -7535,7 +7693,7 @@
         <v>553</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -7560,7 +7718,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>7</v>
@@ -7575,12 +7733,12 @@
         <v>553</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="2" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>7</v>
@@ -7592,15 +7750,15 @@
         <v>35</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>7</v>
@@ -7615,12 +7773,12 @@
         <v>553</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>7</v>
@@ -7635,12 +7793,12 @@
         <v>553</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>7</v>
@@ -7655,12 +7813,12 @@
         <v>553</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>7</v>
@@ -7675,12 +7833,12 @@
         <v>553</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>7</v>
@@ -7695,12 +7853,12 @@
         <v>553</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>7</v>
@@ -7715,12 +7873,12 @@
         <v>553</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="2" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>7</v>
@@ -7735,12 +7893,12 @@
         <v>553</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>7</v>
@@ -7755,12 +7913,12 @@
         <v>553</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="2" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>7</v>
@@ -7775,12 +7933,12 @@
         <v>553</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>7</v>
@@ -7795,7 +7953,7 @@
         <v>553</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -7812,7 +7970,7 @@
         <v>25</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F205" s="2" t="s">
         <v>243</v>
@@ -7820,7 +7978,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>7</v>
@@ -7832,15 +7990,15 @@
         <v>35</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="2" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>7</v>
@@ -7852,15 +8010,15 @@
         <v>35</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>7</v>
@@ -7872,15 +8030,15 @@
         <v>35</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="2" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>7</v>
@@ -7895,12 +8053,12 @@
         <v>553</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="2" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>7</v>
@@ -7915,12 +8073,12 @@
         <v>553</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="2" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>7</v>
@@ -7935,12 +8093,12 @@
         <v>553</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>7</v>
@@ -7955,12 +8113,12 @@
         <v>553</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>7</v>
@@ -7975,12 +8133,12 @@
         <v>553</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>7</v>
@@ -7995,12 +8153,12 @@
         <v>553</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>7</v>
@@ -8015,12 +8173,12 @@
         <v>553</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="2" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>7</v>
@@ -8035,12 +8193,12 @@
         <v>553</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>7</v>
@@ -8055,7 +8213,7 @@
         <v>553</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -8092,7 +8250,7 @@
         <v>25</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>39</v>
@@ -8100,7 +8258,7 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="2" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>7</v>
@@ -8115,12 +8273,12 @@
         <v>553</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="2" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>7</v>
@@ -8135,7 +8293,7 @@
         <v>561</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -8152,7 +8310,7 @@
         <v>25</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F222" s="2" t="s">
         <v>76</v>
@@ -8160,7 +8318,7 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="2" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>7</v>
@@ -8175,7 +8333,7 @@
         <v>553</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -8192,7 +8350,7 @@
         <v>25</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F224" s="2" t="s">
         <v>87</v>
@@ -8200,7 +8358,7 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>7</v>
@@ -8212,10 +8370,10 @@
         <v>35</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -8232,7 +8390,7 @@
         <v>25</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>50</v>
@@ -8240,7 +8398,7 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="2" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>7</v>
@@ -8255,7 +8413,7 @@
         <v>553</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -8280,7 +8438,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>7</v>
@@ -8295,12 +8453,12 @@
         <v>553</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>7</v>
@@ -8315,12 +8473,12 @@
         <v>553</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>7</v>
@@ -8335,12 +8493,12 @@
         <v>553</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="2" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>7</v>
@@ -8355,12 +8513,12 @@
         <v>553</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>7</v>
@@ -8375,12 +8533,12 @@
         <v>553</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>7</v>
@@ -8395,7 +8553,7 @@
         <v>553</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -8420,7 +8578,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>7</v>
@@ -8435,7 +8593,7 @@
         <v>553</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -8460,7 +8618,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="2" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>7</v>
@@ -8475,12 +8633,12 @@
         <v>553</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="2" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>7</v>
@@ -8495,12 +8653,12 @@
         <v>553</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="2" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>7</v>
@@ -8515,12 +8673,12 @@
         <v>553</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="2" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>7</v>
@@ -8535,7 +8693,7 @@
         <v>553</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="242" spans="1:6">
@@ -8580,7 +8738,7 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="2" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>7</v>
@@ -8595,12 +8753,12 @@
         <v>553</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="2" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>7</v>
@@ -8615,12 +8773,12 @@
         <v>553</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="2" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>7</v>
@@ -8635,12 +8793,12 @@
         <v>553</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="2" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>7</v>
@@ -8655,12 +8813,12 @@
         <v>553</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="2" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>7</v>
@@ -8675,12 +8833,12 @@
         <v>553</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="2" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>7</v>
@@ -8695,12 +8853,12 @@
         <v>553</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>7</v>
@@ -8715,12 +8873,12 @@
         <v>553</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="2" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>7</v>
@@ -8735,12 +8893,12 @@
         <v>553</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="2" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>7</v>
@@ -8755,12 +8913,12 @@
         <v>553</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>7</v>
@@ -8775,12 +8933,12 @@
         <v>553</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="2" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>7</v>
@@ -8795,12 +8953,12 @@
         <v>553</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>7</v>
@@ -8815,12 +8973,12 @@
         <v>553</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>7</v>
@@ -8835,12 +8993,12 @@
         <v>553</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>7</v>
@@ -8855,12 +9013,12 @@
         <v>553</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>7</v>
@@ -8875,12 +9033,12 @@
         <v>553</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>7</v>
@@ -8895,7 +9053,7 @@
         <v>553</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="260" spans="1:6">
@@ -8932,7 +9090,7 @@
         <v>25</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F261" s="2" t="s">
         <v>29</v>
@@ -8940,7 +9098,7 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="2" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>7</v>
@@ -8955,12 +9113,12 @@
         <v>553</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>7</v>
@@ -8975,12 +9133,12 @@
         <v>553</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="2" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>7</v>
@@ -8995,7 +9153,7 @@
         <v>553</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="265" spans="1:6">
@@ -9020,7 +9178,7 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="2" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>7</v>
@@ -9035,12 +9193,12 @@
         <v>553</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>7</v>
@@ -9055,7 +9213,7 @@
         <v>553</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="268" spans="1:6">
@@ -9080,7 +9238,7 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>7</v>
@@ -9095,12 +9253,12 @@
         <v>553</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>7</v>
@@ -9115,12 +9273,12 @@
         <v>553</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>7</v>
@@ -9135,7 +9293,7 @@
         <v>553</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="272" spans="1:6">
@@ -9160,7 +9318,7 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="2" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>7</v>
@@ -9175,7 +9333,7 @@
         <v>553</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="274" spans="1:6">
@@ -9200,7 +9358,7 @@
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>7</v>
@@ -9215,7 +9373,7 @@
         <v>553</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="276" spans="1:6">
@@ -9240,7 +9398,7 @@
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>7</v>
@@ -9255,7 +9413,7 @@
         <v>553</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="278" spans="1:6">
@@ -9280,7 +9438,7 @@
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>7</v>
@@ -9295,7 +9453,7 @@
         <v>553</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="280" spans="1:6">
@@ -9312,7 +9470,7 @@
         <v>25</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>50</v>
@@ -9320,7 +9478,7 @@
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="2" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>7</v>
@@ -9335,12 +9493,12 @@
         <v>553</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>24</v>
@@ -9352,15 +9510,15 @@
         <v>25</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="2" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>7</v>
@@ -9375,7 +9533,7 @@
         <v>553</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="284" spans="1:6">
@@ -9392,7 +9550,7 @@
         <v>25</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>279</v>
@@ -9400,7 +9558,7 @@
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="2" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>7</v>
@@ -9415,12 +9573,12 @@
         <v>553</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>24</v>
@@ -9432,10 +9590,10 @@
         <v>25</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="287" spans="1:6">
@@ -9446,13 +9604,13 @@
         <v>24</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F287" s="2" t="s">
         <v>83</v>
@@ -9480,7 +9638,7 @@
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>7</v>
@@ -9495,7 +9653,7 @@
         <v>553</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="290" spans="1:6">
@@ -9506,7 +9664,7 @@
         <v>7</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>9</v>
@@ -9526,13 +9684,13 @@
         <v>24</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>1005</v>
+        <v>996</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F291" s="2" t="s">
         <v>243</v>
@@ -9546,7 +9704,7 @@
         <v>7</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>9</v>
@@ -9566,13 +9724,13 @@
         <v>24</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>1006</v>
+        <v>997</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F293" s="2" t="s">
         <v>149</v>
@@ -9586,7 +9744,7 @@
         <v>7</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>9</v>
@@ -9606,7 +9764,7 @@
         <v>7</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>9</v>
@@ -9626,13 +9784,13 @@
         <v>24</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>1007</v>
+        <v>998</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>101</v>
@@ -9646,13 +9804,13 @@
         <v>24</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>104</v>
@@ -9666,7 +9824,7 @@
         <v>7</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>9</v>
@@ -9686,13 +9844,13 @@
         <v>24</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>130</v>
@@ -9706,7 +9864,7 @@
         <v>7</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -9726,13 +9884,13 @@
         <v>24</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F301" s="2" t="s">
         <v>39</v>
@@ -9746,7 +9904,7 @@
         <v>7</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -9766,13 +9924,13 @@
         <v>24</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F303" s="2" t="s">
         <v>298</v>
@@ -9812,7 +9970,7 @@
         <v>25</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F305" s="2" t="s">
         <v>108</v>
@@ -9852,7 +10010,7 @@
         <v>25</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F307" s="2" t="s">
         <v>130</v>
@@ -9866,7 +10024,7 @@
         <v>7</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -9886,13 +10044,13 @@
         <v>24</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="F309" s="2" t="s">
         <v>135</v>
@@ -9900,7 +10058,7 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" s="2" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>7</v>
@@ -9915,7 +10073,7 @@
         <v>553</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="311" spans="1:6">
@@ -9945,8 +10103,8 @@
       <c r="B312" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C312" s="2" t="s">
-        <v>878</v>
+      <c r="C312" s="13" t="s">
+        <v>1035</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>9</v>
@@ -9966,7 +10124,7 @@
         <v>7</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>9</v>
@@ -9986,7 +10144,7 @@
         <v>7</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>9</v>
@@ -10000,7 +10158,7 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" s="2" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>7</v>
@@ -10015,7 +10173,7 @@
         <v>561</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -10026,7 +10184,7 @@
         <v>7</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="D316" s="2" t="s">
         <v>9</v>
@@ -10040,7 +10198,7 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" s="2" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>7</v>
@@ -10052,55 +10210,55 @@
         <v>35</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>1025</v>
+        <v>28</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="F318" s="13" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1026</v>
+        <v>28</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>7</v>
@@ -10112,10 +10270,10 @@
         <v>35</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -10126,7 +10284,7 @@
         <v>7</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>9</v>
@@ -10146,7 +10304,7 @@
         <v>7</v>
       </c>
       <c r="C322" s="13" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>9</v>
@@ -10166,7 +10324,7 @@
         <v>7</v>
       </c>
       <c r="C323" s="13" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>9</v>
@@ -10180,7 +10338,7 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>7</v>
@@ -10195,7 +10353,7 @@
         <v>561</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -10206,7 +10364,7 @@
         <v>7</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>9</v>
@@ -10220,7 +10378,7 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>7</v>
@@ -10232,50 +10390,50 @@
         <v>35</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>890</v>
+        <v>28</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>892</v>
+        <v>28</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -10286,7 +10444,7 @@
         <v>7</v>
       </c>
       <c r="C329" s="13" t="s">
-        <v>1027</v>
+        <v>1016</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>9</v>
@@ -10306,7 +10464,7 @@
         <v>7</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1028</v>
+        <v>1017</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>9</v>
@@ -10326,7 +10484,7 @@
         <v>7</v>
       </c>
       <c r="C331" s="13" t="s">
-        <v>1032</v>
+        <v>1021</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>9</v>
@@ -10340,7 +10498,7 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>7</v>
@@ -10355,7 +10513,7 @@
         <v>561</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -10366,7 +10524,7 @@
         <v>7</v>
       </c>
       <c r="C333" s="13" t="s">
-        <v>1031</v>
+        <v>1020</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -10380,7 +10538,7 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
-        <v>894</v>
+        <v>887</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>7</v>
@@ -10392,55 +10550,55 @@
         <v>35</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
-        <v>895</v>
+        <v>888</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>1029</v>
+        <v>1018</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
-        <v>896</v>
+        <v>889</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
-        <v>897</v>
+        <v>890</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>7</v>
@@ -10452,10 +10610,10 @@
         <v>35</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -10466,7 +10624,7 @@
         <v>7</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>9</v>
@@ -10486,13 +10644,13 @@
         <v>24</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>898</v>
+        <v>891</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F339" s="2" t="s">
         <v>153</v>
@@ -10506,7 +10664,7 @@
         <v>7</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>9</v>
@@ -10526,13 +10684,13 @@
         <v>24</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>899</v>
+        <v>892</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F341" s="2" t="s">
         <v>54</v>
@@ -10546,7 +10704,7 @@
         <v>7</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -10566,13 +10724,13 @@
         <v>24</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F343" s="2" t="s">
         <v>58</v>
@@ -10586,7 +10744,7 @@
         <v>7</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>9</v>
@@ -10606,13 +10764,13 @@
         <v>24</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>901</v>
+        <v>894</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F345" s="2" t="s">
         <v>62</v>
@@ -10626,7 +10784,7 @@
         <v>7</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>9</v>
@@ -10646,13 +10804,13 @@
         <v>24</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F347" s="2" t="s">
         <v>66</v>
@@ -10666,7 +10824,7 @@
         <v>7</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>9</v>
@@ -10686,13 +10844,13 @@
         <v>24</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F349" s="2" t="s">
         <v>172</v>
@@ -10700,7 +10858,7 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
-        <v>904</v>
+        <v>897</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>7</v>
@@ -10715,7 +10873,7 @@
         <v>553</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="351" spans="1:6">
@@ -10726,7 +10884,7 @@
         <v>7</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>9</v>
@@ -10740,7 +10898,7 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
-        <v>905</v>
+        <v>898</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>7</v>
@@ -10755,7 +10913,7 @@
         <v>553</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="353" spans="1:6">
@@ -10780,7 +10938,7 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>7</v>
@@ -10795,7 +10953,7 @@
         <v>553</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="355" spans="1:6">
@@ -10826,7 +10984,7 @@
         <v>7</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>9</v>
@@ -10846,7 +11004,7 @@
         <v>24</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>25</v>
@@ -10866,7 +11024,7 @@
         <v>7</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>9</v>
@@ -10886,7 +11044,7 @@
         <v>24</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>25</v>
@@ -10900,7 +11058,7 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
-        <v>907</v>
+        <v>900</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>7</v>
@@ -10912,15 +11070,15 @@
         <v>35</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="2" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>7</v>
@@ -10935,7 +11093,7 @@
         <v>553</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="362" spans="1:6">
@@ -10946,7 +11104,7 @@
         <v>7</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>9</v>
@@ -10960,7 +11118,7 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="2" t="s">
-        <v>910</v>
+        <v>903</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>7</v>
@@ -10972,15 +11130,15 @@
         <v>35</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
-        <v>911</v>
+        <v>904</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>7</v>
@@ -10992,55 +11150,55 @@
         <v>35</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
-        <v>912</v>
+        <v>1044</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C365" s="2" t="s">
-        <v>28</v>
+      <c r="C365" s="13" t="s">
+        <v>1042</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>913</v>
+        <v>905</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
-        <v>914</v>
+        <v>1045</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C366" s="2" t="s">
-        <v>28</v>
+      <c r="C366" s="13" t="s">
+        <v>1043</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>7</v>
@@ -11055,7 +11213,7 @@
         <v>553</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -11072,7 +11230,7 @@
         <v>35</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F368" s="2" t="s">
         <v>345</v>
@@ -11080,7 +11238,7 @@
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>7</v>
@@ -11095,7 +11253,7 @@
         <v>553</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -11112,7 +11270,7 @@
         <v>35</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F370" s="2" t="s">
         <v>345</v>
@@ -11120,7 +11278,7 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>7</v>
@@ -11135,7 +11293,7 @@
         <v>553</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -11152,7 +11310,7 @@
         <v>25</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F372" s="2" t="s">
         <v>87</v>
@@ -11160,7 +11318,7 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>7</v>
@@ -11175,12 +11333,12 @@
         <v>553</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>24</v>
@@ -11192,15 +11350,15 @@
         <v>25</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>7</v>
@@ -11215,7 +11373,7 @@
         <v>553</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -11232,7 +11390,7 @@
         <v>25</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>279</v>
@@ -11240,7 +11398,7 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="2" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>7</v>
@@ -11255,12 +11413,12 @@
         <v>553</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>24</v>
@@ -11272,15 +11430,15 @@
         <v>25</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>7</v>
@@ -11295,7 +11453,7 @@
         <v>553</v>
       </c>
       <c r="F379" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -11312,7 +11470,7 @@
         <v>25</v>
       </c>
       <c r="E380" s="2" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F380" s="2" t="s">
         <v>50</v>
@@ -11326,13 +11484,13 @@
         <v>7</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>35</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="F381" s="2" t="s">
         <v>345</v>
@@ -11346,13 +11504,13 @@
         <v>24</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F382" s="2" t="s">
         <v>352</v>
@@ -11366,13 +11524,13 @@
         <v>24</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="F383" s="2" t="s">
         <v>354</v>
@@ -11412,7 +11570,7 @@
         <v>25</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="F385" s="2" t="s">
         <v>83</v>
@@ -11460,7 +11618,7 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="B388" t="s">
         <v>7</v>
@@ -11475,7 +11633,7 @@
         <v>553</v>
       </c>
       <c r="F388" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -11500,7 +11658,7 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="B390" t="s">
         <v>7</v>
@@ -11512,10 +11670,10 @@
         <v>35</v>
       </c>
       <c r="E390" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F390" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -11532,7 +11690,7 @@
         <v>25</v>
       </c>
       <c r="E391" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F391" t="s">
         <v>50</v>
@@ -11572,7 +11730,7 @@
         <v>25</v>
       </c>
       <c r="E393" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F393" t="s">
         <v>43</v>
@@ -11612,7 +11770,7 @@
         <v>25</v>
       </c>
       <c r="E395" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="F395" t="s">
         <v>157</v>
@@ -11652,7 +11810,7 @@
         <v>25</v>
       </c>
       <c r="E397" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="F397" t="s">
         <v>29</v>
@@ -11692,7 +11850,7 @@
         <v>25</v>
       </c>
       <c r="E399" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F399" t="s">
         <v>161</v>
@@ -11732,7 +11890,7 @@
         <v>25</v>
       </c>
       <c r="E401" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F401" t="s">
         <v>66</v>
@@ -11760,7 +11918,7 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="B403" t="s">
         <v>24</v>
@@ -11772,15 +11930,15 @@
         <v>25</v>
       </c>
       <c r="E403" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="F403" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="B404" t="s">
         <v>7</v>
@@ -11795,7 +11953,7 @@
         <v>553</v>
       </c>
       <c r="F404" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -11880,7 +12038,7 @@
     </row>
     <row r="409" spans="1:6">
       <c r="A409" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="B409" t="s">
         <v>7</v>
@@ -11895,7 +12053,7 @@
         <v>561</v>
       </c>
       <c r="F409" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -11920,7 +12078,7 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="B411" t="s">
         <v>7</v>
@@ -11932,15 +12090,15 @@
         <v>35</v>
       </c>
       <c r="E411" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="F411" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="B412" t="s">
         <v>24</v>
@@ -11952,15 +12110,15 @@
         <v>25</v>
       </c>
       <c r="E412" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="F412" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="B413" t="s">
         <v>24</v>
@@ -11972,10 +12130,10 @@
         <v>25</v>
       </c>
       <c r="E413" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F413" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -12012,7 +12170,7 @@
         <v>25</v>
       </c>
       <c r="E415" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="F415" t="s">
         <v>108</v>
@@ -12052,7 +12210,7 @@
         <v>25</v>
       </c>
       <c r="E417" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F417" t="s">
         <v>39</v>
@@ -12060,7 +12218,7 @@
     </row>
     <row r="418" spans="1:6">
       <c r="A418" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="B418" t="s">
         <v>7</v>
@@ -12075,7 +12233,7 @@
         <v>553</v>
       </c>
       <c r="F418" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="419" spans="1:6">
@@ -12100,7 +12258,7 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="B420" t="s">
         <v>7</v>
@@ -12115,7 +12273,7 @@
         <v>553</v>
       </c>
       <c r="F420" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="421" spans="1:6">
@@ -12140,7 +12298,7 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B422" t="s">
         <v>7</v>
@@ -12155,7 +12313,7 @@
         <v>553</v>
       </c>
       <c r="F422" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="423" spans="1:6">
@@ -12180,7 +12338,7 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="B424" t="s">
         <v>7</v>
@@ -12195,7 +12353,7 @@
         <v>553</v>
       </c>
       <c r="F424" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="425" spans="1:6">
@@ -12220,7 +12378,7 @@
     </row>
     <row r="426" spans="1:6">
       <c r="A426" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="B426" t="s">
         <v>7</v>
@@ -12235,7 +12393,7 @@
         <v>553</v>
       </c>
       <c r="F426" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="427" spans="1:6">
@@ -12260,7 +12418,7 @@
     </row>
     <row r="428" spans="1:6">
       <c r="A428" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B428" t="s">
         <v>7</v>
@@ -12275,7 +12433,7 @@
         <v>553</v>
       </c>
       <c r="F428" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="429" spans="1:6">
@@ -12300,7 +12458,7 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="B430" t="s">
         <v>7</v>
@@ -12315,7 +12473,7 @@
         <v>553</v>
       </c>
       <c r="F430" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="431" spans="1:6">
@@ -12340,7 +12498,7 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="B432" t="s">
         <v>7</v>
@@ -12355,7 +12513,7 @@
         <v>553</v>
       </c>
       <c r="F432" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="433" spans="1:6">
@@ -12380,7 +12538,7 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="B434" t="s">
         <v>7</v>
@@ -12395,7 +12553,7 @@
         <v>553</v>
       </c>
       <c r="F434" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="435" spans="1:6">
@@ -12420,7 +12578,7 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="B436" t="s">
         <v>7</v>
@@ -12435,7 +12593,7 @@
         <v>553</v>
       </c>
       <c r="F436" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="437" spans="1:6">
@@ -12460,7 +12618,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="B438" t="s">
         <v>7</v>
@@ -12475,7 +12633,7 @@
         <v>553</v>
       </c>
       <c r="F438" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="439" spans="1:6">
@@ -12500,7 +12658,7 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="B440" t="s">
         <v>7</v>
@@ -12515,7 +12673,7 @@
         <v>553</v>
       </c>
       <c r="F440" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="441" spans="1:6">
@@ -12540,7 +12698,7 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="B442" t="s">
         <v>7</v>
@@ -12555,7 +12713,7 @@
         <v>553</v>
       </c>
       <c r="F442" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="443" spans="1:6">
@@ -12580,7 +12738,7 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="B444" t="s">
         <v>7</v>
@@ -12595,7 +12753,7 @@
         <v>553</v>
       </c>
       <c r="F444" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="445" spans="1:6">
@@ -12620,7 +12778,7 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B446" t="s">
         <v>7</v>
@@ -12635,7 +12793,7 @@
         <v>553</v>
       </c>
       <c r="F446" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -12660,7 +12818,7 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="B448" t="s">
         <v>7</v>
@@ -12675,7 +12833,7 @@
         <v>553</v>
       </c>
       <c r="F448" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -12700,7 +12858,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="B450" t="s">
         <v>7</v>
@@ -12715,7 +12873,7 @@
         <v>553</v>
       </c>
       <c r="F450" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="451" spans="1:6">
@@ -12740,7 +12898,7 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="B452" t="s">
         <v>7</v>
@@ -12755,7 +12913,7 @@
         <v>553</v>
       </c>
       <c r="F452" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="453" spans="1:6">
@@ -12780,7 +12938,7 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="B454" t="s">
         <v>7</v>
@@ -12795,7 +12953,7 @@
         <v>553</v>
       </c>
       <c r="F454" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -12820,7 +12978,7 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="B456" t="s">
         <v>7</v>
@@ -12835,7 +12993,7 @@
         <v>553</v>
       </c>
       <c r="F456" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="457" spans="1:6">
@@ -12860,7 +13018,7 @@
     </row>
     <row r="458" spans="1:6">
       <c r="A458" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="B458" t="s">
         <v>7</v>
@@ -12875,7 +13033,7 @@
         <v>553</v>
       </c>
       <c r="F458" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -12900,7 +13058,7 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="B460" t="s">
         <v>7</v>
@@ -12915,7 +13073,7 @@
         <v>553</v>
       </c>
       <c r="F460" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="461" spans="1:6">
@@ -12940,7 +13098,7 @@
     </row>
     <row r="462" spans="1:6">
       <c r="A462" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="B462" t="s">
         <v>7</v>
@@ -12955,7 +13113,7 @@
         <v>553</v>
       </c>
       <c r="F462" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="463" spans="1:6">
@@ -12980,7 +13138,7 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="B464" t="s">
         <v>7</v>
@@ -12995,7 +13153,7 @@
         <v>553</v>
       </c>
       <c r="F464" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -13020,7 +13178,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B466" t="s">
         <v>7</v>
@@ -13035,7 +13193,7 @@
         <v>553</v>
       </c>
       <c r="F466" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -13060,7 +13218,7 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="B468" t="s">
         <v>7</v>
@@ -13075,7 +13233,7 @@
         <v>553</v>
       </c>
       <c r="F468" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="469" spans="1:6">
@@ -13100,7 +13258,7 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="B470" t="s">
         <v>7</v>
@@ -13115,7 +13273,7 @@
         <v>553</v>
       </c>
       <c r="F470" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -13140,7 +13298,7 @@
     </row>
     <row r="472" spans="1:6">
       <c r="A472" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="B472" t="s">
         <v>7</v>
@@ -13155,7 +13313,7 @@
         <v>553</v>
       </c>
       <c r="F472" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -13180,7 +13338,7 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="B474" t="s">
         <v>7</v>
@@ -13195,7 +13353,7 @@
         <v>553</v>
       </c>
       <c r="F474" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="475" spans="1:6">
@@ -13220,7 +13378,7 @@
     </row>
     <row r="476" spans="1:6">
       <c r="A476" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B476" t="s">
         <v>7</v>
@@ -13235,7 +13393,7 @@
         <v>553</v>
       </c>
       <c r="F476" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -13260,7 +13418,7 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="B478" t="s">
         <v>7</v>
@@ -13275,7 +13433,7 @@
         <v>553</v>
       </c>
       <c r="F478" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -13300,7 +13458,7 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="B480" t="s">
         <v>7</v>
@@ -13315,7 +13473,7 @@
         <v>553</v>
       </c>
       <c r="F480" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="481" spans="1:6">
@@ -13340,7 +13498,7 @@
     </row>
     <row r="482" spans="1:6">
       <c r="A482" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
       <c r="B482" t="s">
         <v>7</v>
@@ -13355,7 +13513,7 @@
         <v>553</v>
       </c>
       <c r="F482" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -13380,7 +13538,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B484" t="s">
         <v>7</v>
@@ -13395,7 +13553,7 @@
         <v>553</v>
       </c>
       <c r="F484" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -13420,7 +13578,7 @@
     </row>
     <row r="486" spans="1:6">
       <c r="A486" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="B486" t="s">
         <v>7</v>
@@ -13435,7 +13593,7 @@
         <v>553</v>
       </c>
       <c r="F486" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="487" spans="1:6">
@@ -13460,7 +13618,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="B488" t="s">
         <v>7</v>
@@ -13475,7 +13633,7 @@
         <v>553</v>
       </c>
       <c r="F488" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -13500,7 +13658,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
       <c r="B490" t="s">
         <v>7</v>
@@ -13515,7 +13673,7 @@
         <v>553</v>
       </c>
       <c r="F490" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="491" spans="1:6">
@@ -13540,7 +13698,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="B492" t="s">
         <v>7</v>
@@ -13555,7 +13713,7 @@
         <v>553</v>
       </c>
       <c r="F492" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -13580,7 +13738,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
       <c r="B494" t="s">
         <v>7</v>
@@ -13595,7 +13753,7 @@
         <v>553</v>
       </c>
       <c r="F494" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -13620,7 +13778,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
       <c r="B496" t="s">
         <v>7</v>
@@ -13635,7 +13793,7 @@
         <v>553</v>
       </c>
       <c r="F496" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="497" spans="1:6">
@@ -13660,7 +13818,7 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="B498" t="s">
         <v>7</v>
@@ -13675,7 +13833,7 @@
         <v>553</v>
       </c>
       <c r="F498" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -13700,7 +13858,7 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="B500" t="s">
         <v>7</v>
@@ -13715,7 +13873,7 @@
         <v>553</v>
       </c>
       <c r="F500" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="501" spans="1:6">
@@ -13740,7 +13898,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="B502" t="s">
         <v>7</v>
@@ -13755,7 +13913,7 @@
         <v>553</v>
       </c>
       <c r="F502" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="503" spans="1:6">
@@ -13780,7 +13938,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="B504" t="s">
         <v>7</v>
@@ -13795,7 +13953,7 @@
         <v>553</v>
       </c>
       <c r="F504" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="505" spans="1:6">
@@ -13820,7 +13978,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
       <c r="B506" t="s">
         <v>7</v>
@@ -13835,7 +13993,7 @@
         <v>553</v>
       </c>
       <c r="F506" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="507" spans="1:6">
@@ -13860,7 +14018,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="B508" t="s">
         <v>7</v>
@@ -13875,7 +14033,7 @@
         <v>553</v>
       </c>
       <c r="F508" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -13900,7 +14058,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="B510" t="s">
         <v>7</v>
@@ -13915,7 +14073,7 @@
         <v>553</v>
       </c>
       <c r="F510" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -13940,7 +14098,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="B512" t="s">
         <v>7</v>
@@ -13955,7 +14113,7 @@
         <v>553</v>
       </c>
       <c r="F512" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -13980,7 +14138,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="B514" t="s">
         <v>7</v>
@@ -13995,7 +14153,7 @@
         <v>553</v>
       </c>
       <c r="F514" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="515" spans="1:6">
@@ -14020,7 +14178,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="B516" t="s">
         <v>7</v>
@@ -14035,7 +14193,7 @@
         <v>553</v>
       </c>
       <c r="F516" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="517" spans="1:6">
@@ -14060,7 +14218,7 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="B518" t="s">
         <v>7</v>
@@ -14075,7 +14233,7 @@
         <v>553</v>
       </c>
       <c r="F518" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="519" spans="1:6">
@@ -14100,7 +14258,7 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="B520" t="s">
         <v>7</v>
@@ -14115,7 +14273,7 @@
         <v>553</v>
       </c>
       <c r="F520" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="521" spans="1:6">
@@ -14140,7 +14298,7 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="B522" t="s">
         <v>7</v>
@@ -14155,7 +14313,7 @@
         <v>553</v>
       </c>
       <c r="F522" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="523" spans="1:6">
@@ -14180,7 +14338,7 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="B524" t="s">
         <v>7</v>
@@ -14195,7 +14353,7 @@
         <v>553</v>
       </c>
       <c r="F524" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="525" spans="1:6">
@@ -14220,7 +14378,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
       <c r="B526" t="s">
         <v>7</v>
@@ -14235,7 +14393,7 @@
         <v>553</v>
       </c>
       <c r="F526" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="527" spans="1:6">
@@ -14260,7 +14418,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="B528" t="s">
         <v>7</v>
@@ -14275,7 +14433,7 @@
         <v>553</v>
       </c>
       <c r="F528" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="529" spans="1:6">
@@ -14300,7 +14458,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="B530" t="s">
         <v>7</v>
@@ -14315,7 +14473,7 @@
         <v>553</v>
       </c>
       <c r="F530" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="531" spans="1:6">
@@ -14340,7 +14498,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="B532" t="s">
         <v>7</v>
@@ -14355,7 +14513,7 @@
         <v>553</v>
       </c>
       <c r="F532" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="533" spans="1:6">
@@ -14380,7 +14538,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
       <c r="B534" t="s">
         <v>7</v>
@@ -14395,7 +14553,7 @@
         <v>553</v>
       </c>
       <c r="F534" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="535" spans="1:6">
@@ -14420,7 +14578,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="B536" t="s">
         <v>7</v>
@@ -14435,7 +14593,7 @@
         <v>553</v>
       </c>
       <c r="F536" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="537" spans="1:6">
@@ -14460,7 +14618,7 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="B538" t="s">
         <v>7</v>
@@ -14475,7 +14633,7 @@
         <v>553</v>
       </c>
       <c r="F538" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
     </row>
     <row r="539" spans="1:6">
@@ -14532,7 +14690,7 @@
         <v>25</v>
       </c>
       <c r="E541" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="F541" t="s">
         <v>39</v>
@@ -14540,7 +14698,7 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" t="s">
-        <v>1000</v>
+        <v>991</v>
       </c>
       <c r="B542" t="s">
         <v>7</v>
@@ -14552,15 +14710,15 @@
         <v>35</v>
       </c>
       <c r="E542" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F542" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="543" spans="1:6">
       <c r="A543" t="s">
-        <v>1001</v>
+        <v>992</v>
       </c>
       <c r="B543" t="s">
         <v>7</v>
@@ -14572,15 +14730,15 @@
         <v>35</v>
       </c>
       <c r="E543" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F543" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="544" spans="1:6">
       <c r="A544" t="s">
-        <v>1002</v>
+        <v>993</v>
       </c>
       <c r="B544" t="s">
         <v>7</v>
@@ -14592,15 +14750,15 @@
         <v>35</v>
       </c>
       <c r="E544" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F544" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
     <row r="545" spans="1:6">
       <c r="A545" t="s">
-        <v>1003</v>
+        <v>994</v>
       </c>
       <c r="B545" t="s">
         <v>7</v>
@@ -14612,15 +14770,15 @@
         <v>35</v>
       </c>
       <c r="E545" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="F545" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="C2:C7 C310:C545 C304:C307 C288:C289 C9:C286">
+  <conditionalFormatting sqref="C2:C7 C304:C307 C288:C289 C9:C286 C310:C545">
     <cfRule type="expression" dxfId="6" priority="4">
       <formula>ISNUMBER(SEARCH("不明",C2))</formula>
     </cfRule>
@@ -14663,7 +14821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14" style="9" customWidth="1"/>
@@ -15601,10 +15759,10 @@
         <v>35</v>
       </c>
       <c r="B85" s="11" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>615</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="86" spans="1:3">
@@ -15612,10 +15770,10 @@
         <v>35</v>
       </c>
       <c r="B86" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="C86" s="8" t="s">
         <v>617</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="87" spans="1:3">
@@ -15623,10 +15781,10 @@
         <v>35</v>
       </c>
       <c r="B87" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C87" s="8" t="s">
         <v>619</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="88" spans="1:3">
@@ -15634,10 +15792,10 @@
         <v>35</v>
       </c>
       <c r="B88" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="C88" s="8" t="s">
         <v>621</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="89" spans="1:3">
@@ -15645,10 +15803,10 @@
         <v>35</v>
       </c>
       <c r="B89" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="C89" s="8" t="s">
         <v>623</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="90" spans="1:3">
@@ -15656,10 +15814,10 @@
         <v>35</v>
       </c>
       <c r="B90" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="C90" s="8" t="s">
         <v>625</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -15667,10 +15825,10 @@
         <v>35</v>
       </c>
       <c r="B91" s="8" t="s">
+        <v>626</v>
+      </c>
+      <c r="C91" s="8" t="s">
         <v>627</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -15678,219 +15836,241 @@
         <v>35</v>
       </c>
       <c r="B92" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="C92" s="8" t="s">
         <v>629</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>632</v>
+        <v>1038</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="A94" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>633</v>
+        <v>1039</v>
       </c>
       <c r="C94" s="8" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="95" spans="1:3">
       <c r="A95" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>634</v>
+        <v>1040</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
     </row>
     <row r="96" spans="1:3">
       <c r="A96" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>635</v>
+        <v>1041</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>628</v>
+        <v>623</v>
       </c>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B97" s="8" t="s">
         <v>631</v>
       </c>
-      <c r="B97" s="8" t="s">
-        <v>636</v>
-      </c>
       <c r="C97" s="8" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="C98" s="8" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
     </row>
     <row r="99" spans="1:3">
       <c r="A99" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B100" s="8" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B101" s="8" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>453</v>
+        <v>637</v>
       </c>
     </row>
     <row r="102" spans="1:3">
       <c r="A102" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B102" s="8" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="103" spans="1:3">
       <c r="A103" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B103" s="8" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>647</v>
+        <v>453</v>
       </c>
     </row>
     <row r="104" spans="1:3">
       <c r="A104" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B104" s="8" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B106" s="8" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
     </row>
     <row r="107" spans="1:3">
       <c r="A107" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B107" s="8" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
     </row>
     <row r="108" spans="1:3">
       <c r="A108" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B108" s="8" t="s">
-        <v>571</v>
+        <v>649</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>573</v>
+        <v>651</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
     </row>
     <row r="110" spans="1:3">
       <c r="A110" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
     </row>
     <row r="111" spans="1:3">
       <c r="A111" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B111" s="8" t="s">
+        <v>573</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B113" s="8" t="s">
         <v>575</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>659</v>
+      <c r="C113" s="8" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>

--- a/bpsr_key_table.xlsx
+++ b/bpsr_key_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GitHub\BPSRControllerHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006C86F4-28F0-4129-B0EC-A7B579507C01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{539FB9B3-2F6D-4A8F-95CA-0A384B35BFE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アクション一覧" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="1066">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3597" uniqueCount="1070">
   <si>
     <t>offsets</t>
   </si>
@@ -2632,12 +2632,6 @@
     <t>+0x02305</t>
   </si>
   <si>
-    <t>+0x0230E</t>
-  </si>
-  <si>
-    <t>+0x02323</t>
-  </si>
-  <si>
     <t>+0x02327</t>
   </si>
   <si>
@@ -2647,16 +2641,7 @@
     <t>+0x0237C</t>
   </si>
   <si>
-    <t>撮影モードカメラパン-右</t>
-  </si>
-  <si>
     <t>+0x02396</t>
-  </si>
-  <si>
-    <t>+0x0239F</t>
-  </si>
-  <si>
-    <t>+0x023B4</t>
   </si>
   <si>
     <t>+0x0240D</t>
@@ -3379,6 +3364,340 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
+    <t>+0x0273A</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x0274F</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>撮影モードカーソル呼出し</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x027B8</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>撮影モードカーソル移動-左右</t>
+    <rPh sb="9" eb="11">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>撮影モードカーソル移動-上下</t>
+    <rPh sb="9" eb="11">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>カーソル移動-上下</t>
+    <rPh sb="4" eb="6">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>カーソル移動-左右</t>
+    <rPh sb="4" eb="6">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x027FE</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x02821</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x01F40</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x01F63</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモードキャスト/竿を引く</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード釣り/図鑑</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ズカン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード釣り/研究</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツリ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ケンキュウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード釣り餌切替</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ツリ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>エサ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>キリカエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿切替</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>キリカエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモードモード/ガイド</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード設定</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモードマウス呼出し</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ダ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿移動-前</t>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿移動-後</t>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>アト</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿移動-左</t>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿移動-右</t>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ミギ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿移動-前後</t>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ゼンゴ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモード竿移動-左右</t>
+    <rPh sb="5" eb="6">
+      <t>サオ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>サユウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモードメニューを閉じる</t>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>装備</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>メニューを閉じる</t>
+    <rPh sb="5" eb="6">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x018B1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x018CB</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x00AC1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>+0x019C0</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撮影モードカメラ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>上下</t>
+    </r>
+    <rPh sb="10" eb="11">
+      <t>シタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撮影モードカメラ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>左右</t>
+    </r>
+    <rPh sb="9" eb="11">
+      <t>サユウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -3403,10 +3722,21 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>上下</t>
+      <t>右</t>
     </r>
-    <rPh sb="12" eb="13">
-      <t>シタ</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>撮影モードカメラパン-上下</t>
+    <rPh sb="11" eb="13">
+      <t>ジョウカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>撮影モードカメラパン-左右</t>
+    <rPh sb="11" eb="13">
+      <t>サユウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -3418,7 +3748,39 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>撮影モードカメラパン</t>
+      <t>撮影モードカメラ移動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>上下</t>
+    </r>
+    <rPh sb="11" eb="13">
+      <t>ジョウカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>撮影モードカメラ移動</t>
     </r>
     <r>
       <rPr>
@@ -3443,273 +3805,19 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>+0x0273A</t>
+    <t>+0x0230E</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>+0x0274F</t>
+    <t>+0x02323</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>撮影モードカーソル呼出し</t>
+    <t>+0x0239F</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>+0x027B8</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>撮影モードカーソル移動-左右</t>
-    <rPh sb="9" eb="11">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>撮影モードカーソル移動-上下</t>
-    <rPh sb="9" eb="11">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>カーソル移動-上下</t>
-    <rPh sb="4" eb="6">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>カーソル移動-左右</t>
-    <rPh sb="4" eb="6">
-      <t>イドウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x027FE</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x02821</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x01F40</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x01F63</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモードキャスト/竿を引く</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>ヒ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード釣り/図鑑</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ツリ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ズカン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード釣り/研究</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ツリ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ケンキュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード釣り餌切替</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ツリ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>エサ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>キリカエ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿切替</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キリカエ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモードモード/ガイド</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード設定</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモードマウス呼出し</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ヨ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ダ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿移動-前</t>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>マエ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿移動-後</t>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>アト</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿移動-左</t>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ヒダリ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿移動-右</t>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ミギ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿移動-前後</t>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ゼンゴ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモード竿移動-左右</t>
-    <rPh sb="5" eb="6">
-      <t>サオ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>イドウ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>サユウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモードメニューを閉じる</t>
-    <rPh sb="10" eb="11">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>装備</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>メニューを閉じる</t>
-    <rPh sb="5" eb="6">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x018B1</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x018CB</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x00AC1</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>+0x019C0</t>
+    <t>+0x023B4</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -4255,7 +4363,7 @@
     </row>
     <row r="8" spans="1:6" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>24</v>
@@ -4267,10 +4375,10 @@
         <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="14.25" customHeight="1">
@@ -4287,10 +4395,10 @@
         <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4381,7 +4489,7 @@
         <v>7</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>9</v>
@@ -4550,7 +4658,7 @@
         <v>663</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5153,7 +5261,7 @@
     </row>
     <row r="53" spans="1:6" ht="14.25" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>24</v>
@@ -5165,15 +5273,15 @@
         <v>25</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="14.25" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>24</v>
@@ -5185,10 +5293,10 @@
         <v>25</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -5659,7 +5767,7 @@
         <v>7</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>9</v>
@@ -6093,7 +6201,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" s="2" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>7</v>
@@ -6259,7 +6367,7 @@
         <v>7</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>9</v>
@@ -7017,7 +7125,7 @@
         <v>7</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>9</v>
@@ -7097,7 +7205,7 @@
         <v>7</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>9</v>
@@ -7377,7 +7485,7 @@
         <v>7</v>
       </c>
       <c r="C164" s="13" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>9</v>
@@ -7417,7 +7525,7 @@
         <v>7</v>
       </c>
       <c r="C166" s="13" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>9</v>
@@ -7457,7 +7565,7 @@
         <v>7</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>9</v>
@@ -7497,7 +7605,7 @@
         <v>7</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>9</v>
@@ -8457,7 +8565,7 @@
         <v>7</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>9</v>
@@ -8477,7 +8585,7 @@
         <v>24</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>25</v>
@@ -8591,7 +8699,7 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="2" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>7</v>
@@ -8611,7 +8719,7 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="2" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>24</v>
@@ -8791,7 +8899,7 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="2" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>7</v>
@@ -9743,7 +9851,7 @@
         <v>25</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F282" s="2" t="s">
         <v>859</v>
@@ -9771,19 +9879,19 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="2" t="s">
-        <v>1043</v>
+        <v>1036</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="D284" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F284" s="2" t="s">
         <v>275</v>
@@ -9811,19 +9919,19 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="2" t="s">
-        <v>1044</v>
+        <v>1037</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>1040</v>
+        <v>1033</v>
       </c>
       <c r="D286" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F286" s="2" t="s">
         <v>862</v>
@@ -9897,7 +10005,7 @@
         <v>7</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D290" s="2" t="s">
         <v>9</v>
@@ -9917,7 +10025,7 @@
         <v>24</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>25</v>
@@ -9937,7 +10045,7 @@
         <v>7</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="D292" s="2" t="s">
         <v>9</v>
@@ -9957,7 +10065,7 @@
         <v>24</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>25</v>
@@ -9977,7 +10085,7 @@
         <v>7</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>9</v>
@@ -9997,7 +10105,7 @@
         <v>7</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>9</v>
@@ -10017,7 +10125,7 @@
         <v>24</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>25</v>
@@ -10037,7 +10145,7 @@
         <v>24</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="D297" s="2" t="s">
         <v>25</v>
@@ -10057,7 +10165,7 @@
         <v>7</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>9</v>
@@ -10077,7 +10185,7 @@
         <v>24</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>25</v>
@@ -10097,7 +10205,7 @@
         <v>7</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -10117,7 +10225,7 @@
         <v>24</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>25</v>
@@ -10137,7 +10245,7 @@
         <v>7</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -10157,7 +10265,7 @@
         <v>24</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>25</v>
@@ -10257,7 +10365,7 @@
         <v>7</v>
       </c>
       <c r="C308" s="12" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -10277,7 +10385,7 @@
         <v>24</v>
       </c>
       <c r="C309" s="12" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>25</v>
@@ -10337,7 +10445,7 @@
         <v>7</v>
       </c>
       <c r="C312" s="13" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>9</v>
@@ -10357,7 +10465,7 @@
         <v>7</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>9</v>
@@ -10377,7 +10485,7 @@
         <v>7</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>9</v>
@@ -10451,47 +10559,47 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" s="2" t="s">
-        <v>868</v>
+        <v>1066</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C318" s="2" t="s">
-        <v>28</v>
+      <c r="C318" s="13" t="s">
+        <v>1064</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F318" s="13" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="319" spans="1:6">
       <c r="A319" s="2" t="s">
-        <v>869</v>
+        <v>1067</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C319" s="2" t="s">
-        <v>28</v>
+      <c r="C319" s="13" t="s">
+        <v>1065</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E319" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="F319" s="2" t="s">
         <v>993</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" s="2" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>7</v>
@@ -10517,7 +10625,7 @@
         <v>7</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>9</v>
@@ -10537,7 +10645,7 @@
         <v>7</v>
       </c>
       <c r="C322" s="13" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="D322" s="2" t="s">
         <v>9</v>
@@ -10557,7 +10665,7 @@
         <v>7</v>
       </c>
       <c r="C323" s="13" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>9</v>
@@ -10571,7 +10679,7 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" s="2" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>7</v>
@@ -10596,8 +10704,8 @@
       <c r="B325" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C325" s="2" t="s">
-        <v>873</v>
+      <c r="C325" s="13" t="s">
+        <v>1061</v>
       </c>
       <c r="D325" s="2" t="s">
         <v>9</v>
@@ -10611,7 +10719,7 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>7</v>
@@ -10631,42 +10739,42 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" s="2" t="s">
-        <v>875</v>
+        <v>1068</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C327" s="2" t="s">
-        <v>28</v>
+      <c r="C327" s="3" t="s">
+        <v>1062</v>
       </c>
       <c r="D327" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="328" spans="1:6">
       <c r="A328" s="2" t="s">
-        <v>876</v>
+        <v>1069</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C328" s="2" t="s">
-        <v>28</v>
+      <c r="C328" s="3" t="s">
+        <v>1063</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -10677,7 +10785,7 @@
         <v>7</v>
       </c>
       <c r="C329" s="13" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="D329" s="2" t="s">
         <v>9</v>
@@ -10697,7 +10805,7 @@
         <v>7</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>9</v>
@@ -10717,7 +10825,7 @@
         <v>7</v>
       </c>
       <c r="C331" s="13" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="D331" s="2" t="s">
         <v>9</v>
@@ -10731,7 +10839,7 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="2" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>7</v>
@@ -10757,7 +10865,7 @@
         <v>7</v>
       </c>
       <c r="C333" s="13" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -10771,7 +10879,7 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="2" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>7</v>
@@ -10791,47 +10899,47 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="2" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="2" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="2" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>7</v>
@@ -10857,7 +10965,7 @@
         <v>7</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>9</v>
@@ -10877,7 +10985,7 @@
         <v>24</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="D339" s="2" t="s">
         <v>25</v>
@@ -10897,7 +11005,7 @@
         <v>7</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>9</v>
@@ -10917,7 +11025,7 @@
         <v>24</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>25</v>
@@ -10937,7 +11045,7 @@
         <v>7</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -10957,7 +11065,7 @@
         <v>24</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>25</v>
@@ -10977,7 +11085,7 @@
         <v>7</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>9</v>
@@ -10997,7 +11105,7 @@
         <v>24</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>25</v>
@@ -11017,7 +11125,7 @@
         <v>7</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>9</v>
@@ -11037,7 +11145,7 @@
         <v>24</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>25</v>
@@ -11057,7 +11165,7 @@
         <v>7</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>9</v>
@@ -11077,7 +11185,7 @@
         <v>24</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>25</v>
@@ -11091,7 +11199,7 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="2" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="B350" s="2" t="s">
         <v>7</v>
@@ -11117,7 +11225,7 @@
         <v>7</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>9</v>
@@ -11131,7 +11239,7 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="2" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B352" s="2" t="s">
         <v>7</v>
@@ -11171,7 +11279,7 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="2" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="B354" s="2" t="s">
         <v>7</v>
@@ -11217,7 +11325,7 @@
         <v>7</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D356" s="2" t="s">
         <v>9</v>
@@ -11237,7 +11345,7 @@
         <v>24</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="D357" s="2" t="s">
         <v>25</v>
@@ -11257,7 +11365,7 @@
         <v>7</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>9</v>
@@ -11277,7 +11385,7 @@
         <v>24</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="D359" s="2" t="s">
         <v>25</v>
@@ -11291,7 +11399,7 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="2" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>7</v>
@@ -11306,12 +11414,12 @@
         <v>610</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="2" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>7</v>
@@ -11337,7 +11445,7 @@
         <v>7</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="D362" s="2" t="s">
         <v>9</v>
@@ -11351,7 +11459,7 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="2" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>7</v>
@@ -11371,7 +11479,7 @@
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="2" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>7</v>
@@ -11391,47 +11499,47 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="2" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C365" s="13" t="s">
-        <v>1031</v>
+        <v>1059</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="2" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C366" s="13" t="s">
-        <v>1032</v>
+        <v>1060</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E366" s="2" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="2" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>7</v>
@@ -11471,7 +11579,7 @@
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="2" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>7</v>
@@ -11511,7 +11619,7 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="2" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>7</v>
@@ -11531,13 +11639,13 @@
     </row>
     <row r="372" spans="1:6">
       <c r="A372" s="2" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="D372" s="2" t="s">
         <v>25</v>
@@ -11551,7 +11659,7 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="2" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>7</v>
@@ -11571,7 +11679,7 @@
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="2" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>24</v>
@@ -11583,7 +11691,7 @@
         <v>25</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="F374" s="2" t="s">
         <v>859</v>
@@ -11591,7 +11699,7 @@
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="2" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>7</v>
@@ -11611,19 +11719,19 @@
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="2" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C376" s="14" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="D376" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E376" s="2" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F376" s="2" t="s">
         <v>275</v>
@@ -11631,7 +11739,7 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="2" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>7</v>
@@ -11651,19 +11759,19 @@
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="2" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>24</v>
       </c>
       <c r="C378" s="14" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F378" s="2" t="s">
         <v>862</v>
@@ -11671,7 +11779,7 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="2" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>7</v>
@@ -11717,7 +11825,7 @@
         <v>7</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="D381" s="2" t="s">
         <v>35</v>
@@ -11737,7 +11845,7 @@
         <v>24</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="D382" s="2" t="s">
         <v>25</v>
@@ -11757,7 +11865,7 @@
         <v>24</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="D383" s="2" t="s">
         <v>25</v>
@@ -11851,7 +11959,7 @@
     </row>
     <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="B388" t="s">
         <v>7</v>
@@ -11891,13 +11999,13 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="B390" t="s">
         <v>7</v>
       </c>
       <c r="C390" s="15" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="D390" t="s">
         <v>35</v>
@@ -11917,7 +12025,7 @@
         <v>24</v>
       </c>
       <c r="C391" s="15" t="s">
-        <v>1045</v>
+        <v>1038</v>
       </c>
       <c r="D391" t="s">
         <v>25</v>
@@ -11937,7 +12045,7 @@
         <v>7</v>
       </c>
       <c r="C392" s="15" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="D392" t="s">
         <v>9</v>
@@ -11957,7 +12065,7 @@
         <v>24</v>
       </c>
       <c r="C393" s="15" t="s">
-        <v>1046</v>
+        <v>1039</v>
       </c>
       <c r="D393" t="s">
         <v>25</v>
@@ -11977,7 +12085,7 @@
         <v>7</v>
       </c>
       <c r="C394" s="15" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="D394" t="s">
         <v>9</v>
@@ -11997,7 +12105,7 @@
         <v>24</v>
       </c>
       <c r="C395" s="15" t="s">
-        <v>1047</v>
+        <v>1040</v>
       </c>
       <c r="D395" t="s">
         <v>25</v>
@@ -12017,7 +12125,7 @@
         <v>7</v>
       </c>
       <c r="C396" s="15" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="D396" t="s">
         <v>9</v>
@@ -12037,7 +12145,7 @@
         <v>24</v>
       </c>
       <c r="C397" s="15" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="D397" t="s">
         <v>25</v>
@@ -12057,7 +12165,7 @@
         <v>7</v>
       </c>
       <c r="C398" s="15" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="D398" t="s">
         <v>9</v>
@@ -12077,7 +12185,7 @@
         <v>24</v>
       </c>
       <c r="C399" s="15" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="D399" t="s">
         <v>25</v>
@@ -12097,7 +12205,7 @@
         <v>7</v>
       </c>
       <c r="C400" s="15" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="D400" t="s">
         <v>9</v>
@@ -12117,7 +12225,7 @@
         <v>24</v>
       </c>
       <c r="C401" s="15" t="s">
-        <v>1050</v>
+        <v>1043</v>
       </c>
       <c r="D401" t="s">
         <v>25</v>
@@ -12137,7 +12245,7 @@
         <v>7</v>
       </c>
       <c r="C402" s="15" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="D402" t="s">
         <v>9</v>
@@ -12151,13 +12259,13 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="B403" t="s">
         <v>24</v>
       </c>
       <c r="C403" s="15" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="D403" t="s">
         <v>25</v>
@@ -12166,12 +12274,12 @@
         <v>632</v>
       </c>
       <c r="F403" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
     </row>
     <row r="404" spans="1:6">
       <c r="A404" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B404" t="s">
         <v>7</v>
@@ -12197,7 +12305,7 @@
         <v>7</v>
       </c>
       <c r="C405" s="15" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="D405" t="s">
         <v>9</v>
@@ -12217,7 +12325,7 @@
         <v>7</v>
       </c>
       <c r="C406" s="16" t="s">
-        <v>1053</v>
+        <v>1046</v>
       </c>
       <c r="D406" t="s">
         <v>9</v>
@@ -12237,7 +12345,7 @@
         <v>7</v>
       </c>
       <c r="C407" s="16" t="s">
-        <v>1054</v>
+        <v>1047</v>
       </c>
       <c r="D407" t="s">
         <v>9</v>
@@ -12257,7 +12365,7 @@
         <v>7</v>
       </c>
       <c r="C408" s="16" t="s">
-        <v>1055</v>
+        <v>1048</v>
       </c>
       <c r="D408" t="s">
         <v>9</v>
@@ -12271,7 +12379,7 @@
     </row>
     <row r="409" spans="1:6">
       <c r="A409" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B409" t="s">
         <v>7</v>
@@ -12297,7 +12405,7 @@
         <v>7</v>
       </c>
       <c r="C410" s="16" t="s">
-        <v>1056</v>
+        <v>1049</v>
       </c>
       <c r="D410" t="s">
         <v>9</v>
@@ -12311,7 +12419,7 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="B411" t="s">
         <v>7</v>
@@ -12331,42 +12439,42 @@
     </row>
     <row r="412" spans="1:6">
       <c r="A412" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B412" t="s">
         <v>24</v>
       </c>
       <c r="C412" s="16" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="D412" t="s">
         <v>25</v>
       </c>
       <c r="E412" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F412" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="B413" t="s">
         <v>24</v>
       </c>
       <c r="C413" s="16" t="s">
-        <v>1058</v>
+        <v>1051</v>
       </c>
       <c r="D413" t="s">
         <v>25</v>
       </c>
       <c r="E413" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F413" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -12417,7 +12525,7 @@
         <v>7</v>
       </c>
       <c r="C416" s="16" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="D416" t="s">
         <v>9</v>
@@ -12437,7 +12545,7 @@
         <v>24</v>
       </c>
       <c r="C417" s="16" t="s">
-        <v>1059</v>
+        <v>1052</v>
       </c>
       <c r="D417" t="s">
         <v>25</v>
@@ -12451,7 +12559,7 @@
     </row>
     <row r="418" spans="1:6">
       <c r="A418" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="B418" t="s">
         <v>7</v>
@@ -12491,7 +12599,7 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B420" t="s">
         <v>7</v>
@@ -12531,7 +12639,7 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B422" t="s">
         <v>7</v>
@@ -12571,7 +12679,7 @@
     </row>
     <row r="424" spans="1:6">
       <c r="A424" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="B424" t="s">
         <v>7</v>
@@ -12611,7 +12719,7 @@
     </row>
     <row r="426" spans="1:6">
       <c r="A426" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="B426" t="s">
         <v>7</v>
@@ -12651,7 +12759,7 @@
     </row>
     <row r="428" spans="1:6">
       <c r="A428" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="B428" t="s">
         <v>7</v>
@@ -12691,7 +12799,7 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B430" t="s">
         <v>7</v>
@@ -12731,7 +12839,7 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="B432" t="s">
         <v>7</v>
@@ -12771,7 +12879,7 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="B434" t="s">
         <v>7</v>
@@ -12811,7 +12919,7 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B436" t="s">
         <v>7</v>
@@ -12851,7 +12959,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="B438" t="s">
         <v>7</v>
@@ -12891,7 +12999,7 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="B440" t="s">
         <v>7</v>
@@ -12931,7 +13039,7 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B442" t="s">
         <v>7</v>
@@ -12971,7 +13079,7 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="B444" t="s">
         <v>7</v>
@@ -13011,7 +13119,7 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="B446" t="s">
         <v>7</v>
@@ -13051,7 +13159,7 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="B448" t="s">
         <v>7</v>
@@ -13091,7 +13199,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="B450" t="s">
         <v>7</v>
@@ -13131,7 +13239,7 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="B452" t="s">
         <v>7</v>
@@ -13171,7 +13279,7 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B454" t="s">
         <v>7</v>
@@ -13211,7 +13319,7 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="B456" t="s">
         <v>7</v>
@@ -13251,7 +13359,7 @@
     </row>
     <row r="458" spans="1:6">
       <c r="A458" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="B458" t="s">
         <v>7</v>
@@ -13291,7 +13399,7 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B460" t="s">
         <v>7</v>
@@ -13331,7 +13439,7 @@
     </row>
     <row r="462" spans="1:6">
       <c r="A462" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="B462" t="s">
         <v>7</v>
@@ -13371,7 +13479,7 @@
     </row>
     <row r="464" spans="1:6">
       <c r="A464" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="B464" t="s">
         <v>7</v>
@@ -13411,7 +13519,7 @@
     </row>
     <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B466" t="s">
         <v>7</v>
@@ -13451,7 +13559,7 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="B468" t="s">
         <v>7</v>
@@ -13491,7 +13599,7 @@
     </row>
     <row r="470" spans="1:6">
       <c r="A470" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="B470" t="s">
         <v>7</v>
@@ -13531,7 +13639,7 @@
     </row>
     <row r="472" spans="1:6">
       <c r="A472" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="B472" t="s">
         <v>7</v>
@@ -13571,7 +13679,7 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B474" t="s">
         <v>7</v>
@@ -13611,7 +13719,7 @@
     </row>
     <row r="476" spans="1:6">
       <c r="A476" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="B476" t="s">
         <v>7</v>
@@ -13651,7 +13759,7 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="B478" t="s">
         <v>7</v>
@@ -13691,7 +13799,7 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B480" t="s">
         <v>7</v>
@@ -13731,7 +13839,7 @@
     </row>
     <row r="482" spans="1:6">
       <c r="A482" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="B482" t="s">
         <v>7</v>
@@ -13771,7 +13879,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="B484" t="s">
         <v>7</v>
@@ -13811,7 +13919,7 @@
     </row>
     <row r="486" spans="1:6">
       <c r="A486" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="B486" t="s">
         <v>7</v>
@@ -13851,7 +13959,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="B488" t="s">
         <v>7</v>
@@ -13891,7 +13999,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="B490" t="s">
         <v>7</v>
@@ -13931,7 +14039,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B492" t="s">
         <v>7</v>
@@ -13971,7 +14079,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="B494" t="s">
         <v>7</v>
@@ -14011,7 +14119,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B496" t="s">
         <v>7</v>
@@ -14051,7 +14159,7 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="B498" t="s">
         <v>7</v>
@@ -14091,7 +14199,7 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="B500" t="s">
         <v>7</v>
@@ -14131,7 +14239,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B502" t="s">
         <v>7</v>
@@ -14171,7 +14279,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="B504" t="s">
         <v>7</v>
@@ -14211,7 +14319,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="B506" t="s">
         <v>7</v>
@@ -14251,7 +14359,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B508" t="s">
         <v>7</v>
@@ -14291,7 +14399,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="B510" t="s">
         <v>7</v>
@@ -14331,7 +14439,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="B512" t="s">
         <v>7</v>
@@ -14371,7 +14479,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B514" t="s">
         <v>7</v>
@@ -14411,7 +14519,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="B516" t="s">
         <v>7</v>
@@ -14451,7 +14559,7 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="B518" t="s">
         <v>7</v>
@@ -14491,7 +14599,7 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="B520" t="s">
         <v>7</v>
@@ -14531,7 +14639,7 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="B522" t="s">
         <v>7</v>
@@ -14571,7 +14679,7 @@
     </row>
     <row r="524" spans="1:6">
       <c r="A524" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="B524" t="s">
         <v>7</v>
@@ -14611,7 +14719,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B526" t="s">
         <v>7</v>
@@ -14651,7 +14759,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="B528" t="s">
         <v>7</v>
@@ -14691,7 +14799,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="B530" t="s">
         <v>7</v>
@@ -14731,7 +14839,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="B532" t="s">
         <v>7</v>
@@ -14771,7 +14879,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="B534" t="s">
         <v>7</v>
@@ -14811,7 +14919,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="B536" t="s">
         <v>7</v>
@@ -14851,7 +14959,7 @@
     </row>
     <row r="538" spans="1:6">
       <c r="A538" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="B538" t="s">
         <v>7</v>
@@ -14931,7 +15039,7 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="B542" t="s">
         <v>7</v>
@@ -14951,7 +15059,7 @@
     </row>
     <row r="543" spans="1:6">
       <c r="A543" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="B543" t="s">
         <v>7</v>
@@ -14971,7 +15079,7 @@
     </row>
     <row r="544" spans="1:6">
       <c r="A544" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="B544" t="s">
         <v>7</v>
@@ -14991,7 +15099,7 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="B545" t="s">
         <v>7</v>
@@ -15011,7 +15119,7 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
-  <conditionalFormatting sqref="C2:C7 C304:C307 C310:C408 C9:C289 C410:C545">
+  <conditionalFormatting sqref="C2:C7 C304:C307 C9:C289 C410:C545 C310:C408">
     <cfRule type="expression" dxfId="6" priority="5">
       <formula>ISNUMBER(SEARCH("不明",C2))</formula>
     </cfRule>
@@ -15992,7 +16100,7 @@
         <v>35</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="C85" s="8" t="s">
         <v>609</v>
@@ -16080,7 +16188,7 @@
         <v>624</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="C93" s="8" t="s">
         <v>611</v>
@@ -16091,7 +16199,7 @@
         <v>624</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="C94" s="8" t="s">
         <v>613</v>
@@ -16102,7 +16210,7 @@
         <v>624</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="C95" s="8" t="s">
         <v>615</v>
@@ -16113,7 +16221,7 @@
         <v>624</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="C96" s="8" t="s">
         <v>617</v>

--- a/bpsr_key_table.xlsx
+++ b/bpsr_key_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GitHub\BPSRControllerHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D988D7E5-8186-4C3D-B142-F459E1A4C958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B489F0-E900-43F1-BEF9-FF814CF0BDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="アクション一覧" sheetId="1" r:id="rId1"/>
@@ -1833,9 +1833,6 @@
     <t>+0x0108D</t>
   </si>
   <si>
-    <t>チャットログチャンネル切り替え-上</t>
-  </si>
-  <si>
     <t>type=0x00000001, value=0x00000111</t>
   </si>
   <si>
@@ -1845,9 +1842,6 @@
     <t>+0x010B0</t>
   </si>
   <si>
-    <t>チャットログチャンネル切り替え-下</t>
-  </si>
-  <si>
     <t>type=0x00000001, value=0x00000112</t>
   </si>
   <si>
@@ -1857,9 +1851,6 @@
     <t>+0x010D3</t>
   </si>
   <si>
-    <t>チャット入力チャンネル切り替え-左</t>
-  </si>
-  <si>
     <t>type=0x00000001, value=0x00000114</t>
   </si>
   <si>
@@ -1867,9 +1858,6 @@
   </si>
   <si>
     <t>+0x010F6</t>
-  </si>
-  <si>
-    <t>チャット入力チャンネル切り替え-右</t>
   </si>
   <si>
     <t>type=0x00000001, value=0x00000113</t>
@@ -4380,179 +4368,191 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>釣りモードチャットログチャンネル切り替え-上</t>
-    <rPh sb="16" eb="17">
+    <t>Enter</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>釣りモードトーク</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>クイックホイール切替</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>クイックホイール</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>C2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>C#2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>D2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>D#2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>E2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>G2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>F2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>F#2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>G#2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>A2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>A#2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>B2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>C#3</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D#3</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>F#3</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>G#3</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A#3</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>C#4</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D#4</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>F#4</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>G#4</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A#4</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>BandTimbre1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BandPedal</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SwitchRange1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>SwitchRange2</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>QuickRange1</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>トークログチャンネル切り替え-上</t>
+  </si>
+  <si>
+    <t>トークログチャンネル切り替え-下</t>
+  </si>
+  <si>
+    <t>トーク入力チャンネル切り替え-左</t>
+  </si>
+  <si>
+    <t>トーク入力チャンネル切り替え-右</t>
+  </si>
+  <si>
+    <t>釣りモードトークログチャンネル切り替え-下</t>
+    <rPh sb="15" eb="16">
       <t>キ</t>
     </rPh>
-    <rPh sb="18" eb="19">
+    <rPh sb="17" eb="18">
       <t>カ</t>
     </rPh>
-    <rPh sb="21" eb="22">
-      <t>ウエ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモードチャットログチャンネル切り替え-下</t>
-    <rPh sb="16" eb="17">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
+    <rPh sb="20" eb="21">
       <t>シタ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>Enter</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>釣りモードトーク</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>クイックホイール切替</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>クイックホイール</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>C2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>C#2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>D2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>D#2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>E2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>G2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>F2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>F#2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>G#2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>A2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>A#2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>B2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>C#3</t>
-  </si>
-  <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D#3</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>F#3</t>
-  </si>
-  <si>
-    <t>G3</t>
-  </si>
-  <si>
-    <t>G#3</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A#3</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>C#4</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t>D#4</t>
-  </si>
-  <si>
-    <t>E4</t>
-  </si>
-  <si>
-    <t>F#4</t>
-  </si>
-  <si>
-    <t>G4</t>
-  </si>
-  <si>
-    <t>G#4</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A#4</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>BandTimbre1</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>BandPedal</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>SwitchRange1</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>SwitchRange2</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>QuickRange1</t>
+    <t>釣りモードトークログチャンネル切り替え-上</t>
+    <rPh sb="15" eb="16">
+      <t>キ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ウエ</t>
+    </rPh>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -4734,13 +4734,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFDDEBF7"/>
         </patternFill>
       </fill>
@@ -4756,6 +4749,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7429,7 +7429,7 @@
         <v>228</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>1437</v>
+        <v>1431</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>3</v>
@@ -8249,7 +8249,7 @@
         <v>228</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>586</v>
+        <v>1471</v>
       </c>
       <c r="D166" s="9" t="s">
         <v>3</v>
@@ -8258,12 +8258,12 @@
         <v>126</v>
       </c>
       <c r="F166" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="167" spans="1:6">
       <c r="A167" s="9" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>228</v>
@@ -8283,13 +8283,13 @@
     </row>
     <row r="168" spans="1:6" ht="28.5">
       <c r="A168" s="9" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C168" s="9" t="s">
-        <v>590</v>
+        <v>1472</v>
       </c>
       <c r="D168" s="9" t="s">
         <v>3</v>
@@ -8298,12 +8298,12 @@
         <v>128</v>
       </c>
       <c r="F168" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="169" spans="1:6">
       <c r="A169" s="9" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>228</v>
@@ -8323,13 +8323,13 @@
     </row>
     <row r="170" spans="1:6" ht="28.5">
       <c r="A170" s="9" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>594</v>
+        <v>1473</v>
       </c>
       <c r="D170" s="9" t="s">
         <v>3</v>
@@ -8338,12 +8338,12 @@
         <v>132</v>
       </c>
       <c r="F170" s="9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="171" spans="1:6">
       <c r="A171" s="9" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>228</v>
@@ -8363,13 +8363,13 @@
     </row>
     <row r="172" spans="1:6" ht="28.5">
       <c r="A172" s="9" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>598</v>
+        <v>1474</v>
       </c>
       <c r="D172" s="9" t="s">
         <v>3</v>
@@ -8378,18 +8378,18 @@
         <v>130</v>
       </c>
       <c r="F172" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="173" spans="1:6">
       <c r="A173" s="9" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D173" s="9" t="s">
         <v>3</v>
@@ -8403,13 +8403,13 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" s="9" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B174" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C174" s="9" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D174" s="9" t="s">
         <v>16</v>
@@ -8423,13 +8423,13 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" s="9" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D175" s="9" t="s">
         <v>3</v>
@@ -8443,13 +8443,13 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" s="9" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B176" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C176" s="9" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="D176" s="9" t="s">
         <v>16</v>
@@ -8463,13 +8463,13 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" s="9" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B177" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>3</v>
@@ -8483,13 +8483,13 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" s="9" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B178" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="D178" s="9" t="s">
         <v>16</v>
@@ -8503,13 +8503,13 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" s="9" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C179" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>3</v>
@@ -8523,13 +8523,13 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" s="9" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B180" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C180" s="9" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="D180" s="9" t="s">
         <v>16</v>
@@ -8543,13 +8543,13 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" s="9" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B181" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D181" s="9" t="s">
         <v>3</v>
@@ -8563,13 +8563,13 @@
     </row>
     <row r="182" spans="1:6" ht="28.5">
       <c r="A182" s="9" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B182" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C182" s="9" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="D182" s="9" t="s">
         <v>16</v>
@@ -8578,18 +8578,18 @@
         <v>192</v>
       </c>
       <c r="F182" s="9" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
     </row>
     <row r="183" spans="1:6">
       <c r="A183" s="9" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B183" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C183" s="9" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D183" s="9" t="s">
         <v>16</v>
@@ -8603,13 +8603,13 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" s="9" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C184" s="9" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="D184" s="9" t="s">
         <v>3</v>
@@ -8623,7 +8623,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" s="9" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>228</v>
@@ -8643,13 +8643,13 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" s="9" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C186" s="9" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="D186" s="9" t="s">
         <v>3</v>
@@ -8663,7 +8663,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" s="9" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B187" s="11" t="s">
         <v>228</v>
@@ -8683,7 +8683,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" s="9" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>228</v>
@@ -8703,7 +8703,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" s="9" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>228</v>
@@ -8723,7 +8723,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" s="9" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>228</v>
@@ -8743,7 +8743,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" s="9" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B191" s="11" t="s">
         <v>228</v>
@@ -8763,7 +8763,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" s="9" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B192" s="11" t="s">
         <v>228</v>
@@ -8783,7 +8783,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" s="9" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>228</v>
@@ -8803,7 +8803,7 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" s="9" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>228</v>
@@ -8823,7 +8823,7 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" s="9" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B195" s="11" t="s">
         <v>228</v>
@@ -8843,7 +8843,7 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" s="9" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>228</v>
@@ -8863,7 +8863,7 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" s="9" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>228</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" s="9" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>228</v>
@@ -8903,7 +8903,7 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" s="9" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B199" s="11" t="s">
         <v>228</v>
@@ -8923,7 +8923,7 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" s="9" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>228</v>
@@ -8943,7 +8943,7 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" s="9" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>228</v>
@@ -8963,7 +8963,7 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" s="9" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>228</v>
@@ -8983,7 +8983,7 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" s="9" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B203" s="11" t="s">
         <v>228</v>
@@ -9003,7 +9003,7 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" s="9" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>228</v>
@@ -9023,7 +9023,7 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" s="9" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>228</v>
@@ -9043,7 +9043,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" s="9" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>228</v>
@@ -9063,7 +9063,7 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" s="9" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B207" s="10" t="s">
         <v>246</v>
@@ -9083,7 +9083,7 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" s="9" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>228</v>
@@ -9103,7 +9103,7 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" s="9" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>228</v>
@@ -9123,7 +9123,7 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" s="9" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>228</v>
@@ -9143,7 +9143,7 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" s="9" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>228</v>
@@ -9163,7 +9163,7 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" s="9" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>228</v>
@@ -9183,7 +9183,7 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" s="9" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B213" s="11" t="s">
         <v>228</v>
@@ -9203,7 +9203,7 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" s="9" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>228</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" s="9" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>228</v>
@@ -9243,7 +9243,7 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" s="9" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>228</v>
@@ -9263,7 +9263,7 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" s="9" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B217" s="11" t="s">
         <v>228</v>
@@ -9283,7 +9283,7 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" s="9" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>228</v>
@@ -9303,7 +9303,7 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" s="9" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>228</v>
@@ -9323,13 +9323,13 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" s="9" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C220" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D220" s="9" t="s">
         <v>3</v>
@@ -9343,13 +9343,13 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" s="9" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B221" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C221" s="9" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D221" s="9" t="s">
         <v>16</v>
@@ -9363,7 +9363,7 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" s="9" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>228</v>
@@ -9383,7 +9383,7 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" s="9" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>228</v>
@@ -9403,7 +9403,7 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" s="9" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B224" s="10" t="s">
         <v>246</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" s="9" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>228</v>
@@ -9443,7 +9443,7 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" s="9" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B226" s="10" t="s">
         <v>246</v>
@@ -9463,7 +9463,7 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" s="9" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B227" s="11" t="s">
         <v>228</v>
@@ -9483,7 +9483,7 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" s="9" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B228" s="10" t="s">
         <v>246</v>
@@ -9503,7 +9503,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" s="9" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B229" s="11" t="s">
         <v>228</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" s="9" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>228</v>
@@ -9543,7 +9543,7 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" s="9" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B231" s="11" t="s">
         <v>228</v>
@@ -9563,7 +9563,7 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" s="9" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>228</v>
@@ -9583,7 +9583,7 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" s="9" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B233" s="11" t="s">
         <v>228</v>
@@ -9603,7 +9603,7 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" s="9" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B234" s="11" t="s">
         <v>228</v>
@@ -9623,7 +9623,7 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" s="9" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B235" s="11" t="s">
         <v>228</v>
@@ -9643,7 +9643,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" s="9" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>228</v>
@@ -9663,7 +9663,7 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" s="9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B237" s="11" t="s">
         <v>228</v>
@@ -9683,7 +9683,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="9" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B238" s="11" t="s">
         <v>228</v>
@@ -9703,7 +9703,7 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" s="9" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B239" s="11" t="s">
         <v>228</v>
@@ -9723,7 +9723,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" s="9" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B240" s="11" t="s">
         <v>228</v>
@@ -9743,7 +9743,7 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" s="9" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B241" s="11" t="s">
         <v>228</v>
@@ -9763,7 +9763,7 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" s="9" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B242" s="11" t="s">
         <v>228</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" s="9" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B243" s="11" t="s">
         <v>228</v>
@@ -9803,7 +9803,7 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" s="9" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B244" s="10" t="s">
         <v>246</v>
@@ -9818,12 +9818,12 @@
         <v>132</v>
       </c>
       <c r="F244" s="9" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
     </row>
     <row r="245" spans="1:6">
       <c r="A245" s="9" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B245" s="10" t="s">
         <v>246</v>
@@ -9838,12 +9838,12 @@
         <v>130</v>
       </c>
       <c r="F245" s="9" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
     </row>
     <row r="246" spans="1:6">
       <c r="A246" s="9" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B246" s="11" t="s">
         <v>228</v>
@@ -9863,7 +9863,7 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" s="9" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B247" s="11" t="s">
         <v>228</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" s="9" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B248" s="11" t="s">
         <v>228</v>
@@ -9903,7 +9903,7 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" s="9" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B249" s="11" t="s">
         <v>228</v>
@@ -9923,7 +9923,7 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" s="9" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>228</v>
@@ -9943,7 +9943,7 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" s="9" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B251" s="11" t="s">
         <v>228</v>
@@ -9963,7 +9963,7 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" s="9" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B252" s="11" t="s">
         <v>228</v>
@@ -9983,7 +9983,7 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" s="9" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B253" s="11" t="s">
         <v>228</v>
@@ -10003,7 +10003,7 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" s="9" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B254" s="11" t="s">
         <v>228</v>
@@ -10023,7 +10023,7 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" s="9" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B255" s="11" t="s">
         <v>228</v>
@@ -10043,7 +10043,7 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" s="9" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>228</v>
@@ -10063,7 +10063,7 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" s="9" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B257" s="11" t="s">
         <v>228</v>
@@ -10083,7 +10083,7 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" s="9" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B258" s="11" t="s">
         <v>228</v>
@@ -10103,7 +10103,7 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" s="9" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B259" s="11" t="s">
         <v>228</v>
@@ -10123,7 +10123,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" s="9" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>228</v>
@@ -10143,7 +10143,7 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" s="9" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B261" s="11" t="s">
         <v>228</v>
@@ -10163,7 +10163,7 @@
     </row>
     <row r="262" spans="1:6">
       <c r="A262" s="9" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B262" s="11" t="s">
         <v>228</v>
@@ -10183,7 +10183,7 @@
     </row>
     <row r="263" spans="1:6">
       <c r="A263" s="9" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B263" s="10" t="s">
         <v>246</v>
@@ -10203,7 +10203,7 @@
     </row>
     <row r="264" spans="1:6">
       <c r="A264" s="9" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B264" s="11" t="s">
         <v>228</v>
@@ -10223,7 +10223,7 @@
     </row>
     <row r="265" spans="1:6">
       <c r="A265" s="9" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B265" s="11" t="s">
         <v>228</v>
@@ -10243,7 +10243,7 @@
     </row>
     <row r="266" spans="1:6">
       <c r="A266" s="9" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>228</v>
@@ -10263,7 +10263,7 @@
     </row>
     <row r="267" spans="1:6">
       <c r="A267" s="9" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B267" s="11" t="s">
         <v>228</v>
@@ -10283,7 +10283,7 @@
     </row>
     <row r="268" spans="1:6">
       <c r="A268" s="9" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B268" s="11" t="s">
         <v>228</v>
@@ -10303,7 +10303,7 @@
     </row>
     <row r="269" spans="1:6">
       <c r="A269" s="9" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B269" s="11" t="s">
         <v>228</v>
@@ -10323,7 +10323,7 @@
     </row>
     <row r="270" spans="1:6">
       <c r="A270" s="9" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>228</v>
@@ -10343,7 +10343,7 @@
     </row>
     <row r="271" spans="1:6">
       <c r="A271" s="9" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B271" s="11" t="s">
         <v>228</v>
@@ -10363,7 +10363,7 @@
     </row>
     <row r="272" spans="1:6">
       <c r="A272" s="9" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B272" s="11" t="s">
         <v>228</v>
@@ -10383,7 +10383,7 @@
     </row>
     <row r="273" spans="1:6">
       <c r="A273" s="9" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B273" s="11" t="s">
         <v>228</v>
@@ -10403,7 +10403,7 @@
     </row>
     <row r="274" spans="1:6">
       <c r="A274" s="9" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B274" s="11" t="s">
         <v>228</v>
@@ -10418,12 +10418,12 @@
         <v>126</v>
       </c>
       <c r="F274" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="275" spans="1:6">
       <c r="A275" s="9" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B275" s="11" t="s">
         <v>228</v>
@@ -10443,7 +10443,7 @@
     </row>
     <row r="276" spans="1:6">
       <c r="A276" s="9" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>228</v>
@@ -10458,12 +10458,12 @@
         <v>128</v>
       </c>
       <c r="F276" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="277" spans="1:6">
       <c r="A277" s="9" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B277" s="11" t="s">
         <v>228</v>
@@ -10483,7 +10483,7 @@
     </row>
     <row r="278" spans="1:6">
       <c r="A278" s="9" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B278" s="11" t="s">
         <v>228</v>
@@ -10498,12 +10498,12 @@
         <v>132</v>
       </c>
       <c r="F278" s="9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="279" spans="1:6">
       <c r="A279" s="9" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B279" s="11" t="s">
         <v>228</v>
@@ -10523,7 +10523,7 @@
     </row>
     <row r="280" spans="1:6">
       <c r="A280" s="9" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>228</v>
@@ -10538,12 +10538,12 @@
         <v>130</v>
       </c>
       <c r="F280" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="281" spans="1:6">
       <c r="A281" s="9" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B281" s="11" t="s">
         <v>228</v>
@@ -10563,7 +10563,7 @@
     </row>
     <row r="282" spans="1:6">
       <c r="A282" s="9" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B282" s="10" t="s">
         <v>246</v>
@@ -10583,7 +10583,7 @@
     </row>
     <row r="283" spans="1:6">
       <c r="A283" s="9" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B283" s="11" t="s">
         <v>228</v>
@@ -10603,7 +10603,7 @@
     </row>
     <row r="284" spans="1:6">
       <c r="A284" s="9" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B284" s="10" t="s">
         <v>246</v>
@@ -10618,12 +10618,12 @@
         <v>363</v>
       </c>
       <c r="F284" s="9" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="285" spans="1:6">
       <c r="A285" s="9" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B285" s="11" t="s">
         <v>228</v>
@@ -10643,13 +10643,13 @@
     </row>
     <row r="286" spans="1:6">
       <c r="A286" s="9" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B286" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C286" s="9" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="D286" s="9" t="s">
         <v>16</v>
@@ -10658,12 +10658,12 @@
         <v>248</v>
       </c>
       <c r="F286" s="9" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="287" spans="1:6">
       <c r="A287" s="9" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B287" s="11" t="s">
         <v>228</v>
@@ -10683,13 +10683,13 @@
     </row>
     <row r="288" spans="1:6">
       <c r="A288" s="9" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B288" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="D288" s="9" t="s">
         <v>16</v>
@@ -10698,12 +10698,12 @@
         <v>252</v>
       </c>
       <c r="F288" s="9" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="289" spans="1:6">
       <c r="A289" s="9" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B289" s="10" t="s">
         <v>246</v>
@@ -10723,7 +10723,7 @@
     </row>
     <row r="290" spans="1:6">
       <c r="A290" s="9" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>228</v>
@@ -10743,7 +10743,7 @@
     </row>
     <row r="291" spans="1:6">
       <c r="A291" s="9" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B291" s="11" t="s">
         <v>228</v>
@@ -10763,13 +10763,13 @@
     </row>
     <row r="292" spans="1:6">
       <c r="A292" s="9" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B292" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C292" s="9" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="D292" s="9"/>
       <c r="E292" s="9"/>
@@ -10777,13 +10777,13 @@
     </row>
     <row r="293" spans="1:6">
       <c r="A293" s="9" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B293" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C293" s="9" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="D293" s="9" t="s">
         <v>3</v>
@@ -10792,18 +10792,18 @@
         <v>10</v>
       </c>
       <c r="F293" s="9" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="294" spans="1:6">
       <c r="A294" s="9" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B294" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C294" s="9" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="D294" s="9" t="s">
         <v>16</v>
@@ -10817,13 +10817,13 @@
     </row>
     <row r="295" spans="1:6">
       <c r="A295" s="9" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B295" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C295" s="9" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D295" s="9" t="s">
         <v>3</v>
@@ -10837,13 +10837,13 @@
     </row>
     <row r="296" spans="1:6">
       <c r="A296" s="9" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B296" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C296" s="9" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D296" s="9" t="s">
         <v>16</v>
@@ -10857,13 +10857,13 @@
     </row>
     <row r="297" spans="1:6">
       <c r="A297" s="9" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B297" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C297" s="9" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D297" s="9" t="s">
         <v>3</v>
@@ -10877,13 +10877,13 @@
     </row>
     <row r="298" spans="1:6">
       <c r="A298" s="9" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B298" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C298" s="9" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D298" s="9" t="s">
         <v>3</v>
@@ -10897,13 +10897,13 @@
     </row>
     <row r="299" spans="1:6">
       <c r="A299" s="9" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B299" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C299" s="9" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="D299" s="9" t="s">
         <v>16</v>
@@ -10917,13 +10917,13 @@
     </row>
     <row r="300" spans="1:6">
       <c r="A300" s="9" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B300" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C300" s="9" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D300" s="9" t="s">
         <v>16</v>
@@ -10937,13 +10937,13 @@
     </row>
     <row r="301" spans="1:6">
       <c r="A301" s="9" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B301" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C301" s="9" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D301" s="9" t="s">
         <v>3</v>
@@ -10957,13 +10957,13 @@
     </row>
     <row r="302" spans="1:6">
       <c r="A302" s="9" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B302" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C302" s="9" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D302" s="9" t="s">
         <v>16</v>
@@ -10977,13 +10977,13 @@
     </row>
     <row r="303" spans="1:6">
       <c r="A303" s="9" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B303" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C303" s="9" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D303" s="9" t="s">
         <v>3</v>
@@ -10992,18 +10992,18 @@
         <v>160</v>
       </c>
       <c r="F303" s="9" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="304" spans="1:6">
       <c r="A304" s="9" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B304" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C304" s="9" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D304" s="9" t="s">
         <v>16</v>
@@ -11017,13 +11017,13 @@
     </row>
     <row r="305" spans="1:6">
       <c r="A305" s="9" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B305" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C305" s="9" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D305" s="9" t="s">
         <v>3</v>
@@ -11037,13 +11037,13 @@
     </row>
     <row r="306" spans="1:6">
       <c r="A306" s="9" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B306" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C306" s="9" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D306" s="9" t="s">
         <v>16</v>
@@ -11052,12 +11052,12 @@
         <v>204</v>
       </c>
       <c r="F306" s="9" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
     </row>
     <row r="307" spans="1:6">
       <c r="A307" s="9" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B307" s="11" t="s">
         <v>228</v>
@@ -11077,7 +11077,7 @@
     </row>
     <row r="308" spans="1:6">
       <c r="A308" s="9" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B308" s="10" t="s">
         <v>246</v>
@@ -11097,7 +11097,7 @@
     </row>
     <row r="309" spans="1:6">
       <c r="A309" s="9" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B309" s="11" t="s">
         <v>228</v>
@@ -11117,7 +11117,7 @@
     </row>
     <row r="310" spans="1:6">
       <c r="A310" s="9" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B310" s="10" t="s">
         <v>246</v>
@@ -11137,13 +11137,13 @@
     </row>
     <row r="311" spans="1:6">
       <c r="A311" s="9" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B311" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C311" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D311" s="9" t="s">
         <v>3</v>
@@ -11157,13 +11157,13 @@
     </row>
     <row r="312" spans="1:6">
       <c r="A312" s="9" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B312" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C312" s="9" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="D312" s="9" t="s">
         <v>16</v>
@@ -11177,7 +11177,7 @@
     </row>
     <row r="313" spans="1:6">
       <c r="A313" s="9" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B313" s="11" t="s">
         <v>228</v>
@@ -11197,7 +11197,7 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" s="9" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>228</v>
@@ -11212,18 +11212,18 @@
         <v>4</v>
       </c>
       <c r="F314" s="9" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
     </row>
     <row r="315" spans="1:6">
       <c r="A315" s="9" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B315" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C315" s="9" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="D315" s="9" t="s">
         <v>3</v>
@@ -11232,18 +11232,18 @@
         <v>126</v>
       </c>
       <c r="F315" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="316" spans="1:6">
       <c r="A316" s="9" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C316" s="9" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="D316" s="9" t="s">
         <v>3</v>
@@ -11252,18 +11252,18 @@
         <v>128</v>
       </c>
       <c r="F316" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="317" spans="1:6">
       <c r="A317" s="9" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B317" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C317" s="9" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="D317" s="9" t="s">
         <v>3</v>
@@ -11272,12 +11272,12 @@
         <v>132</v>
       </c>
       <c r="F317" s="9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="318" spans="1:6">
       <c r="A318" s="9" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>228</v>
@@ -11297,13 +11297,13 @@
     </row>
     <row r="319" spans="1:6">
       <c r="A319" s="9" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B319" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C319" s="9" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="D319" s="9" t="s">
         <v>3</v>
@@ -11312,12 +11312,12 @@
         <v>130</v>
       </c>
       <c r="F319" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="320" spans="1:6">
       <c r="A320" s="9" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>228</v>
@@ -11337,13 +11337,13 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" s="9" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B321" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D321" s="9" t="s">
         <v>16</v>
@@ -11352,18 +11352,18 @@
         <v>248</v>
       </c>
       <c r="F321" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="322" spans="1:6">
       <c r="A322" s="9" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B322" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C322" s="9" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D322" s="9" t="s">
         <v>16</v>
@@ -11372,12 +11372,12 @@
         <v>252</v>
       </c>
       <c r="F322" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="323" spans="1:6">
       <c r="A323" s="9" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B323" s="11" t="s">
         <v>228</v>
@@ -11397,13 +11397,13 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" s="9" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C324" s="9" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="D324" s="9" t="s">
         <v>3</v>
@@ -11417,13 +11417,13 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" s="9" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B325" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C325" s="9" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D325" s="9" t="s">
         <v>3</v>
@@ -11437,13 +11437,13 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" s="9" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C326" s="9" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="D326" s="9" t="s">
         <v>3</v>
@@ -11457,7 +11457,7 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" s="9" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B327" s="11" t="s">
         <v>228</v>
@@ -11477,13 +11477,13 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" s="9" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B328" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C328" s="9" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="D328" s="9" t="s">
         <v>3</v>
@@ -11497,7 +11497,7 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" s="9" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B329" s="11" t="s">
         <v>228</v>
@@ -11517,13 +11517,13 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" s="9" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B330" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C330" s="9" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="D330" s="9" t="s">
         <v>16</v>
@@ -11532,18 +11532,18 @@
         <v>360</v>
       </c>
       <c r="F330" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="331" spans="1:6">
       <c r="A331" s="9" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B331" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C331" s="9" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D331" s="9" t="s">
         <v>16</v>
@@ -11552,18 +11552,18 @@
         <v>363</v>
       </c>
       <c r="F331" s="9" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
     </row>
     <row r="332" spans="1:6">
       <c r="A332" s="9" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="B332" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C332" s="9" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D332" s="9" t="s">
         <v>3</v>
@@ -11572,18 +11572,18 @@
         <v>98</v>
       </c>
       <c r="F332" s="9" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="333" spans="1:6">
       <c r="A333" s="9" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B333" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C333" s="9" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="D333" s="9" t="s">
         <v>3</v>
@@ -11592,18 +11592,18 @@
         <v>90</v>
       </c>
       <c r="F333" s="9" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="334" spans="1:6">
       <c r="A334" s="9" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B334" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C334" s="9" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D334" s="9" t="s">
         <v>3</v>
@@ -11612,12 +11612,12 @@
         <v>54</v>
       </c>
       <c r="F334" s="9" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="335" spans="1:6">
       <c r="A335" s="9" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B335" s="11" t="s">
         <v>228</v>
@@ -11637,13 +11637,13 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" s="9" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B336" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C336" s="9" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="D336" s="9" t="s">
         <v>3</v>
@@ -11652,12 +11652,12 @@
         <v>60</v>
       </c>
       <c r="F336" s="9" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="337" spans="1:6">
       <c r="A337" s="9" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B337" s="11" t="s">
         <v>228</v>
@@ -11677,13 +11677,13 @@
     </row>
     <row r="338" spans="1:6">
       <c r="A338" s="9" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B338" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C338" s="9" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="D338" s="9" t="s">
         <v>16</v>
@@ -11697,13 +11697,13 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" s="9" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B339" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C339" s="9" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="D339" s="9" t="s">
         <v>16</v>
@@ -11717,7 +11717,7 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" s="9" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>228</v>
@@ -11737,13 +11737,13 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" s="9" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B341" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C341" s="9" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D341" s="9" t="s">
         <v>3</v>
@@ -11757,13 +11757,13 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" s="9" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B342" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C342" s="9" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D342" s="9" t="s">
         <v>16</v>
@@ -11777,13 +11777,13 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" s="9" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B343" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C343" s="9" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="D343" s="9" t="s">
         <v>3</v>
@@ -11797,13 +11797,13 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" s="9" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B344" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C344" s="9" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="D344" s="9" t="s">
         <v>16</v>
@@ -11817,13 +11817,13 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" s="9" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B345" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C345" s="9" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="D345" s="9" t="s">
         <v>3</v>
@@ -11837,13 +11837,13 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" s="9" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B346" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C346" s="9" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="D346" s="9" t="s">
         <v>16</v>
@@ -11857,13 +11857,13 @@
     </row>
     <row r="347" spans="1:6">
       <c r="A347" s="9" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B347" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C347" s="9" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D347" s="9" t="s">
         <v>3</v>
@@ -11877,13 +11877,13 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" s="9" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B348" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C348" s="9" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="D348" s="9" t="s">
         <v>16</v>
@@ -11897,13 +11897,13 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" s="9" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B349" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C349" s="9" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="D349" s="9" t="s">
         <v>3</v>
@@ -11917,13 +11917,13 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" s="9" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B350" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C350" s="9" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="D350" s="9" t="s">
         <v>16</v>
@@ -11937,13 +11937,13 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" s="9" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B351" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C351" s="9" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="D351" s="9" t="s">
         <v>3</v>
@@ -11957,13 +11957,13 @@
     </row>
     <row r="352" spans="1:6">
       <c r="A352" s="9" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B352" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C352" s="9" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="D352" s="9" t="s">
         <v>16</v>
@@ -11977,7 +11977,7 @@
     </row>
     <row r="353" spans="1:6">
       <c r="A353" s="9" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B353" s="11" t="s">
         <v>228</v>
@@ -11997,13 +11997,13 @@
     </row>
     <row r="354" spans="1:6">
       <c r="A354" s="9" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B354" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C354" s="9" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="D354" s="9" t="s">
         <v>3</v>
@@ -12017,7 +12017,7 @@
     </row>
     <row r="355" spans="1:6">
       <c r="A355" s="9" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B355" s="11" t="s">
         <v>228</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="356" spans="1:6">
       <c r="A356" s="9" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B356" s="11" t="s">
         <v>228</v>
@@ -12057,7 +12057,7 @@
     </row>
     <row r="357" spans="1:6">
       <c r="A357" s="9" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="B357" s="11" t="s">
         <v>228</v>
@@ -12077,7 +12077,7 @@
     </row>
     <row r="358" spans="1:6">
       <c r="A358" s="9" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B358" s="11" t="s">
         <v>228</v>
@@ -12097,13 +12097,13 @@
     </row>
     <row r="359" spans="1:6">
       <c r="A359" s="9" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B359" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C359" s="9" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D359" s="9" t="s">
         <v>3</v>
@@ -12117,13 +12117,13 @@
     </row>
     <row r="360" spans="1:6">
       <c r="A360" s="9" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B360" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C360" s="9" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D360" s="9" t="s">
         <v>16</v>
@@ -12137,13 +12137,13 @@
     </row>
     <row r="361" spans="1:6">
       <c r="A361" s="9" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B361" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C361" s="9" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D361" s="9" t="s">
         <v>3</v>
@@ -12157,13 +12157,13 @@
     </row>
     <row r="362" spans="1:6">
       <c r="A362" s="9" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B362" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C362" s="9" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D362" s="9" t="s">
         <v>16</v>
@@ -12177,7 +12177,7 @@
     </row>
     <row r="363" spans="1:6">
       <c r="A363" s="9" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="B363" s="11" t="s">
         <v>228</v>
@@ -12192,12 +12192,12 @@
         <v>173</v>
       </c>
       <c r="F363" s="9" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
     </row>
     <row r="364" spans="1:6">
       <c r="A364" s="9" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="B364" s="11" t="s">
         <v>228</v>
@@ -12217,13 +12217,13 @@
     </row>
     <row r="365" spans="1:6">
       <c r="A365" s="9" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B365" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C365" s="9" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="D365" s="9" t="s">
         <v>3</v>
@@ -12232,12 +12232,12 @@
         <v>162</v>
       </c>
       <c r="F365" s="9" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="366" spans="1:6">
       <c r="A366" s="9" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B366" s="11" t="s">
         <v>228</v>
@@ -12257,7 +12257,7 @@
     </row>
     <row r="367" spans="1:6">
       <c r="A367" s="9" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B367" s="11" t="s">
         <v>228</v>
@@ -12277,13 +12277,13 @@
     </row>
     <row r="368" spans="1:6">
       <c r="A368" s="9" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B368" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C368" s="9" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="D368" s="9" t="s">
         <v>16</v>
@@ -12292,18 +12292,18 @@
         <v>360</v>
       </c>
       <c r="F368" s="9" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
     </row>
     <row r="369" spans="1:6">
       <c r="A369" s="9" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B369" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C369" s="9" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="D369" s="9" t="s">
         <v>16</v>
@@ -12312,12 +12312,12 @@
         <v>363</v>
       </c>
       <c r="F369" s="9" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
     </row>
     <row r="370" spans="1:6">
       <c r="A370" s="9" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="B370" s="11" t="s">
         <v>228</v>
@@ -12337,7 +12337,7 @@
     </row>
     <row r="371" spans="1:6">
       <c r="A371" s="9" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B371" s="11" t="s">
         <v>228</v>
@@ -12352,12 +12352,12 @@
         <v>185</v>
       </c>
       <c r="F371" s="9" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="372" spans="1:6">
       <c r="A372" s="9" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B372" s="11" t="s">
         <v>228</v>
@@ -12377,7 +12377,7 @@
     </row>
     <row r="373" spans="1:6">
       <c r="A373" s="9" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B373" s="11" t="s">
         <v>228</v>
@@ -12392,12 +12392,12 @@
         <v>185</v>
       </c>
       <c r="F373" s="9" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="374" spans="1:6">
       <c r="A374" s="9" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B374" s="11" t="s">
         <v>228</v>
@@ -12417,13 +12417,13 @@
     </row>
     <row r="375" spans="1:6">
       <c r="A375" s="9" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B375" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C375" s="9" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="D375" s="9" t="s">
         <v>16</v>
@@ -12437,7 +12437,7 @@
     </row>
     <row r="376" spans="1:6">
       <c r="A376" s="9" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="B376" s="11" t="s">
         <v>228</v>
@@ -12457,7 +12457,7 @@
     </row>
     <row r="377" spans="1:6">
       <c r="A377" s="9" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B377" s="10" t="s">
         <v>246</v>
@@ -12472,12 +12472,12 @@
         <v>363</v>
       </c>
       <c r="F377" s="9" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
     </row>
     <row r="378" spans="1:6">
       <c r="A378" s="9" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="B378" s="11" t="s">
         <v>228</v>
@@ -12497,13 +12497,13 @@
     </row>
     <row r="379" spans="1:6">
       <c r="A379" s="9" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B379" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C379" s="9" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D379" s="9" t="s">
         <v>16</v>
@@ -12512,12 +12512,12 @@
         <v>248</v>
       </c>
       <c r="F379" s="9" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
     </row>
     <row r="380" spans="1:6">
       <c r="A380" s="9" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B380" s="11" t="s">
         <v>228</v>
@@ -12537,13 +12537,13 @@
     </row>
     <row r="381" spans="1:6">
       <c r="A381" s="9" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B381" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C381" s="9" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="D381" s="9" t="s">
         <v>16</v>
@@ -12552,12 +12552,12 @@
         <v>252</v>
       </c>
       <c r="F381" s="9" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
     </row>
     <row r="382" spans="1:6">
       <c r="A382" s="9" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B382" s="11" t="s">
         <v>228</v>
@@ -12577,7 +12577,7 @@
     </row>
     <row r="383" spans="1:6">
       <c r="A383" s="9" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B383" s="10" t="s">
         <v>246</v>
@@ -12597,13 +12597,13 @@
     </row>
     <row r="384" spans="1:6">
       <c r="A384" s="9" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="B384" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C384" s="9" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="D384" s="9"/>
       <c r="E384" s="9"/>
@@ -12611,13 +12611,13 @@
     </row>
     <row r="385" spans="1:6">
       <c r="A385" s="9" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="B385" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C385" s="14" t="s">
-        <v>1436</v>
+        <v>1430</v>
       </c>
       <c r="D385" s="9" t="s">
         <v>170</v>
@@ -12626,18 +12626,18 @@
         <v>185</v>
       </c>
       <c r="F385" s="9" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
     </row>
     <row r="386" spans="1:6">
       <c r="A386" s="9" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="B386" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C386" s="9" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D386" s="9" t="s">
         <v>16</v>
@@ -12646,18 +12646,18 @@
         <v>206</v>
       </c>
       <c r="F386" s="9" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="387" spans="1:6">
       <c r="A387" s="9" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B387" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C387" s="9" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D387" s="9" t="s">
         <v>16</v>
@@ -12666,18 +12666,18 @@
         <v>208</v>
       </c>
       <c r="F387" s="9" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
     </row>
     <row r="388" spans="1:6">
       <c r="A388" s="9" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="B388" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C388" s="9" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D388" s="9" t="s">
         <v>3</v>
@@ -12691,13 +12691,13 @@
     </row>
     <row r="389" spans="1:6">
       <c r="A389" s="9" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="B389" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C389" s="9" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D389" s="9" t="s">
         <v>16</v>
@@ -12711,13 +12711,13 @@
     </row>
     <row r="390" spans="1:6">
       <c r="A390" s="9" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="B390" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C390" s="14" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="D390" s="9" t="s">
         <v>3</v>
@@ -12731,13 +12731,13 @@
     </row>
     <row r="391" spans="1:6">
       <c r="A391" s="9" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B391" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C391" s="14" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="D391" s="9" t="s">
         <v>16</v>
@@ -12751,13 +12751,13 @@
     </row>
     <row r="392" spans="1:6">
       <c r="A392" s="9" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="B392" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C392" s="9" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D392" s="9"/>
       <c r="E392" s="9"/>
@@ -12765,7 +12765,7 @@
     </row>
     <row r="393" spans="1:6">
       <c r="A393" s="9" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="B393" s="11" t="s">
         <v>228</v>
@@ -12785,7 +12785,7 @@
     </row>
     <row r="394" spans="1:6">
       <c r="A394" s="9" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B394" s="11" t="s">
         <v>228</v>
@@ -12805,13 +12805,13 @@
     </row>
     <row r="395" spans="1:6">
       <c r="A395" s="9" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B395" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C395" s="9" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="D395" s="9" t="s">
         <v>170</v>
@@ -12825,13 +12825,13 @@
     </row>
     <row r="396" spans="1:6">
       <c r="A396" s="9" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="B396" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C396" s="9" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="D396" s="9" t="s">
         <v>16</v>
@@ -12845,13 +12845,13 @@
     </row>
     <row r="397" spans="1:6">
       <c r="A397" s="9" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B397" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C397" s="9" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D397" s="9" t="s">
         <v>3</v>
@@ -12865,13 +12865,13 @@
     </row>
     <row r="398" spans="1:6">
       <c r="A398" s="9" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="B398" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C398" s="9" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D398" s="9" t="s">
         <v>16</v>
@@ -12885,13 +12885,13 @@
     </row>
     <row r="399" spans="1:6">
       <c r="A399" s="9" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B399" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C399" s="9" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D399" s="9" t="s">
         <v>3</v>
@@ -12905,13 +12905,13 @@
     </row>
     <row r="400" spans="1:6">
       <c r="A400" s="9" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="B400" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C400" s="9" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
       <c r="D400" s="9" t="s">
         <v>16</v>
@@ -12925,13 +12925,13 @@
     </row>
     <row r="401" spans="1:6">
       <c r="A401" s="9" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B401" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C401" s="9" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D401" s="9" t="s">
         <v>3</v>
@@ -12945,13 +12945,13 @@
     </row>
     <row r="402" spans="1:6">
       <c r="A402" s="9" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="B402" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C402" s="9" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D402" s="9" t="s">
         <v>16</v>
@@ -12965,13 +12965,13 @@
     </row>
     <row r="403" spans="1:6">
       <c r="A403" s="9" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="B403" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C403" s="9" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="D403" s="9" t="s">
         <v>3</v>
@@ -12985,13 +12985,13 @@
     </row>
     <row r="404" spans="1:6">
       <c r="A404" s="9" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="B404" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C404" s="9" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="D404" s="9" t="s">
         <v>16</v>
@@ -13005,13 +13005,13 @@
     </row>
     <row r="405" spans="1:6">
       <c r="A405" s="9" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B405" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C405" s="9" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D405" s="9" t="s">
         <v>3</v>
@@ -13025,13 +13025,13 @@
     </row>
     <row r="406" spans="1:6">
       <c r="A406" s="9" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B406" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C406" s="9" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D406" s="9" t="s">
         <v>16</v>
@@ -13045,13 +13045,13 @@
     </row>
     <row r="407" spans="1:6">
       <c r="A407" s="9" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="B407" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C407" s="9" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D407" s="9" t="s">
         <v>3</v>
@@ -13065,13 +13065,13 @@
     </row>
     <row r="408" spans="1:6">
       <c r="A408" s="9" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B408" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C408" s="9" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D408" s="9" t="s">
         <v>16</v>
@@ -13080,12 +13080,12 @@
         <v>199</v>
       </c>
       <c r="F408" s="9" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
     <row r="409" spans="1:6">
       <c r="A409" s="9" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B409" s="11" t="s">
         <v>228</v>
@@ -13105,13 +13105,13 @@
     </row>
     <row r="410" spans="1:6">
       <c r="A410" s="9" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B410" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C410" s="9" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="D410" s="9" t="s">
         <v>3</v>
@@ -13125,13 +13125,13 @@
     </row>
     <row r="411" spans="1:6">
       <c r="A411" s="9" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B411" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C411" s="9" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="D411" s="9" t="s">
         <v>3</v>
@@ -13140,18 +13140,18 @@
         <v>98</v>
       </c>
       <c r="F411" s="9" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="412" spans="1:6">
       <c r="A412" s="9" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B412" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C412" s="9" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="D412" s="9" t="s">
         <v>3</v>
@@ -13160,18 +13160,18 @@
         <v>90</v>
       </c>
       <c r="F412" s="9" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="413" spans="1:6">
       <c r="A413" s="9" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B413" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C413" s="9" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="D413" s="9" t="s">
         <v>3</v>
@@ -13180,12 +13180,12 @@
         <v>54</v>
       </c>
       <c r="F413" s="9" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="414" spans="1:6">
       <c r="A414" s="9" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>228</v>
@@ -13205,13 +13205,13 @@
     </row>
     <row r="415" spans="1:6">
       <c r="A415" s="9" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="B415" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C415" s="9" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="D415" s="9" t="s">
         <v>3</v>
@@ -13220,12 +13220,12 @@
         <v>60</v>
       </c>
       <c r="F415" s="9" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="416" spans="1:6">
       <c r="A416" s="9" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="B416" s="11" t="s">
         <v>228</v>
@@ -13245,13 +13245,13 @@
     </row>
     <row r="417" spans="1:6">
       <c r="A417" s="9" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B417" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C417" s="9" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D417" s="9" t="s">
         <v>16</v>
@@ -13260,18 +13260,18 @@
         <v>248</v>
       </c>
       <c r="F417" s="9" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="418" spans="1:6">
       <c r="A418" s="9" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="B418" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C418" s="9" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="D418" s="9" t="s">
         <v>16</v>
@@ -13280,12 +13280,12 @@
         <v>252</v>
       </c>
       <c r="F418" s="9" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="419" spans="1:6">
       <c r="A419" s="9" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B419" s="11" t="s">
         <v>228</v>
@@ -13305,7 +13305,7 @@
     </row>
     <row r="420" spans="1:6">
       <c r="A420" s="9" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="B420" s="10" t="s">
         <v>246</v>
@@ -13325,13 +13325,13 @@
     </row>
     <row r="421" spans="1:6">
       <c r="A421" s="9" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B421" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C421" s="9" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="D421" s="9" t="s">
         <v>3</v>
@@ -13345,13 +13345,13 @@
     </row>
     <row r="422" spans="1:6">
       <c r="A422" s="9" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B422" s="10" t="s">
         <v>246</v>
       </c>
       <c r="C422" s="9" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="D422" s="9" t="s">
         <v>16</v>
@@ -13365,19 +13365,19 @@
     </row>
     <row r="423" spans="1:6">
       <c r="A423" s="9" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="B423" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C423" s="14" t="s">
-        <v>1435</v>
+        <v>1429</v>
       </c>
       <c r="D423" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E423" s="9" t="s">
-        <v>1434</v>
+        <v>1428</v>
       </c>
       <c r="F423" s="9" t="s">
         <v>491</v>
@@ -13385,13 +13385,13 @@
     </row>
     <row r="424" spans="1:6" ht="27">
       <c r="A424" s="9" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B424" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C424" s="14" t="s">
-        <v>1433</v>
+        <v>1475</v>
       </c>
       <c r="D424" s="9" t="s">
         <v>3</v>
@@ -13400,18 +13400,18 @@
         <v>126</v>
       </c>
       <c r="F424" s="9" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="425" spans="1:6" ht="27">
       <c r="A425" s="9" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="B425" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C425" s="14" t="s">
-        <v>1432</v>
+        <v>1476</v>
       </c>
       <c r="D425" s="9" t="s">
         <v>3</v>
@@ -13420,18 +13420,18 @@
         <v>128</v>
       </c>
       <c r="F425" s="9" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="426" spans="1:6" ht="27">
       <c r="A426" s="9" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B426" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C426" s="14" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="D426" s="9" t="s">
         <v>3</v>
@@ -13440,18 +13440,18 @@
         <v>132</v>
       </c>
       <c r="F426" s="9" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="427" spans="1:6" ht="27">
       <c r="A427" s="9" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="B427" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C427" s="14" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="D427" s="9" t="s">
         <v>3</v>
@@ -13460,18 +13460,18 @@
         <v>130</v>
       </c>
       <c r="F427" s="9" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
     </row>
     <row r="428" spans="1:6">
       <c r="A428" s="9" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B428" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C428" s="9" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="D428" s="9"/>
       <c r="E428" s="9"/>
@@ -13479,7 +13479,7 @@
     </row>
     <row r="429" spans="1:6">
       <c r="A429" s="9" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B429" s="11" t="s">
         <v>228</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="430" spans="1:6">
       <c r="A430" s="9" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="B430" s="11" t="s">
         <v>228</v>
@@ -13519,13 +13519,13 @@
     </row>
     <row r="431" spans="1:6">
       <c r="A431" s="9" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B431" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C431" s="9" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="D431" s="9"/>
       <c r="E431" s="9"/>
@@ -13533,7 +13533,7 @@
     </row>
     <row r="432" spans="1:6">
       <c r="A432" s="9" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B432" s="11" t="s">
         <v>228</v>
@@ -13553,13 +13553,13 @@
     </row>
     <row r="433" spans="1:6">
       <c r="A433" s="9" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="B433" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C433" s="15" t="s">
-        <v>1438</v>
+        <v>1432</v>
       </c>
       <c r="D433" s="9" t="s">
         <v>3</v>
@@ -13573,7 +13573,7 @@
     </row>
     <row r="434" spans="1:6">
       <c r="A434" s="9" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B434" s="11" t="s">
         <v>228</v>
@@ -13593,13 +13593,13 @@
     </row>
     <row r="435" spans="1:6">
       <c r="A435" s="9" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="B435" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C435" s="15" t="s">
-        <v>1439</v>
+        <v>1433</v>
       </c>
       <c r="D435" s="9" t="s">
         <v>3</v>
@@ -13613,7 +13613,7 @@
     </row>
     <row r="436" spans="1:6">
       <c r="A436" s="9" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B436" s="11" t="s">
         <v>228</v>
@@ -13633,13 +13633,13 @@
     </row>
     <row r="437" spans="1:6">
       <c r="A437" s="9" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="B437" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C437" s="15" t="s">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="D437" s="9" t="s">
         <v>3</v>
@@ -13653,7 +13653,7 @@
     </row>
     <row r="438" spans="1:6">
       <c r="A438" s="9" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B438" s="11" t="s">
         <v>228</v>
@@ -13673,13 +13673,13 @@
     </row>
     <row r="439" spans="1:6">
       <c r="A439" s="9" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="B439" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C439" s="15" t="s">
-        <v>1441</v>
+        <v>1435</v>
       </c>
       <c r="D439" s="9" t="s">
         <v>3</v>
@@ -13693,7 +13693,7 @@
     </row>
     <row r="440" spans="1:6">
       <c r="A440" s="9" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B440" s="11" t="s">
         <v>228</v>
@@ -13713,13 +13713,13 @@
     </row>
     <row r="441" spans="1:6">
       <c r="A441" s="9" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="B441" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C441" s="15" t="s">
-        <v>1442</v>
+        <v>1436</v>
       </c>
       <c r="D441" s="9" t="s">
         <v>3</v>
@@ -13733,7 +13733,7 @@
     </row>
     <row r="442" spans="1:6">
       <c r="A442" s="9" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B442" s="11" t="s">
         <v>228</v>
@@ -13753,13 +13753,13 @@
     </row>
     <row r="443" spans="1:6">
       <c r="A443" s="9" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B443" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C443" s="15" t="s">
-        <v>1444</v>
+        <v>1438</v>
       </c>
       <c r="D443" s="9" t="s">
         <v>3</v>
@@ -13773,7 +13773,7 @@
     </row>
     <row r="444" spans="1:6">
       <c r="A444" s="9" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B444" s="11" t="s">
         <v>228</v>
@@ -13793,13 +13793,13 @@
     </row>
     <row r="445" spans="1:6">
       <c r="A445" s="9" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="B445" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C445" s="15" t="s">
-        <v>1445</v>
+        <v>1439</v>
       </c>
       <c r="D445" s="9" t="s">
         <v>3</v>
@@ -13813,7 +13813,7 @@
     </row>
     <row r="446" spans="1:6">
       <c r="A446" s="9" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B446" s="11" t="s">
         <v>228</v>
@@ -13833,13 +13833,13 @@
     </row>
     <row r="447" spans="1:6">
       <c r="A447" s="9" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="B447" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C447" s="15" t="s">
-        <v>1443</v>
+        <v>1437</v>
       </c>
       <c r="D447" s="9" t="s">
         <v>3</v>
@@ -13853,7 +13853,7 @@
     </row>
     <row r="448" spans="1:6">
       <c r="A448" s="9" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B448" s="11" t="s">
         <v>228</v>
@@ -13873,13 +13873,13 @@
     </row>
     <row r="449" spans="1:6">
       <c r="A449" s="9" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="B449" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C449" s="15" t="s">
-        <v>1446</v>
+        <v>1440</v>
       </c>
       <c r="D449" s="9" t="s">
         <v>3</v>
@@ -13893,7 +13893,7 @@
     </row>
     <row r="450" spans="1:6">
       <c r="A450" s="9" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B450" s="11" t="s">
         <v>228</v>
@@ -13913,13 +13913,13 @@
     </row>
     <row r="451" spans="1:6">
       <c r="A451" s="9" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="B451" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C451" s="15" t="s">
-        <v>1447</v>
+        <v>1441</v>
       </c>
       <c r="D451" s="9" t="s">
         <v>3</v>
@@ -13933,7 +13933,7 @@
     </row>
     <row r="452" spans="1:6">
       <c r="A452" s="9" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B452" s="11" t="s">
         <v>228</v>
@@ -13953,13 +13953,13 @@
     </row>
     <row r="453" spans="1:6">
       <c r="A453" s="9" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="B453" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C453" s="15" t="s">
-        <v>1448</v>
+        <v>1442</v>
       </c>
       <c r="D453" s="9" t="s">
         <v>3</v>
@@ -13973,7 +13973,7 @@
     </row>
     <row r="454" spans="1:6">
       <c r="A454" s="9" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B454" s="11" t="s">
         <v>228</v>
@@ -13993,13 +13993,13 @@
     </row>
     <row r="455" spans="1:6">
       <c r="A455" s="9" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="B455" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C455" s="15" t="s">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="D455" s="9" t="s">
         <v>3</v>
@@ -14013,7 +14013,7 @@
     </row>
     <row r="456" spans="1:6">
       <c r="A456" s="9" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B456" s="11" t="s">
         <v>228</v>
@@ -14033,13 +14033,13 @@
     </row>
     <row r="457" spans="1:6">
       <c r="A457" s="9" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="B457" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C457" s="15" t="s">
-        <v>1450</v>
+        <v>1444</v>
       </c>
       <c r="D457" s="9" t="s">
         <v>3</v>
@@ -14048,12 +14048,12 @@
         <v>54</v>
       </c>
       <c r="F457" s="9" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="458" spans="1:6">
       <c r="A458" s="9" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B458" s="11" t="s">
         <v>228</v>
@@ -14073,13 +14073,13 @@
     </row>
     <row r="459" spans="1:6">
       <c r="A459" s="9" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="B459" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C459" s="15" t="s">
-        <v>1451</v>
+        <v>1445</v>
       </c>
       <c r="D459" s="9" t="s">
         <v>3</v>
@@ -14093,7 +14093,7 @@
     </row>
     <row r="460" spans="1:6">
       <c r="A460" s="9" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B460" s="11" t="s">
         <v>228</v>
@@ -14113,13 +14113,13 @@
     </row>
     <row r="461" spans="1:6">
       <c r="A461" s="9" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="B461" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C461" s="15" t="s">
-        <v>1452</v>
+        <v>1446</v>
       </c>
       <c r="D461" s="9" t="s">
         <v>3</v>
@@ -14128,12 +14128,12 @@
         <v>90</v>
       </c>
       <c r="F461" s="9" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="462" spans="1:6">
       <c r="A462" s="9" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="B462" s="11" t="s">
         <v>228</v>
@@ -14153,13 +14153,13 @@
     </row>
     <row r="463" spans="1:6">
       <c r="A463" s="9" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B463" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C463" s="15" t="s">
-        <v>1453</v>
+        <v>1447</v>
       </c>
       <c r="D463" s="9" t="s">
         <v>3</v>
@@ -14168,12 +14168,12 @@
         <v>36</v>
       </c>
       <c r="F463" s="9" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
     </row>
     <row r="464" spans="1:6">
       <c r="A464" s="9" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="B464" s="11" t="s">
         <v>228</v>
@@ -14193,13 +14193,13 @@
     </row>
     <row r="465" spans="1:6">
       <c r="A465" s="9" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="B465" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C465" s="15" t="s">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="D465" s="9" t="s">
         <v>3</v>
@@ -14208,12 +14208,12 @@
         <v>60</v>
       </c>
       <c r="F465" s="9" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="466" spans="1:6">
       <c r="A466" s="9" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B466" s="11" t="s">
         <v>228</v>
@@ -14233,7 +14233,7 @@
     </row>
     <row r="467" spans="1:6">
       <c r="A467" s="9" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B467" s="11" t="s">
         <v>228</v>
@@ -14253,7 +14253,7 @@
     </row>
     <row r="468" spans="1:6">
       <c r="A468" s="9" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B468" s="11" t="s">
         <v>228</v>
@@ -14273,13 +14273,13 @@
     </row>
     <row r="469" spans="1:6">
       <c r="A469" s="9" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B469" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C469" s="15" t="s">
-        <v>1455</v>
+        <v>1449</v>
       </c>
       <c r="D469" s="9" t="s">
         <v>3</v>
@@ -14288,12 +14288,12 @@
         <v>38</v>
       </c>
       <c r="F469" s="9" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
     </row>
     <row r="470" spans="1:6">
       <c r="A470" s="9" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B470" s="11" t="s">
         <v>228</v>
@@ -14313,13 +14313,13 @@
     </row>
     <row r="471" spans="1:6">
       <c r="A471" s="9" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B471" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C471" s="15" t="s">
-        <v>1456</v>
+        <v>1450</v>
       </c>
       <c r="D471" s="9" t="s">
         <v>3</v>
@@ -14333,7 +14333,7 @@
     </row>
     <row r="472" spans="1:6">
       <c r="A472" s="9" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="B472" s="11" t="s">
         <v>228</v>
@@ -14353,13 +14353,13 @@
     </row>
     <row r="473" spans="1:6">
       <c r="A473" s="9" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B473" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C473" s="15" t="s">
-        <v>1457</v>
+        <v>1451</v>
       </c>
       <c r="D473" s="9" t="s">
         <v>3</v>
@@ -14373,7 +14373,7 @@
     </row>
     <row r="474" spans="1:6">
       <c r="A474" s="9" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="B474" s="11" t="s">
         <v>228</v>
@@ -14393,13 +14393,13 @@
     </row>
     <row r="475" spans="1:6">
       <c r="A475" s="9" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B475" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C475" s="15" t="s">
-        <v>1458</v>
+        <v>1452</v>
       </c>
       <c r="D475" s="9" t="s">
         <v>3</v>
@@ -14413,7 +14413,7 @@
     </row>
     <row r="476" spans="1:6">
       <c r="A476" s="9" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="B476" s="11" t="s">
         <v>228</v>
@@ -14433,13 +14433,13 @@
     </row>
     <row r="477" spans="1:6">
       <c r="A477" s="9" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B477" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C477" s="15" t="s">
-        <v>1459</v>
+        <v>1453</v>
       </c>
       <c r="D477" s="9" t="s">
         <v>3</v>
@@ -14453,7 +14453,7 @@
     </row>
     <row r="478" spans="1:6">
       <c r="A478" s="9" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="B478" s="11" t="s">
         <v>228</v>
@@ -14473,13 +14473,13 @@
     </row>
     <row r="479" spans="1:6">
       <c r="A479" s="9" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="B479" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C479" s="15" t="s">
-        <v>1460</v>
+        <v>1454</v>
       </c>
       <c r="D479" s="9" t="s">
         <v>3</v>
@@ -14493,7 +14493,7 @@
     </row>
     <row r="480" spans="1:6">
       <c r="A480" s="9" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="B480" s="11" t="s">
         <v>228</v>
@@ -14513,13 +14513,13 @@
     </row>
     <row r="481" spans="1:6">
       <c r="A481" s="9" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="B481" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C481" s="15" t="s">
-        <v>1461</v>
+        <v>1455</v>
       </c>
       <c r="D481" s="9" t="s">
         <v>3</v>
@@ -14533,7 +14533,7 @@
     </row>
     <row r="482" spans="1:6">
       <c r="A482" s="9" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B482" s="11" t="s">
         <v>228</v>
@@ -14553,13 +14553,13 @@
     </row>
     <row r="483" spans="1:6">
       <c r="A483" s="9" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="B483" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C483" s="15" t="s">
-        <v>1462</v>
+        <v>1456</v>
       </c>
       <c r="D483" s="9" t="s">
         <v>3</v>
@@ -14573,7 +14573,7 @@
     </row>
     <row r="484" spans="1:6">
       <c r="A484" s="9" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B484" s="11" t="s">
         <v>228</v>
@@ -14593,13 +14593,13 @@
     </row>
     <row r="485" spans="1:6">
       <c r="A485" s="9" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="B485" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C485" s="15" t="s">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="D485" s="9" t="s">
         <v>3</v>
@@ -14608,12 +14608,12 @@
         <v>98</v>
       </c>
       <c r="F485" s="9" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="486" spans="1:6">
       <c r="A486" s="9" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B486" s="11" t="s">
         <v>228</v>
@@ -14633,13 +14633,13 @@
     </row>
     <row r="487" spans="1:6">
       <c r="A487" s="9" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="B487" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C487" s="15" t="s">
-        <v>1464</v>
+        <v>1458</v>
       </c>
       <c r="D487" s="9" t="s">
         <v>3</v>
@@ -14653,7 +14653,7 @@
     </row>
     <row r="488" spans="1:6">
       <c r="A488" s="9" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="B488" s="11" t="s">
         <v>228</v>
@@ -14673,13 +14673,13 @@
     </row>
     <row r="489" spans="1:6">
       <c r="A489" s="9" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="B489" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C489" s="15" t="s">
-        <v>1465</v>
+        <v>1459</v>
       </c>
       <c r="D489" s="9" t="s">
         <v>3</v>
@@ -14693,7 +14693,7 @@
     </row>
     <row r="490" spans="1:6">
       <c r="A490" s="9" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="B490" s="11" t="s">
         <v>228</v>
@@ -14713,7 +14713,7 @@
     </row>
     <row r="491" spans="1:6">
       <c r="A491" s="9" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="B491" s="11" t="s">
         <v>228</v>
@@ -14733,7 +14733,7 @@
     </row>
     <row r="492" spans="1:6">
       <c r="A492" s="9" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="B492" s="11" t="s">
         <v>228</v>
@@ -14753,13 +14753,13 @@
     </row>
     <row r="493" spans="1:6">
       <c r="A493" s="9" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="B493" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C493" s="15" t="s">
-        <v>1466</v>
+        <v>1460</v>
       </c>
       <c r="D493" s="9" t="s">
         <v>3</v>
@@ -14773,7 +14773,7 @@
     </row>
     <row r="494" spans="1:6">
       <c r="A494" s="9" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="B494" s="11" t="s">
         <v>228</v>
@@ -14793,13 +14793,13 @@
     </row>
     <row r="495" spans="1:6">
       <c r="A495" s="9" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="B495" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C495" s="15" t="s">
-        <v>1467</v>
+        <v>1461</v>
       </c>
       <c r="D495" s="9" t="s">
         <v>3</v>
@@ -14813,7 +14813,7 @@
     </row>
     <row r="496" spans="1:6">
       <c r="A496" s="9" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="B496" s="11" t="s">
         <v>228</v>
@@ -14833,13 +14833,13 @@
     </row>
     <row r="497" spans="1:6">
       <c r="A497" s="9" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="B497" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C497" s="15" t="s">
-        <v>1468</v>
+        <v>1462</v>
       </c>
       <c r="D497" s="9" t="s">
         <v>3</v>
@@ -14853,7 +14853,7 @@
     </row>
     <row r="498" spans="1:6">
       <c r="A498" s="9" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B498" s="11" t="s">
         <v>228</v>
@@ -14873,13 +14873,13 @@
     </row>
     <row r="499" spans="1:6">
       <c r="A499" s="9" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="B499" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C499" s="15" t="s">
-        <v>1469</v>
+        <v>1463</v>
       </c>
       <c r="D499" s="9" t="s">
         <v>3</v>
@@ -14893,7 +14893,7 @@
     </row>
     <row r="500" spans="1:6">
       <c r="A500" s="9" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B500" s="11" t="s">
         <v>228</v>
@@ -14913,13 +14913,13 @@
     </row>
     <row r="501" spans="1:6">
       <c r="A501" s="9" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="B501" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C501" s="15" t="s">
-        <v>1470</v>
+        <v>1464</v>
       </c>
       <c r="D501" s="9" t="s">
         <v>3</v>
@@ -14933,7 +14933,7 @@
     </row>
     <row r="502" spans="1:6">
       <c r="A502" s="9" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B502" s="11" t="s">
         <v>228</v>
@@ -14953,13 +14953,13 @@
     </row>
     <row r="503" spans="1:6">
       <c r="A503" s="9" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="B503" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C503" s="15" t="s">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="D503" s="9" t="s">
         <v>3</v>
@@ -14973,7 +14973,7 @@
     </row>
     <row r="504" spans="1:6">
       <c r="A504" s="9" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="B504" s="11" t="s">
         <v>228</v>
@@ -14993,13 +14993,13 @@
     </row>
     <row r="505" spans="1:6">
       <c r="A505" s="9" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="B505" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C505" s="13" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="D505" s="9" t="s">
         <v>3</v>
@@ -15013,7 +15013,7 @@
     </row>
     <row r="506" spans="1:6">
       <c r="A506" s="9" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="B506" s="11" t="s">
         <v>228</v>
@@ -15033,13 +15033,13 @@
     </row>
     <row r="507" spans="1:6">
       <c r="A507" s="9" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="B507" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C507" s="13" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="D507" s="9" t="s">
         <v>3</v>
@@ -15053,7 +15053,7 @@
     </row>
     <row r="508" spans="1:6">
       <c r="A508" s="9" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="B508" s="11" t="s">
         <v>228</v>
@@ -15073,13 +15073,13 @@
     </row>
     <row r="509" spans="1:6">
       <c r="A509" s="9" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="B509" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C509" s="13" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="D509" s="9" t="s">
         <v>3</v>
@@ -15093,7 +15093,7 @@
     </row>
     <row r="510" spans="1:6">
       <c r="A510" s="9" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="B510" s="11" t="s">
         <v>228</v>
@@ -15113,13 +15113,13 @@
     </row>
     <row r="511" spans="1:6">
       <c r="A511" s="9" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="B511" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C511" s="13" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="D511" s="9" t="s">
         <v>3</v>
@@ -15133,7 +15133,7 @@
     </row>
     <row r="512" spans="1:6">
       <c r="A512" s="9" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="B512" s="11" t="s">
         <v>228</v>
@@ -15153,13 +15153,13 @@
     </row>
     <row r="513" spans="1:6">
       <c r="A513" s="9" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="B513" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C513" s="13" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="D513" s="9" t="s">
         <v>3</v>
@@ -15173,7 +15173,7 @@
     </row>
     <row r="514" spans="1:6">
       <c r="A514" s="9" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="B514" s="11" t="s">
         <v>228</v>
@@ -15193,13 +15193,13 @@
     </row>
     <row r="515" spans="1:6">
       <c r="A515" s="9" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="B515" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C515" s="13" t="s">
-        <v>1472</v>
+        <v>1466</v>
       </c>
       <c r="D515" s="9" t="s">
         <v>3</v>
@@ -15213,7 +15213,7 @@
     </row>
     <row r="516" spans="1:6">
       <c r="A516" s="9" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B516" s="11" t="s">
         <v>228</v>
@@ -15233,13 +15233,13 @@
     </row>
     <row r="517" spans="1:6">
       <c r="A517" s="9" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="B517" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C517" s="13" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="D517" s="9" t="s">
         <v>3</v>
@@ -15253,7 +15253,7 @@
     </row>
     <row r="518" spans="1:6">
       <c r="A518" s="9" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="B518" s="11" t="s">
         <v>228</v>
@@ -15273,13 +15273,13 @@
     </row>
     <row r="519" spans="1:6">
       <c r="A519" s="9" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="B519" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C519" s="13" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="D519" s="9" t="s">
         <v>3</v>
@@ -15293,7 +15293,7 @@
     </row>
     <row r="520" spans="1:6">
       <c r="A520" s="9" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="B520" s="11" t="s">
         <v>228</v>
@@ -15313,13 +15313,13 @@
     </row>
     <row r="521" spans="1:6">
       <c r="A521" s="9" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="B521" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C521" s="13" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="D521" s="9" t="s">
         <v>3</v>
@@ -15333,7 +15333,7 @@
     </row>
     <row r="522" spans="1:6">
       <c r="A522" s="9" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="B522" s="11" t="s">
         <v>228</v>
@@ -15353,13 +15353,13 @@
     </row>
     <row r="523" spans="1:6">
       <c r="A523" s="9" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="B523" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C523" s="15" t="s">
-        <v>1473</v>
+        <v>1467</v>
       </c>
       <c r="D523" s="9" t="s">
         <v>3</v>
@@ -15368,12 +15368,12 @@
         <v>10</v>
       </c>
       <c r="F523" s="9" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
     </row>
     <row r="524" spans="1:6">
       <c r="A524" s="9" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="B524" s="11" t="s">
         <v>228</v>
@@ -15393,13 +15393,13 @@
     </row>
     <row r="525" spans="1:6">
       <c r="A525" s="9" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="B525" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C525" s="15" t="s">
-        <v>1474</v>
+        <v>1468</v>
       </c>
       <c r="D525" s="9" t="s">
         <v>3</v>
@@ -15413,7 +15413,7 @@
     </row>
     <row r="526" spans="1:6">
       <c r="A526" s="9" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="B526" s="11" t="s">
         <v>228</v>
@@ -15433,13 +15433,13 @@
     </row>
     <row r="527" spans="1:6">
       <c r="A527" s="9" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="B527" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C527" s="15" t="s">
-        <v>1475</v>
+        <v>1469</v>
       </c>
       <c r="D527" s="9" t="s">
         <v>3</v>
@@ -15453,7 +15453,7 @@
     </row>
     <row r="528" spans="1:6">
       <c r="A528" s="9" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="B528" s="11" t="s">
         <v>228</v>
@@ -15473,13 +15473,13 @@
     </row>
     <row r="529" spans="1:6">
       <c r="A529" s="9" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="B529" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C529" s="15" t="s">
-        <v>1476</v>
+        <v>1470</v>
       </c>
       <c r="D529" s="9" t="s">
         <v>3</v>
@@ -15493,7 +15493,7 @@
     </row>
     <row r="530" spans="1:6">
       <c r="A530" s="9" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="B530" s="11" t="s">
         <v>228</v>
@@ -15513,13 +15513,13 @@
     </row>
     <row r="531" spans="1:6">
       <c r="A531" s="9" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="B531" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C531" s="15" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="D531" s="9" t="s">
         <v>3</v>
@@ -15533,7 +15533,7 @@
     </row>
     <row r="532" spans="1:6">
       <c r="A532" s="9" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B532" s="11" t="s">
         <v>228</v>
@@ -15553,13 +15553,13 @@
     </row>
     <row r="533" spans="1:6">
       <c r="A533" s="9" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B533" s="11" t="s">
         <v>228</v>
       </c>
       <c r="C533" s="15" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="D533" s="9" t="s">
         <v>3</v>
@@ -15573,7 +15573,7 @@
     </row>
     <row r="534" spans="1:6">
       <c r="A534" s="9" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B534" s="11" t="s">
         <v>228</v>
@@ -15593,7 +15593,7 @@
     </row>
     <row r="535" spans="1:6">
       <c r="A535" s="9" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="B535" s="11" t="s">
         <v>228</v>
@@ -15613,7 +15613,7 @@
     </row>
     <row r="536" spans="1:6">
       <c r="A536" s="9" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="B536" s="11" t="s">
         <v>228</v>
@@ -15633,7 +15633,7 @@
     </row>
     <row r="537" spans="1:6">
       <c r="A537" s="9" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="B537" s="11" t="s">
         <v>228</v>
@@ -15648,12 +15648,12 @@
         <v>48</v>
       </c>
       <c r="F537" s="9" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="538" spans="1:6">
       <c r="A538" s="9" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B538" s="11" t="s">
         <v>228</v>
@@ -15673,7 +15673,7 @@
     </row>
     <row r="539" spans="1:6">
       <c r="A539" s="9" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="B539" s="11" t="s">
         <v>228</v>
@@ -15693,7 +15693,7 @@
     </row>
     <row r="540" spans="1:6">
       <c r="A540" s="9" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B540" s="11" t="s">
         <v>228</v>
@@ -15713,7 +15713,7 @@
     </row>
     <row r="541" spans="1:6">
       <c r="A541" s="9" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="B541" s="11" t="s">
         <v>228</v>
@@ -15733,7 +15733,7 @@
     </row>
     <row r="542" spans="1:6">
       <c r="A542" s="9" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B542" s="11" t="s">
         <v>228</v>
@@ -15753,7 +15753,7 @@
     </row>
     <row r="543" spans="1:6">
       <c r="A543" s="9" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="B543" s="11" t="s">
         <v>228</v>
@@ -15773,7 +15773,7 @@
     </row>
     <row r="544" spans="1:6">
       <c r="A544" s="9" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B544" s="11" t="s">
         <v>228</v>
@@ -15793,7 +15793,7 @@
     </row>
     <row r="545" spans="1:6">
       <c r="A545" s="9" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B545" s="11" t="s">
         <v>228</v>
@@ -15808,12 +15808,12 @@
         <v>160</v>
       </c>
       <c r="F545" s="9" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
     </row>
     <row r="546" spans="1:6">
       <c r="A546" s="9" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B546" s="11" t="s">
         <v>228</v>
@@ -15833,7 +15833,7 @@
     </row>
     <row r="547" spans="1:6">
       <c r="A547" s="9" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="B547" s="11" t="s">
         <v>228</v>
@@ -15853,7 +15853,7 @@
     </row>
     <row r="548" spans="1:6">
       <c r="A548" s="9" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B548" s="11" t="s">
         <v>228</v>
@@ -15873,7 +15873,7 @@
     </row>
     <row r="549" spans="1:6">
       <c r="A549" s="9" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="B549" s="11" t="s">
         <v>228</v>
@@ -15888,12 +15888,12 @@
         <v>158</v>
       </c>
       <c r="F549" s="9" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="550" spans="1:6">
       <c r="A550" s="9" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B550" s="11" t="s">
         <v>228</v>
@@ -15913,7 +15913,7 @@
     </row>
     <row r="551" spans="1:6">
       <c r="A551" s="9" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="B551" s="11" t="s">
         <v>228</v>
@@ -15928,12 +15928,12 @@
         <v>162</v>
       </c>
       <c r="F551" s="9" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="552" spans="1:6">
       <c r="A552" s="9" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B552" s="11" t="s">
         <v>228</v>
@@ -15953,7 +15953,7 @@
     </row>
     <row r="553" spans="1:6">
       <c r="A553" s="9" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="B553" s="10" t="s">
         <v>246</v>
@@ -15973,13 +15973,13 @@
     </row>
     <row r="554" spans="1:6">
       <c r="A554" s="9" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="B554" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C554" s="9" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="D554" s="9"/>
       <c r="E554" s="9"/>
@@ -15987,13 +15987,13 @@
     </row>
     <row r="555" spans="1:6">
       <c r="A555" s="9" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="B555" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C555" s="9" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D555" s="9"/>
       <c r="E555" s="9"/>
@@ -16001,7 +16001,7 @@
     </row>
     <row r="556" spans="1:6">
       <c r="A556" s="9" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="B556" s="11" t="s">
         <v>228</v>
@@ -16021,13 +16021,13 @@
     </row>
     <row r="557" spans="1:6">
       <c r="A557" s="9" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="B557" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C557" s="9" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="D557" s="9"/>
       <c r="E557" s="9"/>
@@ -16035,13 +16035,13 @@
     </row>
     <row r="558" spans="1:6">
       <c r="A558" s="9" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="B558" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C558" s="9" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="D558" s="9"/>
       <c r="E558" s="9"/>
@@ -16049,13 +16049,13 @@
     </row>
     <row r="559" spans="1:6">
       <c r="A559" s="9" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B559" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C559" s="9" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="D559" s="9"/>
       <c r="E559" s="9"/>
@@ -16063,13 +16063,13 @@
     </row>
     <row r="560" spans="1:6">
       <c r="A560" s="9" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="B560" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C560" s="9" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="D560" s="9"/>
       <c r="E560" s="9"/>
@@ -16077,13 +16077,13 @@
     </row>
     <row r="561" spans="1:6">
       <c r="A561" s="9" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="B561" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C561" s="9" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="D561" s="9"/>
       <c r="E561" s="9"/>
@@ -16091,13 +16091,13 @@
     </row>
     <row r="562" spans="1:6">
       <c r="A562" s="9" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="B562" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C562" s="9" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="D562" s="9"/>
       <c r="E562" s="9"/>
@@ -16105,13 +16105,13 @@
     </row>
     <row r="563" spans="1:6">
       <c r="A563" s="9" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="B563" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C563" s="9" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="D563" s="9"/>
       <c r="E563" s="9"/>
@@ -16119,13 +16119,13 @@
     </row>
     <row r="564" spans="1:6">
       <c r="A564" s="9" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="B564" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C564" s="9" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="D564" s="9"/>
       <c r="E564" s="9"/>
@@ -16133,13 +16133,13 @@
     </row>
     <row r="565" spans="1:6">
       <c r="A565" s="9" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="B565" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C565" s="9" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="D565" s="9"/>
       <c r="E565" s="9"/>
@@ -16147,13 +16147,13 @@
     </row>
     <row r="566" spans="1:6">
       <c r="A566" s="9" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="B566" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C566" s="9" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="D566" s="9"/>
       <c r="E566" s="9"/>
@@ -16161,13 +16161,13 @@
     </row>
     <row r="567" spans="1:6">
       <c r="A567" s="9" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="B567" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C567" s="9" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="D567" s="9"/>
       <c r="E567" s="9"/>
@@ -16175,13 +16175,13 @@
     </row>
     <row r="568" spans="1:6">
       <c r="A568" s="9" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="B568" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C568" s="9" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="D568" s="9"/>
       <c r="E568" s="9"/>
@@ -16189,13 +16189,13 @@
     </row>
     <row r="569" spans="1:6">
       <c r="A569" s="9" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="B569" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C569" s="9" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="D569" s="9"/>
       <c r="E569" s="9"/>
@@ -16203,13 +16203,13 @@
     </row>
     <row r="570" spans="1:6">
       <c r="A570" s="9" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="B570" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C570" s="9" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="D570" s="9"/>
       <c r="E570" s="9"/>
@@ -16217,13 +16217,13 @@
     </row>
     <row r="571" spans="1:6">
       <c r="A571" s="9" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="B571" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C571" s="9" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="D571" s="9"/>
       <c r="E571" s="9"/>
@@ -16231,13 +16231,13 @@
     </row>
     <row r="572" spans="1:6">
       <c r="A572" s="9" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="B572" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C572" s="9" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="D572" s="9"/>
       <c r="E572" s="9"/>
@@ -16245,13 +16245,13 @@
     </row>
     <row r="573" spans="1:6">
       <c r="A573" s="9" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="B573" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C573" s="9" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="D573" s="9"/>
       <c r="E573" s="9"/>
@@ -16259,13 +16259,13 @@
     </row>
     <row r="574" spans="1:6">
       <c r="A574" s="9" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B574" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C574" s="9" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="D574" s="9"/>
       <c r="E574" s="9"/>
@@ -16273,13 +16273,13 @@
     </row>
     <row r="575" spans="1:6">
       <c r="A575" s="9" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="B575" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C575" s="9" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="D575" s="9"/>
       <c r="E575" s="9"/>
@@ -16287,7 +16287,7 @@
     </row>
     <row r="576" spans="1:6">
       <c r="A576" s="9" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="B576" s="11" t="s">
         <v>228</v>
@@ -16307,13 +16307,13 @@
     </row>
     <row r="577" spans="1:6">
       <c r="A577" s="9" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="B577" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C577" s="9" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="D577" s="9"/>
       <c r="E577" s="9"/>
@@ -16321,13 +16321,13 @@
     </row>
     <row r="578" spans="1:6">
       <c r="A578" s="9" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="B578" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C578" s="9" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="D578" s="9"/>
       <c r="E578" s="9"/>
@@ -16335,13 +16335,13 @@
     </row>
     <row r="579" spans="1:6">
       <c r="A579" s="9" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="B579" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C579" s="9" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="D579" s="9"/>
       <c r="E579" s="9"/>
@@ -16349,13 +16349,13 @@
     </row>
     <row r="580" spans="1:6">
       <c r="A580" s="9" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="B580" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C580" s="9" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="D580" s="9"/>
       <c r="E580" s="9"/>
@@ -16363,13 +16363,13 @@
     </row>
     <row r="581" spans="1:6">
       <c r="A581" s="9" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="B581" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C581" s="9" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="D581" s="9"/>
       <c r="E581" s="9"/>
@@ -16377,13 +16377,13 @@
     </row>
     <row r="582" spans="1:6">
       <c r="A582" s="9" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="B582" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C582" s="9" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="D582" s="9"/>
       <c r="E582" s="9"/>
@@ -16391,13 +16391,13 @@
     </row>
     <row r="583" spans="1:6">
       <c r="A583" s="9" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="B583" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C583" s="9" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="D583" s="9"/>
       <c r="E583" s="9"/>
@@ -16405,13 +16405,13 @@
     </row>
     <row r="584" spans="1:6">
       <c r="A584" s="9" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="B584" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C584" s="9" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="D584" s="9"/>
       <c r="E584" s="9"/>
@@ -16419,13 +16419,13 @@
     </row>
     <row r="585" spans="1:6">
       <c r="A585" s="9" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="B585" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C585" s="9" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="D585" s="9"/>
       <c r="E585" s="9"/>
@@ -16433,13 +16433,13 @@
     </row>
     <row r="586" spans="1:6">
       <c r="A586" s="9" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="B586" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C586" s="9" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="D586" s="9"/>
       <c r="E586" s="9"/>
@@ -16447,13 +16447,13 @@
     </row>
     <row r="587" spans="1:6">
       <c r="A587" s="9" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="B587" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C587" s="9" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="D587" s="9"/>
       <c r="E587" s="9"/>
@@ -16461,13 +16461,13 @@
     </row>
     <row r="588" spans="1:6">
       <c r="A588" s="9" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="B588" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C588" s="9" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="D588" s="9"/>
       <c r="E588" s="9"/>
@@ -16475,13 +16475,13 @@
     </row>
     <row r="589" spans="1:6">
       <c r="A589" s="9" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="B589" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C589" s="9" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="D589" s="9"/>
       <c r="E589" s="9"/>
@@ -16489,13 +16489,13 @@
     </row>
     <row r="590" spans="1:6">
       <c r="A590" s="9" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="B590" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C590" s="9" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="D590" s="9"/>
       <c r="E590" s="9"/>
@@ -16503,13 +16503,13 @@
     </row>
     <row r="591" spans="1:6">
       <c r="A591" s="9" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="B591" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C591" s="9" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="D591" s="9"/>
       <c r="E591" s="9"/>
@@ -16517,13 +16517,13 @@
     </row>
     <row r="592" spans="1:6">
       <c r="A592" s="9" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="B592" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C592" s="9" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="D592" s="9"/>
       <c r="E592" s="9"/>
@@ -16531,13 +16531,13 @@
     </row>
     <row r="593" spans="1:6">
       <c r="A593" s="9" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="B593" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C593" s="9" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="D593" s="9"/>
       <c r="E593" s="9"/>
@@ -16545,13 +16545,13 @@
     </row>
     <row r="594" spans="1:6">
       <c r="A594" s="9" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="B594" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C594" s="9" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="D594" s="9"/>
       <c r="E594" s="9"/>
@@ -16559,13 +16559,13 @@
     </row>
     <row r="595" spans="1:6">
       <c r="A595" s="9" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="B595" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C595" s="9" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="D595" s="9"/>
       <c r="E595" s="9"/>
@@ -16573,13 +16573,13 @@
     </row>
     <row r="596" spans="1:6">
       <c r="A596" s="9" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="B596" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C596" s="9" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="D596" s="9"/>
       <c r="E596" s="9"/>
@@ -16587,13 +16587,13 @@
     </row>
     <row r="597" spans="1:6">
       <c r="A597" s="9" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="B597" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C597" s="9" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="D597" s="9"/>
       <c r="E597" s="9"/>
@@ -16601,13 +16601,13 @@
     </row>
     <row r="598" spans="1:6">
       <c r="A598" s="9" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="B598" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C598" s="9" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="D598" s="9"/>
       <c r="E598" s="9"/>
@@ -16615,13 +16615,13 @@
     </row>
     <row r="599" spans="1:6">
       <c r="A599" s="9" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="B599" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C599" s="9" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="D599" s="9"/>
       <c r="E599" s="9"/>
@@ -16629,13 +16629,13 @@
     </row>
     <row r="600" spans="1:6">
       <c r="A600" s="9" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="B600" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C600" s="9" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="D600" s="9"/>
       <c r="E600" s="9"/>
@@ -16643,13 +16643,13 @@
     </row>
     <row r="601" spans="1:6">
       <c r="A601" s="9" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="B601" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C601" s="9" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D601" s="9"/>
       <c r="E601" s="9"/>
@@ -16657,13 +16657,13 @@
     </row>
     <row r="602" spans="1:6">
       <c r="A602" s="9" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="B602" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C602" s="9" t="s">
-        <v>1178</v>
+        <v>1174</v>
       </c>
       <c r="D602" s="9"/>
       <c r="E602" s="9"/>
@@ -16671,7 +16671,7 @@
     </row>
     <row r="603" spans="1:6">
       <c r="A603" s="9" t="s">
-        <v>1179</v>
+        <v>1175</v>
       </c>
       <c r="B603" s="11" t="s">
         <v>228</v>
@@ -16691,13 +16691,13 @@
     </row>
     <row r="604" spans="1:6">
       <c r="A604" s="9" t="s">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="B604" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C604" s="9" t="s">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="D604" s="9"/>
       <c r="E604" s="9"/>
@@ -16705,13 +16705,13 @@
     </row>
     <row r="605" spans="1:6">
       <c r="A605" s="9" t="s">
-        <v>1182</v>
+        <v>1178</v>
       </c>
       <c r="B605" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C605" s="9" t="s">
-        <v>1183</v>
+        <v>1179</v>
       </c>
       <c r="D605" s="9"/>
       <c r="E605" s="9"/>
@@ -16719,7 +16719,7 @@
     </row>
     <row r="606" spans="1:6">
       <c r="A606" s="9" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="B606" s="11" t="s">
         <v>228</v>
@@ -16739,13 +16739,13 @@
     </row>
     <row r="607" spans="1:6">
       <c r="A607" s="9" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="B607" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C607" s="9" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="D607" s="9"/>
       <c r="E607" s="9"/>
@@ -16753,13 +16753,13 @@
     </row>
     <row r="608" spans="1:6">
       <c r="A608" s="9" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="B608" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C608" s="9" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D608" s="9"/>
       <c r="E608" s="9"/>
@@ -16767,13 +16767,13 @@
     </row>
     <row r="609" spans="1:6">
       <c r="A609" s="9" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="B609" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C609" s="9" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D609" s="9"/>
       <c r="E609" s="9"/>
@@ -16781,13 +16781,13 @@
     </row>
     <row r="610" spans="1:6">
       <c r="A610" s="9" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="B610" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C610" s="9" t="s">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="D610" s="9"/>
       <c r="E610" s="9"/>
@@ -16795,13 +16795,13 @@
     </row>
     <row r="611" spans="1:6">
       <c r="A611" s="9" t="s">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="B611" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C611" s="9" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="D611" s="9"/>
       <c r="E611" s="9"/>
@@ -16809,13 +16809,13 @@
     </row>
     <row r="612" spans="1:6">
       <c r="A612" s="9" t="s">
-        <v>1195</v>
+        <v>1191</v>
       </c>
       <c r="B612" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C612" s="9" t="s">
-        <v>1196</v>
+        <v>1192</v>
       </c>
       <c r="D612" s="9"/>
       <c r="E612" s="9"/>
@@ -16823,13 +16823,13 @@
     </row>
     <row r="613" spans="1:6">
       <c r="A613" s="9" t="s">
-        <v>1197</v>
+        <v>1193</v>
       </c>
       <c r="B613" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C613" s="9" t="s">
-        <v>1198</v>
+        <v>1194</v>
       </c>
       <c r="D613" s="9"/>
       <c r="E613" s="9"/>
@@ -16837,13 +16837,13 @@
     </row>
     <row r="614" spans="1:6">
       <c r="A614" s="9" t="s">
-        <v>1199</v>
+        <v>1195</v>
       </c>
       <c r="B614" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C614" s="9" t="s">
-        <v>1200</v>
+        <v>1196</v>
       </c>
       <c r="D614" s="9"/>
       <c r="E614" s="9"/>
@@ -16851,13 +16851,13 @@
     </row>
     <row r="615" spans="1:6">
       <c r="A615" s="9" t="s">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="B615" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C615" s="9" t="s">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="D615" s="9"/>
       <c r="E615" s="9"/>
@@ -16865,13 +16865,13 @@
     </row>
     <row r="616" spans="1:6">
       <c r="A616" s="9" t="s">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="B616" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C616" s="9" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="D616" s="9"/>
       <c r="E616" s="9"/>
@@ -16879,13 +16879,13 @@
     </row>
     <row r="617" spans="1:6">
       <c r="A617" s="9" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="B617" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C617" s="9" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="D617" s="9"/>
       <c r="E617" s="9"/>
@@ -16893,13 +16893,13 @@
     </row>
     <row r="618" spans="1:6">
       <c r="A618" s="9" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="B618" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C618" s="9" t="s">
-        <v>1208</v>
+        <v>1204</v>
       </c>
       <c r="D618" s="9"/>
       <c r="E618" s="9"/>
@@ -16907,13 +16907,13 @@
     </row>
     <row r="619" spans="1:6">
       <c r="A619" s="9" t="s">
-        <v>1209</v>
+        <v>1205</v>
       </c>
       <c r="B619" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C619" s="9" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="D619" s="9"/>
       <c r="E619" s="9"/>
@@ -16921,13 +16921,13 @@
     </row>
     <row r="620" spans="1:6">
       <c r="A620" s="9" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B620" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C620" s="9" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="D620" s="9"/>
       <c r="E620" s="9"/>
@@ -16935,13 +16935,13 @@
     </row>
     <row r="621" spans="1:6">
       <c r="A621" s="9" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="B621" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C621" s="9" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="D621" s="9"/>
       <c r="E621" s="9"/>
@@ -16949,13 +16949,13 @@
     </row>
     <row r="622" spans="1:6">
       <c r="A622" s="9" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="B622" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C622" s="9" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D622" s="9"/>
       <c r="E622" s="9"/>
@@ -16963,13 +16963,13 @@
     </row>
     <row r="623" spans="1:6">
       <c r="A623" s="9" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="B623" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C623" s="9" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="D623" s="9"/>
       <c r="E623" s="9"/>
@@ -16977,13 +16977,13 @@
     </row>
     <row r="624" spans="1:6">
       <c r="A624" s="9" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="B624" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C624" s="9" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="D624" s="9"/>
       <c r="E624" s="9"/>
@@ -16991,13 +16991,13 @@
     </row>
     <row r="625" spans="1:6">
       <c r="A625" s="9" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="B625" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C625" s="9" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="D625" s="9"/>
       <c r="E625" s="9"/>
@@ -17005,13 +17005,13 @@
     </row>
     <row r="626" spans="1:6">
       <c r="A626" s="9" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B626" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C626" s="9" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="D626" s="9"/>
       <c r="E626" s="9"/>
@@ -17019,13 +17019,13 @@
     </row>
     <row r="627" spans="1:6">
       <c r="A627" s="9" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="B627" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C627" s="9" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="D627" s="9"/>
       <c r="E627" s="9"/>
@@ -17033,13 +17033,13 @@
     </row>
     <row r="628" spans="1:6">
       <c r="A628" s="9" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="B628" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C628" s="9" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="D628" s="9"/>
       <c r="E628" s="9"/>
@@ -17047,13 +17047,13 @@
     </row>
     <row r="629" spans="1:6">
       <c r="A629" s="9" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="B629" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C629" s="9" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="D629" s="9"/>
       <c r="E629" s="9"/>
@@ -17061,13 +17061,13 @@
     </row>
     <row r="630" spans="1:6">
       <c r="A630" s="9" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="B630" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C630" s="9" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="D630" s="9"/>
       <c r="E630" s="9"/>
@@ -17075,13 +17075,13 @@
     </row>
     <row r="631" spans="1:6">
       <c r="A631" s="9" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="B631" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C631" s="9" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="D631" s="9"/>
       <c r="E631" s="9"/>
@@ -17089,13 +17089,13 @@
     </row>
     <row r="632" spans="1:6">
       <c r="A632" s="9" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="B632" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C632" s="9" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="D632" s="9"/>
       <c r="E632" s="9"/>
@@ -17103,13 +17103,13 @@
     </row>
     <row r="633" spans="1:6">
       <c r="A633" s="9" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="B633" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C633" s="9" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="D633" s="9"/>
       <c r="E633" s="9"/>
@@ -17117,13 +17117,13 @@
     </row>
     <row r="634" spans="1:6">
       <c r="A634" s="9" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B634" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C634" s="9" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="D634" s="9"/>
       <c r="E634" s="9"/>
@@ -17131,13 +17131,13 @@
     </row>
     <row r="635" spans="1:6">
       <c r="A635" s="9" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="B635" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C635" s="9" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="D635" s="9"/>
       <c r="E635" s="9"/>
@@ -17145,13 +17145,13 @@
     </row>
     <row r="636" spans="1:6">
       <c r="A636" s="9" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B636" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C636" s="9" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="D636" s="9"/>
       <c r="E636" s="9"/>
@@ -17159,13 +17159,13 @@
     </row>
     <row r="637" spans="1:6">
       <c r="A637" s="9" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="B637" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C637" s="9" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="D637" s="9"/>
       <c r="E637" s="9"/>
@@ -17173,13 +17173,13 @@
     </row>
     <row r="638" spans="1:6">
       <c r="A638" s="9" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="B638" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C638" s="9" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="D638" s="9"/>
       <c r="E638" s="9"/>
@@ -17187,13 +17187,13 @@
     </row>
     <row r="639" spans="1:6">
       <c r="A639" s="9" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="B639" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C639" s="9" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="D639" s="9"/>
       <c r="E639" s="9"/>
@@ -17201,13 +17201,13 @@
     </row>
     <row r="640" spans="1:6">
       <c r="A640" s="9" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="B640" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C640" s="9" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="D640" s="9"/>
       <c r="E640" s="9"/>
@@ -17215,13 +17215,13 @@
     </row>
     <row r="641" spans="1:6">
       <c r="A641" s="9" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="B641" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C641" s="9" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="D641" s="9"/>
       <c r="E641" s="9"/>
@@ -17229,13 +17229,13 @@
     </row>
     <row r="642" spans="1:6">
       <c r="A642" s="9" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="B642" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C642" s="9" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="D642" s="9"/>
       <c r="E642" s="9"/>
@@ -17243,13 +17243,13 @@
     </row>
     <row r="643" spans="1:6">
       <c r="A643" s="9" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="B643" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C643" s="9" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="D643" s="9"/>
       <c r="E643" s="9"/>
@@ -17257,13 +17257,13 @@
     </row>
     <row r="644" spans="1:6">
       <c r="A644" s="9" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B644" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C644" s="9" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="D644" s="9"/>
       <c r="E644" s="9"/>
@@ -17271,13 +17271,13 @@
     </row>
     <row r="645" spans="1:6">
       <c r="A645" s="9" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="B645" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C645" s="9" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="D645" s="9"/>
       <c r="E645" s="9"/>
@@ -17285,13 +17285,13 @@
     </row>
     <row r="646" spans="1:6">
       <c r="A646" s="9" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="B646" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C646" s="9" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="D646" s="9"/>
       <c r="E646" s="9"/>
@@ -17299,13 +17299,13 @@
     </row>
     <row r="647" spans="1:6">
       <c r="A647" s="9" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="B647" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C647" s="9" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="D647" s="9"/>
       <c r="E647" s="9"/>
@@ -17313,13 +17313,13 @@
     </row>
     <row r="648" spans="1:6">
       <c r="A648" s="9" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="B648" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C648" s="9" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="D648" s="9"/>
       <c r="E648" s="9"/>
@@ -17327,13 +17327,13 @@
     </row>
     <row r="649" spans="1:6">
       <c r="A649" s="9" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="B649" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C649" s="9" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="D649" s="9"/>
       <c r="E649" s="9"/>
@@ -17341,13 +17341,13 @@
     </row>
     <row r="650" spans="1:6">
       <c r="A650" s="9" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="B650" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C650" s="9" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="D650" s="9"/>
       <c r="E650" s="9"/>
@@ -17355,13 +17355,13 @@
     </row>
     <row r="651" spans="1:6">
       <c r="A651" s="9" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="B651" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C651" s="9" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="D651" s="9"/>
       <c r="E651" s="9"/>
@@ -17369,13 +17369,13 @@
     </row>
     <row r="652" spans="1:6">
       <c r="A652" s="9" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="B652" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C652" s="9" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="D652" s="9"/>
       <c r="E652" s="9"/>
@@ -17383,13 +17383,13 @@
     </row>
     <row r="653" spans="1:6">
       <c r="A653" s="9" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="B653" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C653" s="9" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="D653" s="9"/>
       <c r="E653" s="9"/>
@@ -17397,13 +17397,13 @@
     </row>
     <row r="654" spans="1:6">
       <c r="A654" s="9" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="B654" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C654" s="9" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="D654" s="9"/>
       <c r="E654" s="9"/>
@@ -17411,13 +17411,13 @@
     </row>
     <row r="655" spans="1:6">
       <c r="A655" s="9" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="B655" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C655" s="9" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="D655" s="9"/>
       <c r="E655" s="9"/>
@@ -17425,13 +17425,13 @@
     </row>
     <row r="656" spans="1:6">
       <c r="A656" s="9" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="B656" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C656" s="9" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="D656" s="9"/>
       <c r="E656" s="9"/>
@@ -17439,13 +17439,13 @@
     </row>
     <row r="657" spans="1:6">
       <c r="A657" s="9" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="B657" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C657" s="9" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="D657" s="9"/>
       <c r="E657" s="9"/>
@@ -17453,13 +17453,13 @@
     </row>
     <row r="658" spans="1:6">
       <c r="A658" s="9" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="B658" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C658" s="9" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="D658" s="9"/>
       <c r="E658" s="9"/>
@@ -17467,13 +17467,13 @@
     </row>
     <row r="659" spans="1:6">
       <c r="A659" s="9" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="B659" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C659" s="9" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="D659" s="9"/>
       <c r="E659" s="9"/>
@@ -17481,13 +17481,13 @@
     </row>
     <row r="660" spans="1:6">
       <c r="A660" s="9" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="B660" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C660" s="9" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="D660" s="9"/>
       <c r="E660" s="9"/>
@@ -17495,13 +17495,13 @@
     </row>
     <row r="661" spans="1:6">
       <c r="A661" s="9" t="s">
-        <v>1293</v>
+        <v>1289</v>
       </c>
       <c r="B661" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C661" s="9" t="s">
-        <v>1294</v>
+        <v>1290</v>
       </c>
       <c r="D661" s="9"/>
       <c r="E661" s="9"/>
@@ -17509,13 +17509,13 @@
     </row>
     <row r="662" spans="1:6">
       <c r="A662" s="9" t="s">
-        <v>1295</v>
+        <v>1291</v>
       </c>
       <c r="B662" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C662" s="9" t="s">
-        <v>1296</v>
+        <v>1292</v>
       </c>
       <c r="D662" s="9"/>
       <c r="E662" s="9"/>
@@ -17523,13 +17523,13 @@
     </row>
     <row r="663" spans="1:6">
       <c r="A663" s="9" t="s">
-        <v>1297</v>
+        <v>1293</v>
       </c>
       <c r="B663" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C663" s="9" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="D663" s="9"/>
       <c r="E663" s="9"/>
@@ -17537,13 +17537,13 @@
     </row>
     <row r="664" spans="1:6">
       <c r="A664" s="9" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="B664" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C664" s="9" t="s">
-        <v>1300</v>
+        <v>1296</v>
       </c>
       <c r="D664" s="9"/>
       <c r="E664" s="9"/>
@@ -17551,13 +17551,13 @@
     </row>
     <row r="665" spans="1:6">
       <c r="A665" s="9" t="s">
-        <v>1301</v>
+        <v>1297</v>
       </c>
       <c r="B665" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C665" s="9" t="s">
-        <v>1302</v>
+        <v>1298</v>
       </c>
       <c r="D665" s="9"/>
       <c r="E665" s="9"/>
@@ -17565,13 +17565,13 @@
     </row>
     <row r="666" spans="1:6">
       <c r="A666" s="9" t="s">
-        <v>1303</v>
+        <v>1299</v>
       </c>
       <c r="B666" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C666" s="9" t="s">
-        <v>1304</v>
+        <v>1300</v>
       </c>
       <c r="D666" s="9"/>
       <c r="E666" s="9"/>
@@ -17579,13 +17579,13 @@
     </row>
     <row r="667" spans="1:6">
       <c r="A667" s="9" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B667" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C667" s="9" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="D667" s="9"/>
       <c r="E667" s="9"/>
@@ -17593,13 +17593,13 @@
     </row>
     <row r="668" spans="1:6">
       <c r="A668" s="9" t="s">
-        <v>1307</v>
+        <v>1303</v>
       </c>
       <c r="B668" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C668" s="9" t="s">
-        <v>1308</v>
+        <v>1304</v>
       </c>
       <c r="D668" s="9"/>
       <c r="E668" s="9"/>
@@ -17607,13 +17607,13 @@
     </row>
     <row r="669" spans="1:6">
       <c r="A669" s="9" t="s">
-        <v>1309</v>
+        <v>1305</v>
       </c>
       <c r="B669" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C669" s="9" t="s">
-        <v>1310</v>
+        <v>1306</v>
       </c>
       <c r="D669" s="9"/>
       <c r="E669" s="9"/>
@@ -17621,13 +17621,13 @@
     </row>
     <row r="670" spans="1:6">
       <c r="A670" s="9" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="B670" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C670" s="9" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="D670" s="9"/>
       <c r="E670" s="9"/>
@@ -17635,13 +17635,13 @@
     </row>
     <row r="671" spans="1:6">
       <c r="A671" s="9" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="B671" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C671" s="9" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="D671" s="9"/>
       <c r="E671" s="9"/>
@@ -17649,13 +17649,13 @@
     </row>
     <row r="672" spans="1:6">
       <c r="A672" s="9" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="B672" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C672" s="9" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="D672" s="9"/>
       <c r="E672" s="9"/>
@@ -17663,13 +17663,13 @@
     </row>
     <row r="673" spans="1:6">
       <c r="A673" s="9" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="B673" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C673" s="9" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="D673" s="9"/>
       <c r="E673" s="9"/>
@@ -17677,13 +17677,13 @@
     </row>
     <row r="674" spans="1:6">
       <c r="A674" s="9" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="B674" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C674" s="9" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="D674" s="9"/>
       <c r="E674" s="9"/>
@@ -17691,13 +17691,13 @@
     </row>
     <row r="675" spans="1:6">
       <c r="A675" s="9" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="B675" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C675" s="9" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="D675" s="9"/>
       <c r="E675" s="9"/>
@@ -17705,13 +17705,13 @@
     </row>
     <row r="676" spans="1:6">
       <c r="A676" s="9" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="B676" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C676" s="9" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="D676" s="9"/>
       <c r="E676" s="9"/>
@@ -17719,13 +17719,13 @@
     </row>
     <row r="677" spans="1:6">
       <c r="A677" s="9" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="B677" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C677" s="9" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="D677" s="9"/>
       <c r="E677" s="9"/>
@@ -17733,13 +17733,13 @@
     </row>
     <row r="678" spans="1:6">
       <c r="A678" s="9" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="B678" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C678" s="9" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="D678" s="9"/>
       <c r="E678" s="9"/>
@@ -17747,13 +17747,13 @@
     </row>
     <row r="679" spans="1:6">
       <c r="A679" s="9" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="B679" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C679" s="9" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="D679" s="9"/>
       <c r="E679" s="9"/>
@@ -17761,13 +17761,13 @@
     </row>
     <row r="680" spans="1:6">
       <c r="A680" s="9" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="B680" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C680" s="9" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="D680" s="9"/>
       <c r="E680" s="9"/>
@@ -17775,13 +17775,13 @@
     </row>
     <row r="681" spans="1:6">
       <c r="A681" s="9" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="B681" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C681" s="9" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="D681" s="9"/>
       <c r="E681" s="9"/>
@@ -17789,13 +17789,13 @@
     </row>
     <row r="682" spans="1:6">
       <c r="A682" s="9" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="B682" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C682" s="9" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="D682" s="9"/>
       <c r="E682" s="9"/>
@@ -17803,13 +17803,13 @@
     </row>
     <row r="683" spans="1:6">
       <c r="A683" s="9" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="B683" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C683" s="9" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="D683" s="9"/>
       <c r="E683" s="9"/>
@@ -17817,13 +17817,13 @@
     </row>
     <row r="684" spans="1:6">
       <c r="A684" s="9" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="B684" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C684" s="9" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="D684" s="9"/>
       <c r="E684" s="9"/>
@@ -17831,13 +17831,13 @@
     </row>
     <row r="685" spans="1:6">
       <c r="A685" s="9" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="B685" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C685" s="9" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="D685" s="9"/>
       <c r="E685" s="9"/>
@@ -17845,13 +17845,13 @@
     </row>
     <row r="686" spans="1:6">
       <c r="A686" s="9" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="B686" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C686" s="9" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="D686" s="9"/>
       <c r="E686" s="9"/>
@@ -17859,13 +17859,13 @@
     </row>
     <row r="687" spans="1:6">
       <c r="A687" s="9" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="B687" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C687" s="9" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="D687" s="9"/>
       <c r="E687" s="9"/>
@@ -17873,13 +17873,13 @@
     </row>
     <row r="688" spans="1:6">
       <c r="A688" s="9" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="B688" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C688" s="9" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="D688" s="9"/>
       <c r="E688" s="9"/>
@@ -17887,13 +17887,13 @@
     </row>
     <row r="689" spans="1:6">
       <c r="A689" s="9" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="B689" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C689" s="9" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="D689" s="9"/>
       <c r="E689" s="9"/>
@@ -17901,13 +17901,13 @@
     </row>
     <row r="690" spans="1:6">
       <c r="A690" s="9" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="B690" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C690" s="9" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D690" s="9"/>
       <c r="E690" s="9"/>
@@ -17915,13 +17915,13 @@
     </row>
     <row r="691" spans="1:6">
       <c r="A691" s="9" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="B691" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C691" s="9" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="D691" s="9"/>
       <c r="E691" s="9"/>
@@ -17929,13 +17929,13 @@
     </row>
     <row r="692" spans="1:6">
       <c r="A692" s="9" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="B692" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C692" s="9" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="D692" s="9"/>
       <c r="E692" s="9"/>
@@ -17943,13 +17943,13 @@
     </row>
     <row r="693" spans="1:6">
       <c r="A693" s="9" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="B693" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C693" s="9" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="D693" s="9"/>
       <c r="E693" s="9"/>
@@ -17957,13 +17957,13 @@
     </row>
     <row r="694" spans="1:6">
       <c r="A694" s="9" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="B694" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C694" s="9" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="D694" s="9"/>
       <c r="E694" s="9"/>
@@ -17971,13 +17971,13 @@
     </row>
     <row r="695" spans="1:6">
       <c r="A695" s="9" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="B695" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C695" s="9" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="D695" s="9"/>
       <c r="E695" s="9"/>
@@ -17985,13 +17985,13 @@
     </row>
     <row r="696" spans="1:6">
       <c r="A696" s="9" t="s">
-        <v>1363</v>
+        <v>1359</v>
       </c>
       <c r="B696" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C696" s="9" t="s">
-        <v>1364</v>
+        <v>1360</v>
       </c>
       <c r="D696" s="9"/>
       <c r="E696" s="9"/>
@@ -17999,13 +17999,13 @@
     </row>
     <row r="697" spans="1:6">
       <c r="A697" s="9" t="s">
-        <v>1365</v>
+        <v>1361</v>
       </c>
       <c r="B697" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C697" s="9" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="D697" s="9"/>
       <c r="E697" s="9"/>
@@ -18013,13 +18013,13 @@
     </row>
     <row r="698" spans="1:6">
       <c r="A698" s="9" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="B698" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C698" s="9" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="D698" s="9"/>
       <c r="E698" s="9"/>
@@ -18027,13 +18027,13 @@
     </row>
     <row r="699" spans="1:6">
       <c r="A699" s="9" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="B699" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C699" s="9" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="D699" s="9"/>
       <c r="E699" s="9"/>
@@ -18041,13 +18041,13 @@
     </row>
     <row r="700" spans="1:6">
       <c r="A700" s="9" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="B700" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C700" s="9" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="D700" s="9"/>
       <c r="E700" s="9"/>
@@ -18055,13 +18055,13 @@
     </row>
     <row r="701" spans="1:6">
       <c r="A701" s="9" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="B701" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C701" s="9" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="D701" s="9"/>
       <c r="E701" s="9"/>
@@ -18069,13 +18069,13 @@
     </row>
     <row r="702" spans="1:6">
       <c r="A702" s="9" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="B702" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C702" s="9" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="D702" s="9"/>
       <c r="E702" s="9"/>
@@ -18083,13 +18083,13 @@
     </row>
     <row r="703" spans="1:6">
       <c r="A703" s="9" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="B703" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C703" s="9" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="D703" s="9"/>
       <c r="E703" s="9"/>
@@ -18097,13 +18097,13 @@
     </row>
     <row r="704" spans="1:6">
       <c r="A704" s="9" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="B704" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C704" s="9" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="D704" s="9"/>
       <c r="E704" s="9"/>
@@ -18111,13 +18111,13 @@
     </row>
     <row r="705" spans="1:6">
       <c r="A705" s="9" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="B705" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C705" s="9" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="D705" s="9"/>
       <c r="E705" s="9"/>
@@ -18125,13 +18125,13 @@
     </row>
     <row r="706" spans="1:6">
       <c r="A706" s="9" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="B706" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C706" s="9" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="D706" s="9"/>
       <c r="E706" s="9"/>
@@ -18139,13 +18139,13 @@
     </row>
     <row r="707" spans="1:6">
       <c r="A707" s="9" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="B707" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C707" s="9" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="D707" s="9"/>
       <c r="E707" s="9"/>
@@ -18153,13 +18153,13 @@
     </row>
     <row r="708" spans="1:6">
       <c r="A708" s="9" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="B708" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C708" s="9" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="D708" s="9"/>
       <c r="E708" s="9"/>
@@ -18167,13 +18167,13 @@
     </row>
     <row r="709" spans="1:6">
       <c r="A709" s="9" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="B709" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C709" s="9" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="D709" s="9"/>
       <c r="E709" s="9"/>
@@ -18181,13 +18181,13 @@
     </row>
     <row r="710" spans="1:6">
       <c r="A710" s="9" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="B710" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C710" s="9" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="D710" s="9"/>
       <c r="E710" s="9"/>
@@ -18195,13 +18195,13 @@
     </row>
     <row r="711" spans="1:6">
       <c r="A711" s="9" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="B711" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C711" s="9" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="D711" s="9"/>
       <c r="E711" s="9"/>
@@ -18209,13 +18209,13 @@
     </row>
     <row r="712" spans="1:6">
       <c r="A712" s="9" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="B712" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C712" s="9" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="D712" s="9"/>
       <c r="E712" s="9"/>
@@ -18223,13 +18223,13 @@
     </row>
     <row r="713" spans="1:6">
       <c r="A713" s="9" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="B713" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C713" s="9" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="D713" s="9"/>
       <c r="E713" s="9"/>
@@ -18237,13 +18237,13 @@
     </row>
     <row r="714" spans="1:6">
       <c r="A714" s="9" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="B714" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C714" s="9" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="D714" s="9"/>
       <c r="E714" s="9"/>
@@ -18251,13 +18251,13 @@
     </row>
     <row r="715" spans="1:6">
       <c r="A715" s="9" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B715" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C715" s="9" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="D715" s="9"/>
       <c r="E715" s="9"/>
@@ -18265,13 +18265,13 @@
     </row>
     <row r="716" spans="1:6">
       <c r="A716" s="9" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B716" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C716" s="9" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="D716" s="9"/>
       <c r="E716" s="9"/>
@@ -18279,13 +18279,13 @@
     </row>
     <row r="717" spans="1:6">
       <c r="A717" s="9" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B717" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C717" s="9" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="D717" s="9"/>
       <c r="E717" s="9"/>
@@ -18293,13 +18293,13 @@
     </row>
     <row r="718" spans="1:6">
       <c r="A718" s="9" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B718" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C718" s="9" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="D718" s="9"/>
       <c r="E718" s="9"/>
@@ -18307,13 +18307,13 @@
     </row>
     <row r="719" spans="1:6">
       <c r="A719" s="9" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B719" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C719" s="9" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="D719" s="9"/>
       <c r="E719" s="9"/>
@@ -18321,13 +18321,13 @@
     </row>
     <row r="720" spans="1:6">
       <c r="A720" s="9" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B720" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C720" s="9" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="D720" s="9"/>
       <c r="E720" s="9"/>
@@ -18335,13 +18335,13 @@
     </row>
     <row r="721" spans="1:6">
       <c r="A721" s="9" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="B721" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C721" s="9" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="D721" s="9"/>
       <c r="E721" s="9"/>
@@ -18349,13 +18349,13 @@
     </row>
     <row r="722" spans="1:6">
       <c r="A722" s="9" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B722" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C722" s="9" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="D722" s="9"/>
       <c r="E722" s="9"/>
@@ -18363,13 +18363,13 @@
     </row>
     <row r="723" spans="1:6">
       <c r="A723" s="9" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="B723" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C723" s="9" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="D723" s="9"/>
       <c r="E723" s="9"/>
@@ -18377,13 +18377,13 @@
     </row>
     <row r="724" spans="1:6">
       <c r="A724" s="9" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="B724" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C724" s="9" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="D724" s="9"/>
       <c r="E724" s="9"/>
@@ -18391,13 +18391,13 @@
     </row>
     <row r="725" spans="1:6">
       <c r="A725" s="9" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="B725" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C725" s="9" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="D725" s="9"/>
       <c r="E725" s="9"/>
@@ -18405,13 +18405,13 @@
     </row>
     <row r="726" spans="1:6">
       <c r="A726" s="9" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="B726" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C726" s="9" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="D726" s="9"/>
       <c r="E726" s="9"/>
@@ -18419,13 +18419,13 @@
     </row>
     <row r="727" spans="1:6">
       <c r="A727" s="9" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="B727" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C727" s="9" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="D727" s="9"/>
       <c r="E727" s="9"/>
@@ -18433,13 +18433,13 @@
     </row>
     <row r="728" spans="1:6">
       <c r="A728" s="9" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="B728" s="12" t="s">
         <v>223</v>
       </c>
       <c r="C728" s="9" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="D728" s="9"/>
       <c r="E728" s="9"/>
@@ -18448,35 +18448,35 @@
   </sheetData>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="C2:C7 C304:C307 C9:C289 C310:C408 C410:C545">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>ISNUMBER(SEARCH("不明",C2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E7 E9:E545">
-    <cfRule type="expression" dxfId="6" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>ISNUMBER(SEARCH("不明",E2))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B7 B9:B545">
-    <cfRule type="expression" dxfId="5" priority="7">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>B2="controller"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="8">
+    <cfRule type="expression" dxfId="3" priority="8">
       <formula>B2="kb/mouse"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C308:C309">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>ISNUMBER(SEARCH("不明",C308))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C290:C303">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>ISNUMBER(SEARCH("不明",C290))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C409">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>ISNUMBER(SEARCH("不明",C409))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/bpsr_key_table.xlsx
+++ b/bpsr_key_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\GitHub\BPSRControllerHelper\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B489F0-E900-43F1-BEF9-FF814CF0BDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BE9377-B140-4EE7-8F98-51B675E14E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4161" uniqueCount="1477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4161" uniqueCount="1478">
   <si>
     <t>入力種別</t>
   </si>
@@ -4553,6 +4553,10 @@
     <rPh sb="20" eb="21">
       <t>ウエ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ソーシャルモード</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -13290,8 +13294,8 @@
       <c r="B419" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="C419" s="13" t="s">
-        <v>238</v>
+      <c r="C419" s="14" t="s">
+        <v>1477</v>
       </c>
       <c r="D419" s="9" t="s">
         <v>3</v>
@@ -13310,8 +13314,8 @@
       <c r="B420" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C420" s="13" t="s">
-        <v>238</v>
+      <c r="C420" s="9" t="s">
+        <v>377</v>
       </c>
       <c r="D420" s="9" t="s">
         <v>16</v>
@@ -13391,7 +13395,7 @@
         <v>228</v>
       </c>
       <c r="C424" s="14" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="D424" s="9" t="s">
         <v>3</v>
@@ -13411,7 +13415,7 @@
         <v>228</v>
       </c>
       <c r="C425" s="14" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="D425" s="9" t="s">
         <v>3</v>
